--- a/data/ABLE Dataset.xlsx
+++ b/data/ABLE Dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BonoGONG/Desktop/8.Paper_draft/Paper_materials/Version10_full_data/1.Main_Figures/Figure5/Fig5B-E.ABLE_performance/B-E1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BonoGONG/Desktop/8.Paper_draft/Paper_materials/Version13_full_NC/4.Github_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBBE5ED-45E6-5F40-9136-E8DDD3CC1C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97988280-A2BC-E748-9D3C-97DB403E7181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="26240" windowHeight="14560" xr2:uid="{0674E527-E1AB-E348-9FF3-CA6262F7D631}"/>
+    <workbookView xWindow="-35600" yWindow="2240" windowWidth="26240" windowHeight="14560" xr2:uid="{0674E527-E1AB-E348-9FF3-CA6262F7D631}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -836,184 +836,10 @@
     <t>N' monomer</t>
   </si>
   <si>
-    <r>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>D,N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (nM)</t>
-    </r>
-  </si>
-  <si>
     <t>C' monomer</t>
   </si>
   <si>
-    <r>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>D,C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (nM)</t>
-    </r>
-  </si>
-  <si>
     <t>Biparatopic dimer</t>
-  </si>
-  <si>
-    <r>
-      <t>K</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>D,Bipara</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (nM)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>d</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>epi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Å)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>L</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>link</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Å）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>mono</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Å）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>link</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>area,N</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1047,21 +873,6 @@
   </si>
   <si>
     <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>area,C</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Polar A</t>
     </r>
     <r>
@@ -1091,21 +902,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>area</t>
-    </r>
-  </si>
-  <si>
     <t>N hydrogen bond</t>
   </si>
   <si>
@@ -1115,21 +911,6 @@
     <t>N salt bridge</t>
   </si>
   <si>
-    <r>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t,N</t>
-    </r>
-  </si>
-  <si>
     <t>C hydrogen bond</t>
   </si>
   <si>
@@ -1139,47 +920,46 @@
     <t>C salt bridge</t>
   </si>
   <si>
-    <r>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t,C</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>bond</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>geometry</t>
-    </r>
+    <t>n_bonds_C</t>
+  </si>
+  <si>
+    <t>n_bonds_N</t>
+  </si>
+  <si>
+    <t>R_bond</t>
+  </si>
+  <si>
+    <t>L_link</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>d_epi</t>
+  </si>
+  <si>
+    <t>KD_N</t>
+  </si>
+  <si>
+    <t>R_link</t>
+  </si>
+  <si>
+    <t>KD_C</t>
+  </si>
+  <si>
+    <t>KD_bipara</t>
+  </si>
+  <si>
+    <t>D_mono</t>
+  </si>
+  <si>
+    <t>R_area</t>
+  </si>
+  <si>
+    <t>AN</t>
+  </si>
+  <si>
+    <t>S_geometry</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +970,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1247,19 +1027,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri (Body)"/>
     </font>
     <font>
       <sz val="13"/>
@@ -1336,7 +1103,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1694,85 +1461,85 @@
         <v>256</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>93</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>192</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="W1" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="X1" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="AA1" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="Q1" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="R1" s="3" t="s">
+      <c r="AB1" s="10" t="s">
         <v>271</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB1" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="AC1" s="10" t="s">
         <v>282</v>

--- a/data/ABLE Dataset.xlsx
+++ b/data/ABLE Dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BonoGONG/Desktop/8.Paper_draft/Paper_materials/Version13_full_NC/4.Github_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2339BB80-8D86-104D-A4BA-2ADE76A41828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5FD740-3432-2743-9DD1-28A4D4D320BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-68720" yWindow="1640" windowWidth="26240" windowHeight="14560" xr2:uid="{0674E527-E1AB-E348-9FF3-CA6262F7D631}"/>
+    <workbookView xWindow="-76800" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{0674E527-E1AB-E348-9FF3-CA6262F7D631}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="240">
   <si>
     <t>7D12–9G8</t>
   </si>
@@ -222,9 +222,6 @@
     <t>BBsR29</t>
   </si>
   <si>
-    <t>BBsR32</t>
-  </si>
-  <si>
     <t>BBsR37</t>
   </si>
   <si>
@@ -474,9 +471,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>S9R4P1A3</t>
-  </si>
-  <si>
     <t>S9R4P4F10</t>
   </si>
   <si>
@@ -558,10 +552,6 @@
   </si>
   <si>
     <t>BBsR26-L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BBsR32-L</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1289,7 +1279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25302E3-D780-C043-8AFB-452B651797D6}">
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -1326,102 +1316,102 @@
   <sheetData>
     <row r="1" spans="1:29" ht="18">
       <c r="A1" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="P1" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="T1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC1" s="7" t="s">
         <v>239</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="17">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2">
         <v>10.4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" s="2">
         <v>14.4</v>
@@ -1439,7 +1429,7 @@
         <v>28.285</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J2" s="2">
         <v>36</v>
@@ -1505,13 +1495,13 @@
     </row>
     <row r="3" spans="1:29" ht="17">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="2">
         <v>14.4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2">
         <v>10.4</v>
@@ -1529,7 +1519,7 @@
         <v>28.285</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J3" s="2">
         <v>36</v>
@@ -1595,13 +1585,13 @@
     </row>
     <row r="4" spans="1:29" ht="17">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2">
         <v>2.6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2">
         <v>16.3</v>
@@ -1619,7 +1609,7 @@
         <v>3.7429999999999999</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J4" s="2">
         <v>54</v>
@@ -1685,13 +1675,13 @@
     </row>
     <row r="5" spans="1:29" ht="17">
       <c r="A5" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="2">
         <v>2.6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2">
         <v>3.31</v>
@@ -1709,7 +1699,7 @@
         <v>14.116</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J5" s="2">
         <v>54</v>
@@ -1775,13 +1765,13 @@
     </row>
     <row r="6" spans="1:29" ht="17">
       <c r="A6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" s="2">
         <v>8.6880000000000006</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" s="2">
         <v>2.6309999999999998</v>
@@ -1799,7 +1789,7 @@
         <v>22.439</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J6" s="2">
         <v>121.80500000000001</v>
@@ -1865,13 +1855,13 @@
     </row>
     <row r="7" spans="1:29" ht="17">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="2">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2">
         <v>891</v>
@@ -1889,7 +1879,7 @@
         <v>2.4180000000000001</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J7" s="2">
         <v>72</v>
@@ -1955,13 +1945,13 @@
     </row>
     <row r="8" spans="1:29" ht="17">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2">
         <v>6.61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" s="2">
         <v>891</v>
@@ -1979,7 +1969,7 @@
         <v>2.859</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J8" s="2">
         <v>72</v>
@@ -2045,13 +2035,13 @@
     </row>
     <row r="9" spans="1:29" ht="17">
       <c r="A9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2">
         <v>6.61</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2">
         <v>112</v>
@@ -2069,7 +2059,7 @@
         <v>-1.6919999999999999</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J9" s="2">
         <v>72</v>
@@ -2135,13 +2125,13 @@
     </row>
     <row r="10" spans="1:29" ht="17">
       <c r="A10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2">
         <v>0.3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" s="2">
         <v>32.299999999999997</v>
@@ -2159,7 +2149,7 @@
         <v>8.6029999999999998</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J10" s="2">
         <v>72</v>
@@ -2225,13 +2215,13 @@
     </row>
     <row r="11" spans="1:29" ht="17">
       <c r="A11" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" s="2">
         <v>0.3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2">
         <v>3.1</v>
@@ -2249,7 +2239,7 @@
         <v>6.4989999999999997</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J11" s="2">
         <v>72</v>
@@ -2315,13 +2305,13 @@
     </row>
     <row r="12" spans="1:29" ht="17">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" s="2">
         <v>0.3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" s="2">
         <v>18</v>
@@ -2339,7 +2329,7 @@
         <v>20.423999999999999</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J12" s="2">
         <v>72</v>
@@ -2405,13 +2395,13 @@
     </row>
     <row r="13" spans="1:29" ht="17">
       <c r="A13" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2">
         <v>0.3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" s="2">
         <v>27.3</v>
@@ -2429,7 +2419,7 @@
         <v>10.417999999999999</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J13" s="2">
         <v>72</v>
@@ -2495,13 +2485,13 @@
     </row>
     <row r="14" spans="1:29" ht="17">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14" s="2">
         <v>3.85</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" s="2">
         <v>1.45</v>
@@ -2519,7 +2509,7 @@
         <v>33.926000000000002</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J14" s="2">
         <v>36</v>
@@ -2585,13 +2575,13 @@
     </row>
     <row r="15" spans="1:29" ht="17">
       <c r="A15" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B15" s="2">
         <v>6.02</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D15" s="2">
         <v>55.44</v>
@@ -2609,7 +2599,7 @@
         <v>40.637</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J15" s="2">
         <v>54</v>
@@ -2675,13 +2665,13 @@
     </row>
     <row r="16" spans="1:29" ht="17">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16" s="2">
         <v>20.52</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" s="2">
         <v>55.44</v>
@@ -2699,7 +2689,7 @@
         <v>17.477</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J16" s="2">
         <v>54</v>
@@ -2765,13 +2755,13 @@
     </row>
     <row r="17" spans="1:29" ht="17">
       <c r="A17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17" s="2">
         <v>15.194000000000001</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D17" s="2">
         <v>5.7539999999999996</v>
@@ -2789,7 +2779,7 @@
         <v>6.7009999999999996</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J17" s="2">
         <v>72</v>
@@ -2855,13 +2845,13 @@
     </row>
     <row r="18" spans="1:29" ht="17">
       <c r="A18" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B18" s="2">
         <v>0.23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18" s="2">
         <v>5.0000000000000001E-3</v>
@@ -2879,7 +2869,7 @@
         <v>-2.1539999999999999</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J18" s="2">
         <v>54</v>
@@ -2945,13 +2935,13 @@
     </row>
     <row r="19" spans="1:29" ht="17">
       <c r="A19" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19" s="2">
         <v>2720</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D19" s="2">
         <v>60.3</v>
@@ -2969,7 +2959,7 @@
         <v>19.088000000000001</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J19" s="2">
         <v>54</v>
@@ -3035,13 +3025,13 @@
     </row>
     <row r="20" spans="1:29" ht="17">
       <c r="A20" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B20" s="2">
         <v>429</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D20" s="2">
         <v>2720</v>
@@ -3059,7 +3049,7 @@
         <v>19.111999999999998</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J20" s="2">
         <v>54</v>
@@ -3125,13 +3115,13 @@
     </row>
     <row r="21" spans="1:29" ht="17">
       <c r="A21" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21" s="2">
         <v>429</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" s="2">
         <v>60.3</v>
@@ -3149,7 +3139,7 @@
         <v>-1.4279999999999999</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J21" s="2">
         <v>54</v>
@@ -3215,13 +3205,13 @@
     </row>
     <row r="22" spans="1:29" ht="17">
       <c r="A22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" s="2">
         <v>429</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2">
         <v>38.5</v>
@@ -3239,7 +3229,7 @@
         <v>-1.712</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J22" s="2">
         <v>54</v>
@@ -3305,13 +3295,13 @@
     </row>
     <row r="23" spans="1:29" ht="17">
       <c r="A23" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2">
         <v>38.5</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="2">
         <v>60.3</v>
@@ -3329,7 +3319,7 @@
         <v>7.02</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J23" s="2">
         <v>54</v>
@@ -3395,13 +3385,13 @@
     </row>
     <row r="24" spans="1:29" ht="17">
       <c r="A24" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2">
         <v>0.72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2">
         <v>5.0000000000000001E-3</v>
@@ -3419,7 +3409,7 @@
         <v>3.681</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J24" s="2">
         <v>54</v>
@@ -3485,13 +3475,13 @@
     </row>
     <row r="25" spans="1:29" ht="17">
       <c r="A25" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="2">
         <v>0.11</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" s="2">
         <v>0.23</v>
@@ -3509,7 +3499,7 @@
         <v>26.31</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J25" s="2">
         <v>54</v>
@@ -3575,13 +3565,13 @@
     </row>
     <row r="26" spans="1:29" ht="17">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="2">
         <v>0.34100000000000003</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="2">
         <v>0.35499999999999998</v>
@@ -3599,7 +3589,7 @@
         <v>14.042</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J26" s="2">
         <v>110.86799999999999</v>
@@ -3665,13 +3655,13 @@
     </row>
     <row r="27" spans="1:29" ht="17">
       <c r="A27" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="2">
         <v>3.86</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D27" s="2">
         <v>4.2</v>
@@ -3689,7 +3679,7 @@
         <v>5.8849999999999998</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J27" s="2">
         <v>54</v>
@@ -3755,13 +3745,13 @@
     </row>
     <row r="28" spans="1:29" ht="17">
       <c r="A28" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D28" s="2">
         <v>27</v>
@@ -3779,7 +3769,7 @@
         <v>-2.15</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J28" s="2">
         <v>108</v>
@@ -3845,19 +3835,19 @@
     </row>
     <row r="29" spans="1:29" ht="17">
       <c r="A29" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B29" s="3">
         <v>47.1</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D29" s="3">
         <v>85.7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F29" s="3">
         <v>0.56999999999999995</v>
@@ -3869,7 +3859,7 @@
         <v>7.9550000000000001</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J29" s="3">
         <v>22.091000000000001</v>
@@ -3936,13 +3926,13 @@
     </row>
     <row r="30" spans="1:29" ht="17">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="2">
         <v>1.6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D30" s="2">
         <v>2.2999999999999998</v>
@@ -3960,7 +3950,7 @@
         <v>17.094000000000001</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J30" s="2">
         <v>36</v>
@@ -4026,13 +4016,13 @@
     </row>
     <row r="31" spans="1:29" ht="17">
       <c r="A31" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2">
         <v>1.86</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D31" s="2">
         <v>8.92</v>
@@ -4050,7 +4040,7 @@
         <v>5.0880000000000001</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J31" s="2">
         <v>54</v>
@@ -4116,13 +4106,13 @@
     </row>
     <row r="32" spans="1:29" ht="17">
       <c r="A32" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2">
         <v>8.92</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D32" s="2">
         <v>1.86</v>
@@ -4140,7 +4130,7 @@
         <v>5.0880000000000001</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J32" s="2">
         <v>54</v>
@@ -4206,13 +4196,13 @@
     </row>
     <row r="33" spans="1:29" ht="17">
       <c r="A33" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B33" s="2">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D33" s="2">
         <v>0.13</v>
@@ -4230,7 +4220,7 @@
         <v>56.042999999999999</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J33" s="2">
         <v>54</v>
@@ -4296,13 +4286,13 @@
     </row>
     <row r="34" spans="1:29" ht="17">
       <c r="A34" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B34" s="2">
         <v>16.7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D34" s="2">
         <v>70</v>
@@ -4320,7 +4310,7 @@
         <v>16.52</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J34" s="2">
         <v>72</v>
@@ -4386,13 +4376,13 @@
     </row>
     <row r="35" spans="1:29" ht="17">
       <c r="A35" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B35" s="2">
         <v>867.3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D35" s="2">
         <v>209.8</v>
@@ -4410,7 +4400,7 @@
         <v>-26.19</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J35" s="2">
         <v>72</v>
@@ -4476,13 +4466,13 @@
     </row>
     <row r="36" spans="1:29" ht="17">
       <c r="A36" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" s="2">
         <v>867.3</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D36" s="2">
         <v>101.7</v>
@@ -4500,7 +4490,7 @@
         <v>-27.199000000000002</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J36" s="2">
         <v>72</v>
@@ -4566,13 +4556,13 @@
     </row>
     <row r="37" spans="1:29" ht="17">
       <c r="A37" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B37" s="2">
         <v>867.3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D37" s="2">
         <v>19.100000000000001</v>
@@ -4590,7 +4580,7 @@
         <v>71.206999999999994</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J37" s="2">
         <v>72</v>
@@ -4656,13 +4646,13 @@
     </row>
     <row r="38" spans="1:29" ht="17">
       <c r="A38" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B38" s="2">
         <v>209.8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D38" s="2">
         <v>101.7</v>
@@ -4680,7 +4670,7 @@
         <v>-20.690999999999999</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J38" s="2">
         <v>72</v>
@@ -4746,13 +4736,13 @@
     </row>
     <row r="39" spans="1:29" ht="17">
       <c r="A39" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B39" s="2">
         <v>209.8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D39" s="2">
         <v>19.100000000000001</v>
@@ -4770,7 +4760,7 @@
         <v>53.537999999999997</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J39" s="2">
         <v>72</v>
@@ -4836,13 +4826,13 @@
     </row>
     <row r="40" spans="1:29" ht="17">
       <c r="A40" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B40" s="2">
         <v>37.300000000000004</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D40" s="2">
         <v>113</v>
@@ -4860,7 +4850,7 @@
         <v>7.7050000000000001</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J40" s="2">
         <v>90</v>
@@ -4926,13 +4916,13 @@
     </row>
     <row r="41" spans="1:29" ht="17">
       <c r="A41" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B41" s="2">
         <v>37.300000000000004</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D41" s="2">
         <v>48.6</v>
@@ -4950,7 +4940,7 @@
         <v>5.0250000000000004</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J41" s="2">
         <v>90</v>
@@ -5016,13 +5006,13 @@
     </row>
     <row r="42" spans="1:29" ht="17">
       <c r="A42" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B42" s="2">
         <v>37.300000000000004</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D42" s="2">
         <v>1480</v>
@@ -5040,7 +5030,7 @@
         <v>6.9109999999999996</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J42" s="2">
         <v>90</v>
@@ -5106,13 +5096,13 @@
     </row>
     <row r="43" spans="1:29" ht="17">
       <c r="A43" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="D43" s="2">
         <v>113</v>
@@ -5130,7 +5120,7 @@
         <v>15.272</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J43" s="2">
         <v>90</v>
@@ -5196,13 +5186,13 @@
     </row>
     <row r="44" spans="1:29" ht="17">
       <c r="A44" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B44" s="2">
         <v>113</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D44" s="2">
         <v>52.4</v>
@@ -5220,7 +5210,7 @@
         <v>2.2389999999999999</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J44" s="2">
         <v>90</v>
@@ -5286,13 +5276,13 @@
     </row>
     <row r="45" spans="1:29" ht="17">
       <c r="A45" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B45" s="2">
         <v>113</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D45" s="2">
         <v>462</v>
@@ -5310,7 +5300,7 @@
         <v>4.0490000000000004</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J45" s="2">
         <v>90</v>
@@ -5376,13 +5366,13 @@
     </row>
     <row r="46" spans="1:29" ht="17">
       <c r="A46" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B46" s="2">
         <v>113</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D46" s="2">
         <v>114</v>
@@ -5400,7 +5390,7 @@
         <v>11.583</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J46" s="2">
         <v>90</v>
@@ -5466,13 +5456,13 @@
     </row>
     <row r="47" spans="1:29" ht="17">
       <c r="A47" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B47" s="4">
         <v>113</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D47" s="4">
         <v>78.5</v>
@@ -5490,7 +5480,7 @@
         <v>21.332000000000001</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J47" s="2">
         <v>90</v>
@@ -5556,13 +5546,13 @@
     </row>
     <row r="48" spans="1:29" ht="17">
       <c r="A48" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B48" s="2">
         <v>113</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D48" s="2">
         <v>1480</v>
@@ -5580,7 +5570,7 @@
         <v>7.1079999999999997</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J48" s="2">
         <v>90</v>
@@ -5646,13 +5636,13 @@
     </row>
     <row r="49" spans="1:29" ht="17">
       <c r="A49" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B49" s="2">
         <v>113</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D49" s="2">
         <v>3000</v>
@@ -5670,7 +5660,7 @@
         <v>6.3029999999999999</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J49" s="2">
         <v>90</v>
@@ -5736,13 +5726,13 @@
     </row>
     <row r="50" spans="1:29" ht="17">
       <c r="A50" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B50" s="2">
         <v>52.4</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D50" s="2">
         <v>35.1</v>
@@ -5760,7 +5750,7 @@
         <v>13.598000000000001</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J50" s="2">
         <v>90</v>
@@ -5826,13 +5816,13 @@
     </row>
     <row r="51" spans="1:29" ht="17">
       <c r="A51" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B51" s="2">
         <v>462</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D51" s="2">
         <v>35.1</v>
@@ -5850,7 +5840,7 @@
         <v>-28.074000000000002</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J51" s="2">
         <v>90</v>
@@ -5916,13 +5906,13 @@
     </row>
     <row r="52" spans="1:29" ht="17">
       <c r="A52" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B52" s="2">
         <v>462</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D52" s="2">
         <v>1180</v>
@@ -5940,7 +5930,7 @@
         <v>-5.2720000000000002</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J52" s="2">
         <v>90</v>
@@ -6000,19 +5990,19 @@
         <v>1</v>
       </c>
       <c r="AC52" s="11">
-        <f t="shared" ref="AC52:AC102" si="2">(1-MIN(ABS(L52-1),1))+(1-MIN(ABS(S52-1),0.5))+(1-MIN(ABS(AB52-1),0.5))</f>
+        <f t="shared" ref="AC52:AC100" si="2">(1-MIN(ABS(L52-1),1))+(1-MIN(ABS(S52-1),0.5))+(1-MIN(ABS(AB52-1),0.5))</f>
         <v>2.3955945992898862</v>
       </c>
     </row>
     <row r="53" spans="1:29" ht="17">
       <c r="A53" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B53" s="2">
         <v>462</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D53" s="2">
         <v>3000</v>
@@ -6030,7 +6020,7 @@
         <v>13.241</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J53" s="2">
         <v>90</v>
@@ -6096,13 +6086,13 @@
     </row>
     <row r="54" spans="1:29" ht="17">
       <c r="A54" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B54" s="2">
         <v>35.1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D54" s="2">
         <v>113</v>
@@ -6120,7 +6110,7 @@
         <v>8.77</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J54" s="2">
         <v>90</v>
@@ -6186,13 +6176,13 @@
     </row>
     <row r="55" spans="1:29" ht="17">
       <c r="A55" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B55" s="2">
         <v>35.1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D55" s="2">
         <v>114</v>
@@ -6210,7 +6200,7 @@
         <v>-2.9529999999999998</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J55" s="2">
         <v>90</v>
@@ -6276,13 +6266,13 @@
     </row>
     <row r="56" spans="1:29" ht="17">
       <c r="A56" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B56" s="2">
         <v>35.1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D56" s="2">
         <v>48.6</v>
@@ -6300,7 +6290,7 @@
         <v>-2.1920000000000002</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J56" s="2">
         <v>90</v>
@@ -6366,13 +6356,13 @@
     </row>
     <row r="57" spans="1:29" ht="17">
       <c r="A57" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B57" s="5">
         <v>114</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D57" s="5">
         <v>52.4</v>
@@ -6390,7 +6380,7 @@
         <v>9.0120000000000005</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J57" s="2">
         <v>90</v>
@@ -6456,13 +6446,13 @@
     </row>
     <row r="58" spans="1:29" ht="17">
       <c r="A58" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B58" s="2">
         <v>114</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D58" s="2">
         <v>106</v>
@@ -6480,7 +6470,7 @@
         <v>11.065</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J58" s="2">
         <v>90</v>
@@ -6546,13 +6536,13 @@
     </row>
     <row r="59" spans="1:29" ht="17">
       <c r="A59" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B59" s="2">
         <v>114</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D59" s="2">
         <v>1180</v>
@@ -6570,7 +6560,7 @@
         <v>-3.0539999999999998</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J59" s="2">
         <v>90</v>
@@ -6636,13 +6626,13 @@
     </row>
     <row r="60" spans="1:29" ht="17">
       <c r="A60" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B60" s="2">
         <v>114</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D60" s="2">
         <v>3000</v>
@@ -6660,7 +6650,7 @@
         <v>12.696</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J60" s="2">
         <v>90</v>
@@ -6726,13 +6716,13 @@
     </row>
     <row r="61" spans="1:29" ht="17">
       <c r="A61" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B61" s="2">
         <v>48.6</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D61" s="2">
         <v>1180</v>
@@ -6750,7 +6740,7 @@
         <v>20.206</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J61" s="2">
         <v>90</v>
@@ -6816,13 +6806,13 @@
     </row>
     <row r="62" spans="1:29" ht="17">
       <c r="A62" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B62" s="2">
         <v>48.6</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D62" s="2">
         <v>3000</v>
@@ -6840,7 +6830,7 @@
         <v>-2.3959999999999999</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J62" s="2">
         <v>90</v>
@@ -6906,220 +6896,220 @@
     </row>
     <row r="63" spans="1:29" ht="17">
       <c r="A63" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1180</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D63" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>59</v>
       </c>
       <c r="F63" s="2">
-        <v>1.22</v>
+        <v>123</v>
       </c>
       <c r="G63" s="2">
-        <v>93.442622950819668</v>
+        <v>0.91869918699186992</v>
       </c>
       <c r="H63" s="2">
-        <v>6.99</v>
+        <v>18.169</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J63" s="2">
         <v>90</v>
       </c>
       <c r="K63" s="3">
-        <v>42.616</v>
+        <v>47.44</v>
       </c>
       <c r="L63" s="2">
-        <v>2.1118828608973157</v>
+        <v>1.897133220910624</v>
       </c>
       <c r="M63" s="2">
-        <v>348.74787699999996</v>
+        <v>307.27678800000001</v>
       </c>
       <c r="N63" s="2">
-        <v>162.614959</v>
+        <v>171.27784100000002</v>
       </c>
       <c r="O63" s="2">
-        <v>186.13324399999999</v>
+        <v>135.99903099999997</v>
       </c>
       <c r="P63" s="2">
-        <v>321.49026300000003</v>
+        <v>326.98653399999995</v>
       </c>
       <c r="Q63" s="2">
-        <v>171.64188399999998</v>
+        <v>186.83260499999997</v>
       </c>
       <c r="R63" s="2">
-        <v>149.84830299999999</v>
+        <v>140.15379000000001</v>
       </c>
       <c r="S63" s="2">
-        <v>1.0847851930122061</v>
+        <v>0.93972306517062887</v>
       </c>
       <c r="T63" s="2">
         <v>7</v>
       </c>
       <c r="U63" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V63" s="2">
         <v>0</v>
       </c>
       <c r="W63" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="X63" s="2">
         <v>4</v>
       </c>
       <c r="Y63" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z63" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA63" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AB63" s="2">
-        <v>0.90909090909090906</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="AC63" s="11">
         <f t="shared" si="2"/>
-        <v>1.8243057160787028</v>
+        <v>1.542589844260005</v>
       </c>
     </row>
     <row r="64" spans="1:29" ht="17">
-      <c r="A64" s="4" t="s">
-        <v>143</v>
+      <c r="A64" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="B64" s="2">
-        <v>1180</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="D64" s="2">
-        <v>113</v>
+        <v>99.5</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F64" s="2">
-        <v>123</v>
+        <v>2.91</v>
       </c>
       <c r="G64" s="2">
-        <v>0.91869918699186992</v>
+        <v>34.192439862542955</v>
       </c>
       <c r="H64" s="2">
-        <v>18.169</v>
+        <v>6.0439999999999996</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J64" s="2">
         <v>90</v>
       </c>
       <c r="K64" s="3">
-        <v>47.44</v>
+        <v>46.444000000000003</v>
       </c>
       <c r="L64" s="2">
-        <v>1.897133220910624</v>
+        <v>1.9378175867711651</v>
       </c>
       <c r="M64" s="2">
-        <v>307.27678800000001</v>
+        <v>401.78200400000003</v>
       </c>
       <c r="N64" s="2">
-        <v>171.27784100000002</v>
+        <v>220.08053999999998</v>
       </c>
       <c r="O64" s="2">
-        <v>135.99903099999997</v>
+        <v>181.70129399999999</v>
       </c>
       <c r="P64" s="2">
-        <v>326.98653399999995</v>
+        <v>355.54163900000003</v>
       </c>
       <c r="Q64" s="2">
-        <v>186.83260499999997</v>
+        <v>93.098927000000018</v>
       </c>
       <c r="R64" s="2">
-        <v>140.15379000000001</v>
+        <v>262.44285100000008</v>
       </c>
       <c r="S64" s="2">
-        <v>0.93972306517062887</v>
+        <v>1.130056116999562</v>
       </c>
       <c r="T64" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U64" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V64" s="2">
         <v>0</v>
       </c>
       <c r="W64" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X64" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y64" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA64" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AB64" s="2">
-        <v>1.8571428571428572</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="AC64" s="11">
         <f t="shared" si="2"/>
-        <v>1.542589844260005</v>
+        <v>1.7556557079939787</v>
       </c>
     </row>
     <row r="65" spans="1:29" ht="17">
       <c r="A65" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B65" s="2">
         <v>138</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D65" s="2">
-        <v>99.5</v>
+        <v>212</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F65" s="2">
-        <v>2.91</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="G65" s="2">
-        <v>34.192439862542955</v>
+        <v>174.24242424242422</v>
       </c>
       <c r="H65" s="2">
-        <v>6.0439999999999996</v>
+        <v>-3.5390000000000001</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J65" s="2">
         <v>90</v>
       </c>
       <c r="K65" s="3">
-        <v>46.444000000000003</v>
+        <v>55.52</v>
       </c>
       <c r="L65" s="2">
-        <v>1.9378175867711651</v>
+        <v>1.6210374639769451</v>
       </c>
       <c r="M65" s="2">
         <v>401.78200400000003</v>
@@ -7131,16 +7121,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P65" s="2">
-        <v>355.54163900000003</v>
+        <v>365.21654600000005</v>
       </c>
       <c r="Q65" s="2">
-        <v>93.098927000000018</v>
+        <v>128.86028300000001</v>
       </c>
       <c r="R65" s="2">
-        <v>262.44285100000008</v>
+        <v>236.35607899999999</v>
       </c>
       <c r="S65" s="2">
-        <v>1.130056116999562</v>
+        <v>1.100119938158552</v>
       </c>
       <c r="T65" s="2">
         <v>12</v>
@@ -7158,58 +7148,58 @@
         <v>5</v>
       </c>
       <c r="Y65" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z65" s="2">
         <v>0</v>
       </c>
       <c r="AA65" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AB65" s="2">
-        <v>0.82352941176470584</v>
+        <v>0.70588235294117652</v>
       </c>
       <c r="AC65" s="11">
         <f t="shared" si="2"/>
-        <v>1.7556557079939787</v>
+        <v>1.9847249508056795</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="17">
       <c r="A66" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B66" s="2">
         <v>138</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D66" s="2">
-        <v>212</v>
+        <v>26.9</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>62</v>
       </c>
       <c r="F66" s="2">
-        <v>0.79200000000000004</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="G66" s="2">
-        <v>174.24242424242422</v>
+        <v>37.257617728531855</v>
       </c>
       <c r="H66" s="2">
-        <v>-3.5390000000000001</v>
+        <v>5.7229999999999999</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J66" s="2">
         <v>90</v>
       </c>
       <c r="K66" s="3">
-        <v>55.52</v>
+        <v>46.881</v>
       </c>
       <c r="L66" s="2">
-        <v>1.6210374639769451</v>
+        <v>1.9197542714532541</v>
       </c>
       <c r="M66" s="2">
         <v>401.78200400000003</v>
@@ -7221,16 +7211,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P66" s="2">
-        <v>365.21654600000005</v>
+        <v>361.04667599999999</v>
       </c>
       <c r="Q66" s="2">
-        <v>128.86028300000001</v>
+        <v>122.77821399999999</v>
       </c>
       <c r="R66" s="2">
-        <v>236.35607899999999</v>
+        <v>238.26829699999999</v>
       </c>
       <c r="S66" s="2">
-        <v>1.100119938158552</v>
+        <v>1.1128256558163134</v>
       </c>
       <c r="T66" s="2">
         <v>12</v>
@@ -7245,10 +7235,10 @@
         <v>17</v>
       </c>
       <c r="X66" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y66" s="2">
         <v>5</v>
-      </c>
-      <c r="Y66" s="2">
-        <v>7</v>
       </c>
       <c r="Z66" s="2">
         <v>0</v>
@@ -7261,45 +7251,45 @@
       </c>
       <c r="AC66" s="11">
         <f t="shared" si="2"/>
-        <v>1.9847249508056795</v>
+        <v>1.6733024256716091</v>
       </c>
     </row>
     <row r="67" spans="1:29" ht="17">
       <c r="A67" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B67" s="2">
         <v>138</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D67" s="2">
-        <v>26.9</v>
+        <v>69.300000000000011</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>63</v>
       </c>
       <c r="F67" s="2">
-        <v>0.72199999999999998</v>
+        <v>100</v>
       </c>
       <c r="G67" s="2">
-        <v>37.257617728531855</v>
+        <v>0.69300000000000006</v>
       </c>
       <c r="H67" s="2">
-        <v>5.7229999999999999</v>
+        <v>3.3159999999999998</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J67" s="2">
         <v>90</v>
       </c>
       <c r="K67" s="3">
-        <v>46.881</v>
+        <v>57.631</v>
       </c>
       <c r="L67" s="2">
-        <v>1.9197542714532541</v>
+        <v>1.5616595235203277</v>
       </c>
       <c r="M67" s="2">
         <v>401.78200400000003</v>
@@ -7311,16 +7301,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P67" s="2">
-        <v>361.04667599999999</v>
+        <v>451.19195999999999</v>
       </c>
       <c r="Q67" s="2">
-        <v>122.77821399999999</v>
+        <v>138.02437800000001</v>
       </c>
       <c r="R67" s="2">
-        <v>238.26829699999999</v>
+        <v>313.16749299999992</v>
       </c>
       <c r="S67" s="2">
-        <v>1.1128256558163134</v>
+        <v>0.89049016742230969</v>
       </c>
       <c r="T67" s="2">
         <v>12</v>
@@ -7351,45 +7341,45 @@
       </c>
       <c r="AC67" s="11">
         <f t="shared" si="2"/>
-        <v>1.6733024256716091</v>
+        <v>2.0347129968431585</v>
       </c>
     </row>
     <row r="68" spans="1:29" ht="17">
       <c r="A68" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B68" s="2">
         <v>138</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D68" s="2">
-        <v>69.300000000000011</v>
+        <v>413</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>64</v>
       </c>
       <c r="F68" s="2">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="G68" s="2">
-        <v>0.69300000000000006</v>
+        <v>0.83636363636363631</v>
       </c>
       <c r="H68" s="2">
-        <v>3.3159999999999998</v>
+        <v>7.0330000000000004</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J68" s="2">
         <v>90</v>
       </c>
       <c r="K68" s="3">
-        <v>57.631</v>
+        <v>47.951000000000001</v>
       </c>
       <c r="L68" s="2">
-        <v>1.5616595235203277</v>
+        <v>1.8769160184354863</v>
       </c>
       <c r="M68" s="2">
         <v>401.78200400000003</v>
@@ -7401,16 +7391,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P68" s="2">
-        <v>451.19195999999999</v>
+        <v>460.04647499999993</v>
       </c>
       <c r="Q68" s="2">
-        <v>138.02437800000001</v>
+        <v>113.94948100000002</v>
       </c>
       <c r="R68" s="2">
-        <v>313.16749299999992</v>
+        <v>346.09716400000002</v>
       </c>
       <c r="S68" s="2">
-        <v>0.89049016742230969</v>
+        <v>0.87335090221047795</v>
       </c>
       <c r="T68" s="2">
         <v>12</v>
@@ -7425,61 +7415,61 @@
         <v>17</v>
       </c>
       <c r="X68" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y68" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z68" s="2">
         <v>0</v>
       </c>
       <c r="AA68" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB68" s="2">
-        <v>0.70588235294117652</v>
+        <v>1</v>
       </c>
       <c r="AC68" s="11">
         <f t="shared" si="2"/>
-        <v>2.0347129968431585</v>
+        <v>1.9964348837749917</v>
       </c>
     </row>
     <row r="69" spans="1:29" ht="17">
       <c r="A69" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B69" s="2">
         <v>138</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D69" s="2">
-        <v>413</v>
+        <v>1470</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F69" s="2">
-        <v>165</v>
+        <v>52.7</v>
       </c>
       <c r="G69" s="2">
-        <v>0.83636363636363631</v>
+        <v>2.618595825426945</v>
       </c>
       <c r="H69" s="2">
-        <v>7.0330000000000004</v>
+        <v>10.057</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J69" s="2">
         <v>90</v>
       </c>
       <c r="K69" s="3">
-        <v>47.951000000000001</v>
+        <v>37.786000000000001</v>
       </c>
       <c r="L69" s="2">
-        <v>1.8769160184354863</v>
+        <v>2.3818345418938232</v>
       </c>
       <c r="M69" s="2">
         <v>401.78200400000003</v>
@@ -7491,16 +7481,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P69" s="2">
-        <v>460.04647499999993</v>
+        <v>479.61241899999999</v>
       </c>
       <c r="Q69" s="2">
-        <v>113.94948100000002</v>
+        <v>138.09142900000001</v>
       </c>
       <c r="R69" s="2">
-        <v>346.09716400000002</v>
+        <v>341.52099600000003</v>
       </c>
       <c r="S69" s="2">
-        <v>0.87335090221047795</v>
+        <v>0.83772226923923765</v>
       </c>
       <c r="T69" s="2">
         <v>12</v>
@@ -7515,34 +7505,34 @@
         <v>17</v>
       </c>
       <c r="X69" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y69" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z69" s="2">
         <v>0</v>
       </c>
       <c r="AA69" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AB69" s="2">
-        <v>1</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AC69" s="11">
         <f t="shared" si="2"/>
-        <v>1.9964348837749917</v>
+        <v>1.4847810927686496</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="17">
       <c r="A70" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B70" s="2">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D70" s="2">
         <v>1470</v>
@@ -7551,34 +7541,34 @@
         <v>66</v>
       </c>
       <c r="F70" s="2">
-        <v>52.7</v>
+        <v>7.13</v>
       </c>
       <c r="G70" s="2">
-        <v>2.618595825426945</v>
+        <v>30.855539971949508</v>
       </c>
       <c r="H70" s="2">
-        <v>10.057</v>
+        <v>31.024000000000001</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J70" s="2">
         <v>90</v>
       </c>
       <c r="K70" s="3">
-        <v>37.786000000000001</v>
+        <v>55.347999999999999</v>
       </c>
       <c r="L70" s="2">
-        <v>2.3818345418938232</v>
+        <v>1.6260750162607502</v>
       </c>
       <c r="M70" s="2">
-        <v>401.78200400000003</v>
+        <v>489.53467200000006</v>
       </c>
       <c r="N70" s="2">
-        <v>220.08053999999998</v>
+        <v>159.10767099999998</v>
       </c>
       <c r="O70" s="2">
-        <v>181.70129399999999</v>
+        <v>330.42694800000004</v>
       </c>
       <c r="P70" s="2">
         <v>479.61241899999999</v>
@@ -7590,19 +7580,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S70" s="2">
-        <v>0.83772226923923765</v>
+        <v>1.0206880652104215</v>
       </c>
       <c r="T70" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U70" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V70" s="2">
         <v>0</v>
       </c>
       <c r="W70" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X70" s="2">
         <v>8</v>
@@ -7617,22 +7607,22 @@
         <v>11</v>
       </c>
       <c r="AB70" s="2">
-        <v>0.6470588235294118</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AC70" s="11">
         <f t="shared" si="2"/>
-        <v>1.4847810927686496</v>
+        <v>2.138951204243114</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="17">
       <c r="A71" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B71" s="2">
-        <v>220</v>
+        <v>702</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D71" s="2">
         <v>1470</v>
@@ -7641,34 +7631,34 @@
         <v>67</v>
       </c>
       <c r="F71" s="2">
-        <v>7.13</v>
+        <v>546</v>
       </c>
       <c r="G71" s="2">
-        <v>30.855539971949508</v>
+        <v>1.2857142857142858</v>
       </c>
       <c r="H71" s="2">
-        <v>31.024000000000001</v>
+        <v>25.725000000000001</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J71" s="2">
         <v>90</v>
       </c>
       <c r="K71" s="3">
-        <v>55.347999999999999</v>
+        <v>46.280999999999999</v>
       </c>
       <c r="L71" s="2">
-        <v>1.6260750162607502</v>
+        <v>1.9446425098852662</v>
       </c>
       <c r="M71" s="2">
-        <v>489.53467200000006</v>
+        <v>489.48157500000002</v>
       </c>
       <c r="N71" s="2">
-        <v>159.10767099999998</v>
+        <v>125.21337999999999</v>
       </c>
       <c r="O71" s="2">
-        <v>330.42694800000004</v>
+        <v>364.26828999999998</v>
       </c>
       <c r="P71" s="2">
         <v>479.61241899999999</v>
@@ -7680,19 +7670,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S71" s="2">
-        <v>1.0206880652104215</v>
+        <v>1.0205773570679788</v>
       </c>
       <c r="T71" s="2">
         <v>7</v>
       </c>
       <c r="U71" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X71" s="2">
         <v>8</v>
@@ -7707,22 +7697,22 @@
         <v>11</v>
       </c>
       <c r="AB71" s="2">
-        <v>0.7857142857142857</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="AC71" s="11">
         <f t="shared" si="2"/>
-        <v>2.138951204243114</v>
+        <v>1.8809339792006012</v>
       </c>
     </row>
     <row r="72" spans="1:29" ht="17">
       <c r="A72" s="2" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B72" s="2">
-        <v>702</v>
+        <v>99.5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D72" s="2">
         <v>1470</v>
@@ -7731,34 +7721,34 @@
         <v>68</v>
       </c>
       <c r="F72" s="2">
-        <v>546</v>
+        <v>688</v>
       </c>
       <c r="G72" s="2">
-        <v>1.2857142857142858</v>
+        <v>0.14462209302325582</v>
       </c>
       <c r="H72" s="2">
-        <v>25.725000000000001</v>
+        <v>27.274000000000001</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J72" s="2">
         <v>90</v>
       </c>
       <c r="K72" s="3">
-        <v>46.280999999999999</v>
+        <v>64.635000000000005</v>
       </c>
       <c r="L72" s="2">
-        <v>1.9446425098852662</v>
+        <v>1.392434439545138</v>
       </c>
       <c r="M72" s="2">
-        <v>489.48157500000002</v>
+        <v>355.54163900000003</v>
       </c>
       <c r="N72" s="2">
-        <v>125.21337999999999</v>
+        <v>93.098927000000018</v>
       </c>
       <c r="O72" s="2">
-        <v>364.26828999999998</v>
+        <v>262.44285100000008</v>
       </c>
       <c r="P72" s="2">
         <v>479.61241899999999</v>
@@ -7770,19 +7760,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S72" s="2">
-        <v>1.0205773570679788</v>
+        <v>0.74131032666191243</v>
       </c>
       <c r="T72" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U72" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X72" s="2">
         <v>8</v>
@@ -7797,11 +7787,11 @@
         <v>11</v>
       </c>
       <c r="AB72" s="2">
-        <v>0.84615384615384615</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AC72" s="11">
         <f t="shared" si="2"/>
-        <v>1.8809339792006012</v>
+        <v>2.1345901728310599</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="17">
@@ -7809,10 +7799,10 @@
         <v>148</v>
       </c>
       <c r="B73" s="2">
-        <v>99.5</v>
+        <v>26.9</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D73" s="2">
         <v>1470</v>
@@ -7821,34 +7811,34 @@
         <v>69</v>
       </c>
       <c r="F73" s="2">
-        <v>688</v>
+        <v>115</v>
       </c>
       <c r="G73" s="2">
-        <v>0.14462209302325582</v>
+        <v>0.23391304347826086</v>
       </c>
       <c r="H73" s="2">
-        <v>27.274000000000001</v>
+        <v>25.725000000000001</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J73" s="2">
         <v>90</v>
       </c>
       <c r="K73" s="3">
-        <v>64.635000000000005</v>
+        <v>55.18</v>
       </c>
       <c r="L73" s="2">
-        <v>1.392434439545138</v>
+        <v>1.6310257339615803</v>
       </c>
       <c r="M73" s="2">
-        <v>355.54163900000003</v>
+        <v>361.04667599999999</v>
       </c>
       <c r="N73" s="2">
-        <v>93.098927000000018</v>
+        <v>122.77821399999999</v>
       </c>
       <c r="O73" s="2">
-        <v>262.44285100000008</v>
+        <v>238.26829699999999</v>
       </c>
       <c r="P73" s="2">
         <v>479.61241899999999</v>
@@ -7860,19 +7850,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S73" s="2">
-        <v>0.74131032666191243</v>
+        <v>0.75278842185277106</v>
       </c>
       <c r="T73" s="2">
+        <v>7</v>
+      </c>
+      <c r="U73" s="2">
         <v>5</v>
       </c>
-      <c r="U73" s="2">
-        <v>9</v>
-      </c>
       <c r="V73" s="2">
         <v>0</v>
       </c>
       <c r="W73" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X73" s="2">
         <v>8</v>
@@ -7887,22 +7877,22 @@
         <v>11</v>
       </c>
       <c r="AB73" s="2">
-        <v>0.7857142857142857</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="AC73" s="11">
         <f t="shared" si="2"/>
-        <v>2.1345901728310599</v>
+        <v>2.0384293545578571</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="17">
       <c r="A74" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B74" s="2">
-        <v>26.9</v>
+        <v>69.300000000000011</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D74" s="2">
         <v>1470</v>
@@ -7911,34 +7901,34 @@
         <v>70</v>
       </c>
       <c r="F74" s="2">
-        <v>115</v>
+        <v>7.19</v>
       </c>
       <c r="G74" s="2">
-        <v>0.23391304347826086</v>
+        <v>9.6383866481223937</v>
       </c>
       <c r="H74" s="2">
-        <v>25.725000000000001</v>
+        <v>20.786999999999999</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J74" s="2">
         <v>90</v>
       </c>
       <c r="K74" s="3">
-        <v>55.18</v>
+        <v>67.56</v>
       </c>
       <c r="L74" s="2">
-        <v>1.6310257339615803</v>
+        <v>1.3321492007104796</v>
       </c>
       <c r="M74" s="2">
-        <v>361.04667599999999</v>
+        <v>451.19195999999999</v>
       </c>
       <c r="N74" s="2">
-        <v>122.77821399999999</v>
+        <v>138.02437800000001</v>
       </c>
       <c r="O74" s="2">
-        <v>238.26829699999999</v>
+        <v>313.16749299999992</v>
       </c>
       <c r="P74" s="2">
         <v>479.61241899999999</v>
@@ -7950,7 +7940,7 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S74" s="2">
-        <v>0.75278842185277106</v>
+        <v>0.94074286262383044</v>
       </c>
       <c r="T74" s="2">
         <v>7</v>
@@ -7981,7 +7971,7 @@
       </c>
       <c r="AC74" s="11">
         <f t="shared" si="2"/>
-        <v>2.0384293545578571</v>
+        <v>2.5252603285800173</v>
       </c>
     </row>
     <row r="75" spans="1:29" ht="17">
@@ -7989,10 +7979,10 @@
         <v>151</v>
       </c>
       <c r="B75" s="2">
-        <v>69.300000000000011</v>
+        <v>698</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D75" s="2">
         <v>1470</v>
@@ -8001,34 +7991,34 @@
         <v>71</v>
       </c>
       <c r="F75" s="2">
-        <v>7.19</v>
+        <v>198</v>
       </c>
       <c r="G75" s="2">
-        <v>9.6383866481223937</v>
+        <v>3.5252525252525251</v>
       </c>
       <c r="H75" s="2">
-        <v>20.786999999999999</v>
+        <v>23.596</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J75" s="2">
         <v>90</v>
       </c>
       <c r="K75" s="3">
-        <v>67.56</v>
+        <v>44.731999999999999</v>
       </c>
       <c r="L75" s="2">
-        <v>1.3321492007104796</v>
+        <v>2.0119824733971208</v>
       </c>
       <c r="M75" s="2">
-        <v>451.19195999999999</v>
+        <v>528.88547800000015</v>
       </c>
       <c r="N75" s="2">
-        <v>138.02437800000001</v>
+        <v>156.73678100000001</v>
       </c>
       <c r="O75" s="2">
-        <v>313.16749299999992</v>
+        <v>372.14883200000003</v>
       </c>
       <c r="P75" s="2">
         <v>479.61241899999999</v>
@@ -8040,19 +8030,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S75" s="2">
-        <v>0.94074286262383044</v>
+        <v>1.1027351608257669</v>
       </c>
       <c r="T75" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U75" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V75" s="2">
         <v>0</v>
       </c>
       <c r="W75" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X75" s="2">
         <v>8</v>
@@ -8067,229 +8057,229 @@
         <v>11</v>
       </c>
       <c r="AB75" s="2">
-        <v>0.91666666666666663</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AC75" s="11">
         <f t="shared" si="2"/>
-        <v>2.5252603285800173</v>
+        <v>1.5443236627036447</v>
       </c>
     </row>
     <row r="76" spans="1:29" ht="17">
-      <c r="A76" s="2" t="s">
-        <v>153</v>
+      <c r="A76" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="B76" s="2">
-        <v>698</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>147</v>
+        <v>113</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="D76" s="2">
-        <v>1470</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>72</v>
+        <v>3000</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="F76" s="2">
-        <v>198</v>
+        <v>59.1</v>
       </c>
       <c r="G76" s="2">
-        <v>3.5252525252525251</v>
-      </c>
-      <c r="H76" s="2">
-        <v>23.596</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J76" s="2">
-        <v>90</v>
+        <v>1.91</v>
+      </c>
+      <c r="H76" s="3">
+        <v>6.3029999999999999</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J76" s="3">
+        <v>48.423999999999999</v>
       </c>
       <c r="K76" s="3">
-        <v>44.731999999999999</v>
-      </c>
-      <c r="L76" s="2">
-        <v>2.0119824733971208</v>
+        <v>48.039000000000001</v>
+      </c>
+      <c r="L76" s="6">
+        <v>1.008014322</v>
       </c>
       <c r="M76" s="2">
-        <v>528.88547800000015</v>
+        <v>326.98653399999995</v>
       </c>
       <c r="N76" s="2">
-        <v>156.73678100000001</v>
+        <v>186.83260499999997</v>
       </c>
       <c r="O76" s="2">
-        <v>372.14883200000003</v>
+        <v>140.15379000000001</v>
       </c>
       <c r="P76" s="2">
-        <v>479.61241899999999</v>
+        <v>258.476448</v>
       </c>
       <c r="Q76" s="2">
-        <v>138.09142900000001</v>
+        <v>157.37730500000006</v>
       </c>
       <c r="R76" s="2">
-        <v>341.52099600000003</v>
+        <v>101.099051</v>
       </c>
       <c r="S76" s="2">
-        <v>1.1027351608257669</v>
+        <v>1.2650534953188459</v>
       </c>
       <c r="T76" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U76" s="2">
+        <v>2</v>
+      </c>
+      <c r="V76" s="2">
+        <v>1</v>
+      </c>
+      <c r="W76" s="2">
+        <v>7</v>
+      </c>
+      <c r="X76" s="2">
+        <v>4</v>
+      </c>
+      <c r="Y76" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z76" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA76" s="2">
         <v>9</v>
       </c>
-      <c r="V76" s="2">
-        <v>0</v>
-      </c>
-      <c r="W76" s="2">
-        <v>17</v>
-      </c>
-      <c r="X76" s="2">
-        <v>8</v>
-      </c>
-      <c r="Y76" s="2">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="2">
-        <v>11</v>
-      </c>
       <c r="AB76" s="2">
-        <v>0.6470588235294118</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="AC76" s="11">
         <f t="shared" si="2"/>
-        <v>1.5443236627036447</v>
+        <v>2.504709960458932</v>
       </c>
     </row>
     <row r="77" spans="1:29" ht="17">
       <c r="A77" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B77" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>141</v>
       </c>
       <c r="D77" s="2">
-        <v>3000</v>
+        <v>1180</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F77" s="2">
-        <v>59.1</v>
+        <v>9.9500000000000005E-2</v>
       </c>
       <c r="G77" s="2">
-        <v>1.91</v>
+        <v>1145.73</v>
       </c>
       <c r="H77" s="3">
-        <v>6.3029999999999999</v>
+        <v>-3.0539999999999998</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J77" s="3">
-        <v>48.423999999999999</v>
+        <v>44.796999999999997</v>
       </c>
       <c r="K77" s="3">
-        <v>48.039000000000001</v>
+        <v>39.755000000000003</v>
       </c>
       <c r="L77" s="6">
-        <v>1.008014322</v>
+        <v>1.126826814</v>
       </c>
       <c r="M77" s="2">
-        <v>326.98653399999995</v>
+        <v>321.49026300000003</v>
       </c>
       <c r="N77" s="2">
-        <v>186.83260499999997</v>
+        <v>171.64188399999998</v>
       </c>
       <c r="O77" s="2">
-        <v>140.15379000000001</v>
+        <v>149.84830299999999</v>
       </c>
       <c r="P77" s="2">
-        <v>258.476448</v>
+        <v>307.27678800000001</v>
       </c>
       <c r="Q77" s="2">
-        <v>157.37730500000006</v>
+        <v>171.27784100000002</v>
       </c>
       <c r="R77" s="2">
-        <v>101.099051</v>
+        <v>135.99903099999997</v>
       </c>
       <c r="S77" s="2">
-        <v>1.2650534953188459</v>
+        <v>1.0462562600075083</v>
       </c>
       <c r="T77" s="2">
         <v>4</v>
       </c>
       <c r="U77" s="2">
+        <v>5</v>
+      </c>
+      <c r="V77" s="2">
         <v>2</v>
       </c>
-      <c r="V77" s="2">
-        <v>1</v>
-      </c>
       <c r="W77" s="2">
+        <v>11</v>
+      </c>
+      <c r="X77" s="2">
         <v>7</v>
       </c>
-      <c r="X77" s="2">
-        <v>4</v>
-      </c>
       <c r="Y77" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA77" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB77" s="2">
-        <v>0.77777777777777779</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="AC77" s="11">
         <f t="shared" si="2"/>
-        <v>2.504709960458932</v>
+        <v>2.673070772146338</v>
       </c>
     </row>
     <row r="78" spans="1:29" ht="17">
       <c r="A78" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B78" s="2">
         <v>114</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D78" s="2">
-        <v>1180</v>
+        <v>3000</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F78" s="2">
-        <v>9.9500000000000005E-2</v>
+        <v>7.7799999999999994E-2</v>
       </c>
       <c r="G78" s="2">
-        <v>1145.73</v>
+        <v>1465.3</v>
       </c>
       <c r="H78" s="3">
-        <v>-3.0539999999999998</v>
+        <v>12.696</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J78" s="3">
-        <v>44.796999999999997</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="K78" s="3">
-        <v>39.755000000000003</v>
+        <v>45.518999999999998</v>
       </c>
       <c r="L78" s="6">
-        <v>1.126826814</v>
+        <v>1.4246798039999999</v>
       </c>
       <c r="M78" s="2">
         <v>321.49026300000003</v>
@@ -8301,16 +8291,16 @@
         <v>149.84830299999999</v>
       </c>
       <c r="P78" s="2">
-        <v>307.27678800000001</v>
+        <v>258.476448</v>
       </c>
       <c r="Q78" s="2">
-        <v>171.27784100000002</v>
+        <v>157.37730500000006</v>
       </c>
       <c r="R78" s="2">
-        <v>135.99903099999997</v>
+        <v>101.099051</v>
       </c>
       <c r="S78" s="2">
-        <v>1.0462562600075083</v>
+        <v>1.2437893877278909</v>
       </c>
       <c r="T78" s="2">
         <v>4</v>
@@ -8325,1238 +8315,1238 @@
         <v>11</v>
       </c>
       <c r="X78" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y78" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA78" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AB78" s="2">
-        <v>0.84615384615384615</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="AC78" s="11">
         <f t="shared" si="2"/>
-        <v>2.673070772146338</v>
+        <v>2.1093085860498868</v>
       </c>
     </row>
     <row r="79" spans="1:29" ht="17">
-      <c r="A79" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B79" s="2">
-        <v>114</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" s="2">
-        <v>3000</v>
+      <c r="A79" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B79" s="3">
+        <v>867.3</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D79" s="3">
+        <v>101.7</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F79" s="2">
-        <v>7.7799999999999994E-2</v>
-      </c>
-      <c r="G79" s="2">
-        <v>1465.3</v>
-      </c>
-      <c r="H79" s="3">
-        <v>12.696</v>
+        <v>4.09</v>
+      </c>
+      <c r="G79" s="7">
+        <v>24.865525672371639</v>
+      </c>
+      <c r="H79" s="2">
+        <v>-27.199000000000002</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="J79" s="3">
-        <v>64.849999999999994</v>
+        <v>41.493000000000002</v>
       </c>
       <c r="K79" s="3">
-        <v>45.518999999999998</v>
-      </c>
-      <c r="L79" s="6">
-        <v>1.4246798039999999</v>
+        <v>35.933</v>
+      </c>
+      <c r="L79" s="3">
+        <v>1.1547324186680767</v>
       </c>
       <c r="M79" s="2">
-        <v>321.49026300000003</v>
+        <v>245.92968800000003</v>
       </c>
       <c r="N79" s="2">
-        <v>171.64188399999998</v>
+        <v>129.30007800000001</v>
       </c>
       <c r="O79" s="2">
-        <v>149.84830299999999</v>
+        <v>116.629651</v>
       </c>
       <c r="P79" s="2">
-        <v>258.476448</v>
+        <v>271.65998100000002</v>
       </c>
       <c r="Q79" s="2">
-        <v>157.37730500000006</v>
+        <v>121.86641</v>
       </c>
       <c r="R79" s="2">
-        <v>101.099051</v>
+        <v>149.79363000000001</v>
       </c>
       <c r="S79" s="2">
-        <v>1.2437893877278909</v>
+        <v>0.90528493411033562</v>
       </c>
       <c r="T79" s="2">
+        <v>3</v>
+      </c>
+      <c r="U79" s="2">
+        <v>1</v>
+      </c>
+      <c r="V79" s="2">
+        <v>0</v>
+      </c>
+      <c r="W79" s="2">
         <v>4</v>
       </c>
-      <c r="U79" s="2">
-        <v>5</v>
-      </c>
-      <c r="V79" s="2">
-        <v>2</v>
-      </c>
-      <c r="W79" s="2">
-        <v>11</v>
-      </c>
       <c r="X79" s="2">
+        <v>6</v>
+      </c>
+      <c r="Y79" s="2">
+        <v>7</v>
+      </c>
+      <c r="Z79" s="2">
+        <v>3</v>
+      </c>
+      <c r="AA79" s="2">
+        <v>16</v>
+      </c>
+      <c r="AB79" s="2">
         <v>4</v>
-      </c>
-      <c r="Y79" s="2">
-        <v>4</v>
-      </c>
-      <c r="Z79" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA79" s="2">
-        <v>9</v>
-      </c>
-      <c r="AB79" s="2">
-        <v>1.2222222222222223</v>
       </c>
       <c r="AC79" s="11">
         <f t="shared" si="2"/>
-        <v>2.1093085860498868</v>
+        <v>2.250552515442259</v>
       </c>
     </row>
     <row r="80" spans="1:29" ht="17">
-      <c r="A80" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D80" s="2">
-        <v>114</v>
+      <c r="A80" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B80" s="3">
+        <v>209.8</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D80" s="3">
+        <v>101.7</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F80" s="2">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="G80" s="2">
-        <v>1868.85</v>
-      </c>
-      <c r="H80" s="3">
-        <v>6.99</v>
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="G80" s="7">
+        <v>438.36206896551721</v>
+      </c>
+      <c r="H80" s="2">
+        <v>-20.690999999999999</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J80" s="3">
-        <v>48.423999999999999</v>
+        <v>44.796999999999997</v>
       </c>
       <c r="K80" s="3">
-        <v>42.616</v>
-      </c>
-      <c r="L80" s="6">
-        <v>1.136286841</v>
+        <v>41.962000000000003</v>
+      </c>
+      <c r="L80" s="3">
+        <v>1.0675611267337113</v>
       </c>
       <c r="M80" s="2">
-        <v>348.74787699999996</v>
+        <v>443.05761199999995</v>
       </c>
       <c r="N80" s="2">
-        <v>162.614959</v>
+        <v>273.54349500000006</v>
       </c>
       <c r="O80" s="2">
-        <v>186.13324399999999</v>
+        <v>169.51407600000005</v>
       </c>
       <c r="P80" s="2">
-        <v>321.49026300000003</v>
+        <v>271.65998100000002</v>
       </c>
       <c r="Q80" s="2">
-        <v>171.64188399999998</v>
+        <v>121.86641</v>
       </c>
       <c r="R80" s="2">
-        <v>149.84830299999999</v>
+        <v>149.79363000000001</v>
       </c>
       <c r="S80" s="2">
-        <v>1.0847851930122061</v>
+        <v>1.6309270521520058</v>
       </c>
       <c r="T80" s="2">
+        <v>12</v>
+      </c>
+      <c r="U80" s="2">
+        <v>6</v>
+      </c>
+      <c r="V80" s="2">
+        <v>2</v>
+      </c>
+      <c r="W80" s="2">
+        <v>20</v>
+      </c>
+      <c r="X80" s="2">
+        <v>6</v>
+      </c>
+      <c r="Y80" s="2">
         <v>7</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Z80" s="2">
         <v>3</v>
       </c>
-      <c r="V80" s="2">
-        <v>0</v>
-      </c>
-      <c r="W80" s="2">
-        <v>10</v>
-      </c>
-      <c r="X80" s="2">
-        <v>4</v>
-      </c>
-      <c r="Y80" s="2">
-        <v>5</v>
-      </c>
-      <c r="Z80" s="2">
-        <v>2</v>
-      </c>
       <c r="AA80" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AB80" s="2">
-        <v>0.90909090909090906</v>
+        <v>0.8</v>
       </c>
       <c r="AC80" s="11">
         <f t="shared" si="2"/>
-        <v>2.6880188750787029</v>
+        <v>2.2324388732662888</v>
       </c>
     </row>
     <row r="81" spans="1:29" ht="17">
       <c r="A81" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B81" s="3">
+        <v>209.8</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B81" s="3">
-        <v>867.3</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="D81" s="3">
-        <v>101.7</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F81" s="2">
-        <v>4.09</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="G81" s="7">
-        <v>24.865525672371639</v>
+        <v>0.29429892141756547</v>
       </c>
       <c r="H81" s="2">
-        <v>-27.199000000000002</v>
+        <v>53.537999999999997</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="J81" s="3">
-        <v>41.493000000000002</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="K81" s="3">
-        <v>35.933</v>
+        <v>59.643999999999998</v>
       </c>
       <c r="L81" s="3">
-        <v>1.1547324186680767</v>
+        <v>1.0872845550264905</v>
       </c>
       <c r="M81" s="2">
-        <v>245.92968800000003</v>
+        <v>443.05761199999995</v>
       </c>
       <c r="N81" s="2">
-        <v>129.30007800000001</v>
+        <v>273.54349500000006</v>
       </c>
       <c r="O81" s="2">
-        <v>116.629651</v>
+        <v>169.51407600000005</v>
       </c>
       <c r="P81" s="2">
-        <v>271.65998100000002</v>
+        <v>313.33782000000002</v>
       </c>
       <c r="Q81" s="2">
-        <v>121.86641</v>
+        <v>153.24117900000005</v>
       </c>
       <c r="R81" s="2">
-        <v>149.79363000000001</v>
+        <v>160.0966</v>
       </c>
       <c r="S81" s="2">
-        <v>0.90528493411033562</v>
+        <v>1.4139934081369427</v>
       </c>
       <c r="T81" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U81" s="2">
+        <v>6</v>
+      </c>
+      <c r="V81" s="2">
+        <v>2</v>
+      </c>
+      <c r="W81" s="2">
+        <v>20</v>
+      </c>
+      <c r="X81" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="2">
         <v>1</v>
       </c>
-      <c r="V81" s="2">
-        <v>0</v>
-      </c>
-      <c r="W81" s="2">
-        <v>4</v>
-      </c>
-      <c r="X81" s="2">
+      <c r="Z81" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="2">
         <v>6</v>
       </c>
-      <c r="Y81" s="2">
-        <v>7</v>
-      </c>
-      <c r="Z81" s="2">
-        <v>3</v>
-      </c>
-      <c r="AA81" s="2">
-        <v>16</v>
-      </c>
       <c r="AB81" s="2">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="AC81" s="11">
         <f t="shared" si="2"/>
-        <v>2.250552515442259</v>
+        <v>1.9987220368365668</v>
       </c>
     </row>
     <row r="82" spans="1:29" ht="17">
       <c r="A82" s="3" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="B82" s="3">
-        <v>209.8</v>
+        <v>1480</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="D82" s="3">
-        <v>101.7</v>
+        <v>601</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F82" s="2">
-        <v>0.23200000000000001</v>
+        <v>181</v>
+      </c>
+      <c r="F82" s="3">
+        <v>2.25</v>
       </c>
       <c r="G82" s="7">
-        <v>438.36206896551721</v>
+        <v>267.11111111111109</v>
       </c>
       <c r="H82" s="2">
-        <v>-20.690999999999999</v>
+        <v>25.981000000000002</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J82" s="3">
-        <v>44.796999999999997</v>
-      </c>
-      <c r="K82" s="3">
-        <v>41.962000000000003</v>
-      </c>
-      <c r="L82" s="3">
-        <v>1.0675611267337113</v>
+        <v>166</v>
+      </c>
+      <c r="J82" s="7">
+        <v>48.484000000000002</v>
+      </c>
+      <c r="K82" s="7">
+        <v>47.137</v>
+      </c>
+      <c r="L82" s="7">
+        <f t="shared" ref="L82" si="3">J82/K82</f>
+        <v>1.0285762776587395</v>
       </c>
       <c r="M82" s="2">
-        <v>443.05761199999995</v>
+        <v>497.53826999999995</v>
       </c>
       <c r="N82" s="2">
-        <v>273.54349500000006</v>
+        <v>239.94313700000006</v>
       </c>
       <c r="O82" s="2">
-        <v>169.51407600000005</v>
+        <v>257.59497199999998</v>
       </c>
       <c r="P82" s="2">
-        <v>271.65998100000002</v>
+        <v>539.15123300000005</v>
       </c>
       <c r="Q82" s="2">
-        <v>121.86641</v>
+        <v>297.34429000000006</v>
       </c>
       <c r="R82" s="2">
-        <v>149.79363000000001</v>
+        <v>241.80690300000003</v>
       </c>
       <c r="S82" s="2">
-        <v>1.6309270521520058</v>
+        <v>0.92281764289315815</v>
       </c>
       <c r="T82" s="2">
+        <v>14</v>
+      </c>
+      <c r="U82" s="2">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2">
+        <v>0</v>
+      </c>
+      <c r="W82" s="2">
+        <v>14</v>
+      </c>
+      <c r="X82" s="2">
         <v>12</v>
       </c>
-      <c r="U82" s="2">
-        <v>6</v>
-      </c>
-      <c r="V82" s="2">
-        <v>2</v>
-      </c>
-      <c r="W82" s="2">
-        <v>20</v>
-      </c>
-      <c r="X82" s="2">
-        <v>6</v>
-      </c>
       <c r="Y82" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z82" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA82" s="2">
         <v>16</v>
       </c>
       <c r="AB82" s="2">
-        <v>0.8</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="AC82" s="11">
         <f t="shared" si="2"/>
-        <v>2.2324388732662888</v>
+        <v>2.751384222377276</v>
       </c>
     </row>
     <row r="83" spans="1:29" ht="17">
       <c r="A83" s="3" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="B83" s="3">
-        <v>209.8</v>
+        <v>1480</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="D83" s="3">
-        <v>19.100000000000001</v>
+        <v>2060</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F83" s="2">
-        <v>64.900000000000006</v>
+        <v>1.66</v>
       </c>
       <c r="G83" s="7">
-        <v>0.29429892141756547</v>
+        <v>891.56626506024099</v>
       </c>
       <c r="H83" s="2">
-        <v>53.537999999999997</v>
+        <v>37.536999999999999</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J83" s="3">
-        <v>64.849999999999994</v>
-      </c>
-      <c r="K83" s="3">
-        <v>59.643999999999998</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1.0872845550264905</v>
+        <v>186</v>
+      </c>
+      <c r="J83" s="7">
+        <v>84.430999999999997</v>
+      </c>
+      <c r="K83" s="7">
+        <v>82.947999999999993</v>
+      </c>
+      <c r="L83" s="7">
+        <f>J83/K83</f>
+        <v>1.0178786709745866</v>
       </c>
       <c r="M83" s="2">
-        <v>443.05761199999995</v>
+        <v>497.53826999999995</v>
       </c>
       <c r="N83" s="2">
-        <v>273.54349500000006</v>
+        <v>239.94313700000006</v>
       </c>
       <c r="O83" s="2">
-        <v>169.51407600000005</v>
+        <v>257.59497199999998</v>
       </c>
       <c r="P83" s="2">
-        <v>313.33782000000002</v>
+        <v>411.8296180000001</v>
       </c>
       <c r="Q83" s="2">
-        <v>153.24117900000005</v>
+        <v>235.11411600000005</v>
       </c>
       <c r="R83" s="2">
-        <v>160.0966</v>
+        <v>176.71553800000004</v>
       </c>
       <c r="S83" s="2">
-        <v>1.4139934081369427</v>
+        <v>1.2081167751271349</v>
       </c>
       <c r="T83" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U83" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V83" s="2">
+        <v>0</v>
+      </c>
+      <c r="W83" s="2">
+        <v>14</v>
+      </c>
+      <c r="X83" s="2">
+        <v>9</v>
+      </c>
+      <c r="Y83" s="2">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="2">
         <v>2</v>
       </c>
-      <c r="W83" s="2">
-        <v>20</v>
-      </c>
-      <c r="X83" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="2">
+      <c r="AA83" s="2">
+        <v>14</v>
+      </c>
+      <c r="AB83" s="2">
         <v>1</v>
-      </c>
-      <c r="Z83" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="2">
-        <v>6</v>
-      </c>
-      <c r="AB83" s="2">
-        <v>0.3</v>
       </c>
       <c r="AC83" s="11">
         <f t="shared" si="2"/>
-        <v>1.9987220368365668</v>
+        <v>2.7740045538982785</v>
       </c>
     </row>
     <row r="84" spans="1:29" ht="17">
       <c r="A84" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B84" s="3">
-        <v>1480</v>
+        <v>100</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D84" s="3">
-        <v>601</v>
+        <v>105</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="F84" s="3">
-        <v>2.25</v>
+        <v>183</v>
+      </c>
+      <c r="F84" s="2">
+        <v>3.7</v>
       </c>
       <c r="G84" s="7">
-        <v>267.11111111111109</v>
+        <v>27.027027027027025</v>
       </c>
       <c r="H84" s="2">
-        <v>25.981000000000002</v>
+        <v>5.9850000000000003</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J84" s="7">
-        <v>48.484000000000002</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="K84" s="7">
-        <v>47.137</v>
+        <v>62.48</v>
       </c>
       <c r="L84" s="7">
-        <f t="shared" ref="L84" si="3">J84/K84</f>
-        <v>1.0285762776587395</v>
+        <f t="shared" ref="L84:L88" si="4">J84/K84</f>
+        <v>1.037932138284251</v>
       </c>
       <c r="M84" s="2">
-        <v>497.53826999999995</v>
+        <v>462.43215500000002</v>
       </c>
       <c r="N84" s="2">
-        <v>239.94313700000006</v>
+        <v>239.18309600000001</v>
       </c>
       <c r="O84" s="2">
-        <v>257.59497199999998</v>
+        <v>223.24905699999997</v>
       </c>
       <c r="P84" s="2">
-        <v>539.15123300000005</v>
+        <v>530.66215899999997</v>
       </c>
       <c r="Q84" s="2">
-        <v>297.34429000000006</v>
+        <v>330.95660999999996</v>
       </c>
       <c r="R84" s="2">
-        <v>241.80690300000003</v>
+        <v>199.70535100000001</v>
       </c>
       <c r="S84" s="2">
-        <v>0.92281764289315815</v>
+        <v>0.87142477969679399</v>
       </c>
       <c r="T84" s="2">
+        <v>15</v>
+      </c>
+      <c r="U84" s="2">
+        <v>5</v>
+      </c>
+      <c r="V84" s="2">
+        <v>0</v>
+      </c>
+      <c r="W84" s="2">
+        <v>20</v>
+      </c>
+      <c r="X84" s="2">
         <v>14</v>
       </c>
-      <c r="U84" s="2">
-        <v>0</v>
-      </c>
-      <c r="V84" s="2">
-        <v>0</v>
-      </c>
-      <c r="W84" s="2">
-        <v>14</v>
-      </c>
-      <c r="X84" s="2">
-        <v>12</v>
-      </c>
       <c r="Y84" s="2">
+        <v>7</v>
+      </c>
+      <c r="Z84" s="2">
         <v>4</v>
       </c>
-      <c r="Z84" s="2">
-        <v>0</v>
-      </c>
       <c r="AA84" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AB84" s="2">
-        <v>1.1428571428571428</v>
+        <v>1.25</v>
       </c>
       <c r="AC84" s="11">
         <f t="shared" si="2"/>
-        <v>2.751384222377276</v>
+        <v>2.5834926414125432</v>
       </c>
     </row>
     <row r="85" spans="1:29" ht="17">
       <c r="A85" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B85" s="3">
-        <v>1480</v>
+        <v>4370</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>124</v>
       </c>
       <c r="D85" s="3">
-        <v>2060</v>
+        <v>921</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F85" s="2">
-        <v>1.66</v>
+        <v>140</v>
       </c>
       <c r="G85" s="7">
-        <v>891.56626506024099</v>
+        <v>6.5785714285714283</v>
       </c>
       <c r="H85" s="2">
-        <v>37.536999999999999</v>
+        <v>37.963000000000001</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J85" s="7">
-        <v>84.430999999999997</v>
+        <v>56.567</v>
       </c>
       <c r="K85" s="7">
-        <v>82.947999999999993</v>
+        <v>52.018999999999998</v>
       </c>
       <c r="L85" s="7">
-        <f>J85/K85</f>
-        <v>1.0178786709745866</v>
+        <f t="shared" si="4"/>
+        <v>1.0874295930333149</v>
       </c>
       <c r="M85" s="2">
-        <v>497.53826999999995</v>
+        <v>506.43552499999987</v>
       </c>
       <c r="N85" s="2">
-        <v>239.94313700000006</v>
+        <v>259.91992799999997</v>
       </c>
       <c r="O85" s="2">
-        <v>257.59497199999998</v>
+        <v>246.51551700000005</v>
       </c>
       <c r="P85" s="2">
-        <v>411.8296180000001</v>
+        <v>414.92451099999994</v>
       </c>
       <c r="Q85" s="2">
-        <v>235.11411600000005</v>
+        <v>301.91507500000006</v>
       </c>
       <c r="R85" s="2">
-        <v>176.71553800000004</v>
+        <v>113.009351</v>
       </c>
       <c r="S85" s="2">
-        <v>1.2081167751271349</v>
+        <v>1.2205485855233074</v>
       </c>
       <c r="T85" s="2">
+        <v>16</v>
+      </c>
+      <c r="U85" s="2">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2">
+        <v>0</v>
+      </c>
+      <c r="W85" s="2">
+        <v>16</v>
+      </c>
+      <c r="X85" s="2">
         <v>14</v>
-      </c>
-      <c r="U85" s="2">
-        <v>0</v>
-      </c>
-      <c r="V85" s="2">
-        <v>0</v>
-      </c>
-      <c r="W85" s="2">
-        <v>14</v>
-      </c>
-      <c r="X85" s="2">
-        <v>9</v>
       </c>
       <c r="Y85" s="2">
         <v>3</v>
       </c>
       <c r="Z85" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA85" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AB85" s="2">
-        <v>1</v>
+        <v>1.0625</v>
       </c>
       <c r="AC85" s="11">
         <f t="shared" si="2"/>
-        <v>2.7740045538982785</v>
+        <v>2.6295218214433778</v>
       </c>
     </row>
     <row r="86" spans="1:29" ht="17">
       <c r="A86" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B86" s="3">
-        <v>100</v>
+        <v>4370</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D86" s="3">
-        <v>105</v>
+        <v>2060</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F86" s="2">
-        <v>3.7</v>
+        <v>180</v>
+      </c>
+      <c r="F86" s="3">
+        <v>1540</v>
       </c>
       <c r="G86" s="7">
-        <v>27.027027027027025</v>
+        <v>1.3376623376623376</v>
       </c>
       <c r="H86" s="2">
-        <v>5.9850000000000003</v>
+        <v>34.478999999999999</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="J86" s="7">
-        <v>64.849999999999994</v>
+        <v>82.206000000000003</v>
       </c>
       <c r="K86" s="7">
-        <v>62.48</v>
+        <v>79.210999999999999</v>
       </c>
       <c r="L86" s="7">
-        <f t="shared" ref="L86:L90" si="4">J86/K86</f>
-        <v>1.037932138284251</v>
+        <f t="shared" si="4"/>
+        <v>1.037810405120501</v>
       </c>
       <c r="M86" s="2">
-        <v>462.43215500000002</v>
+        <v>506.43552499999987</v>
       </c>
       <c r="N86" s="2">
-        <v>239.18309600000001</v>
+        <v>259.91992799999997</v>
       </c>
       <c r="O86" s="2">
-        <v>223.24905699999997</v>
+        <v>246.51551700000005</v>
       </c>
       <c r="P86" s="2">
-        <v>530.66215899999997</v>
+        <v>411.8296180000001</v>
       </c>
       <c r="Q86" s="2">
-        <v>330.95660999999996</v>
+        <v>235.11411600000005</v>
       </c>
       <c r="R86" s="2">
-        <v>199.70535100000001</v>
+        <v>176.71553800000004</v>
       </c>
       <c r="S86" s="2">
-        <v>0.87142477969679399</v>
+        <v>1.2297209886443858</v>
       </c>
       <c r="T86" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U86" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V86" s="2">
         <v>0</v>
       </c>
       <c r="W86" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="X86" s="2">
+        <v>9</v>
+      </c>
+      <c r="Y86" s="2">
+        <v>3</v>
+      </c>
+      <c r="Z86" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA86" s="2">
         <v>14</v>
       </c>
-      <c r="Y86" s="2">
-        <v>7</v>
-      </c>
-      <c r="Z86" s="2">
-        <v>4</v>
-      </c>
-      <c r="AA86" s="2">
-        <v>25</v>
-      </c>
       <c r="AB86" s="2">
-        <v>1.25</v>
+        <v>0.875</v>
       </c>
       <c r="AC86" s="11">
         <f t="shared" si="2"/>
-        <v>2.5834926414125432</v>
+        <v>2.6074686062351131</v>
       </c>
     </row>
     <row r="87" spans="1:29" ht="17">
       <c r="A87" s="3" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="B87" s="3">
-        <v>4370</v>
+        <v>138</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="D87" s="3">
-        <v>921</v>
+        <v>99.5</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F87" s="2">
-        <v>140</v>
+        <v>19.2</v>
       </c>
       <c r="G87" s="7">
-        <v>6.5785714285714283</v>
+        <v>5.182291666666667</v>
       </c>
       <c r="H87" s="2">
-        <v>37.963000000000001</v>
+        <v>6.0439999999999996</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="J87" s="7">
-        <v>56.567</v>
+        <v>48.484000000000002</v>
       </c>
       <c r="K87" s="7">
-        <v>52.018999999999998</v>
+        <v>46.444000000000003</v>
       </c>
       <c r="L87" s="7">
         <f t="shared" si="4"/>
-        <v>1.0874295930333149</v>
+        <v>1.0439238653001464</v>
       </c>
       <c r="M87" s="2">
-        <v>506.43552499999987</v>
+        <v>401.78200400000003</v>
       </c>
       <c r="N87" s="2">
-        <v>259.91992799999997</v>
+        <v>220.08053999999998</v>
       </c>
       <c r="O87" s="2">
-        <v>246.51551700000005</v>
+        <v>181.70129399999999</v>
       </c>
       <c r="P87" s="2">
-        <v>414.92451099999994</v>
+        <v>355.54163900000003</v>
       </c>
       <c r="Q87" s="2">
-        <v>301.91507500000006</v>
+        <v>93.098927000000018</v>
       </c>
       <c r="R87" s="2">
-        <v>113.009351</v>
+        <v>262.44285100000008</v>
       </c>
       <c r="S87" s="2">
-        <v>1.2205485855233074</v>
+        <v>1.130056116999562</v>
       </c>
       <c r="T87" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="U87" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V87" s="2">
         <v>0</v>
       </c>
       <c r="W87" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X87" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y87" s="2">
+        <v>9</v>
+      </c>
+      <c r="Z87" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="2">
         <v>14</v>
       </c>
-      <c r="Y87" s="2">
-        <v>3</v>
-      </c>
-      <c r="Z87" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="2">
-        <v>17</v>
-      </c>
       <c r="AB87" s="2">
-        <v>1.0625</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="AC87" s="11">
         <f t="shared" si="2"/>
-        <v>2.6295218214433778</v>
+        <v>2.6495494294649973</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="17">
       <c r="A88" s="3" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="B88" s="3">
-        <v>4370</v>
+        <v>220</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D88" s="3">
-        <v>2060</v>
+        <v>1470</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F88" s="3">
-        <v>1540</v>
+        <v>66</v>
+      </c>
+      <c r="F88" s="2">
+        <v>2.7</v>
       </c>
       <c r="G88" s="7">
-        <v>1.3376623376623376</v>
+        <v>81.481481481481481</v>
       </c>
       <c r="H88" s="2">
-        <v>34.478999999999999</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>163</v>
+        <v>31.024000000000001</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="J88" s="7">
-        <v>82.206000000000003</v>
+        <v>56.567</v>
       </c>
       <c r="K88" s="7">
-        <v>79.210999999999999</v>
+        <v>55.347999999999999</v>
       </c>
       <c r="L88" s="7">
         <f t="shared" si="4"/>
-        <v>1.037810405120501</v>
+        <v>1.0220242827202428</v>
       </c>
       <c r="M88" s="2">
-        <v>506.43552499999987</v>
+        <v>489.53467200000006</v>
       </c>
       <c r="N88" s="2">
-        <v>259.91992799999997</v>
+        <v>159.10767099999998</v>
       </c>
       <c r="O88" s="2">
-        <v>246.51551700000005</v>
+        <v>330.42694800000004</v>
       </c>
       <c r="P88" s="2">
-        <v>411.8296180000001</v>
+        <v>479.61241899999999</v>
       </c>
       <c r="Q88" s="2">
-        <v>235.11411600000005</v>
+        <v>138.09142900000001</v>
       </c>
       <c r="R88" s="2">
-        <v>176.71553800000004</v>
+        <v>341.52099600000003</v>
       </c>
       <c r="S88" s="2">
-        <v>1.2297209886443858</v>
+        <v>1.0206880652104215</v>
       </c>
       <c r="T88" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U88" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V88" s="2">
         <v>0</v>
       </c>
       <c r="W88" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X88" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y88" s="2">
         <v>3</v>
       </c>
       <c r="Z88" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA88" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AB88" s="2">
-        <v>0.875</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AC88" s="11">
         <f t="shared" si="2"/>
-        <v>2.6074686062351131</v>
+        <v>2.7430019377836214</v>
       </c>
     </row>
     <row r="89" spans="1:29" ht="17">
-      <c r="A89" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B89" s="3">
-        <v>138</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D89" s="3">
-        <v>99.5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>187</v>
+      <c r="A89" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" s="2">
+        <v>1750</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D89" s="2">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="F89" s="2">
-        <v>19.2</v>
-      </c>
-      <c r="G89" s="7">
-        <v>5.182291666666667</v>
-      </c>
-      <c r="H89" s="2">
-        <v>6.0439999999999996</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J89" s="7">
-        <v>48.484000000000002</v>
-      </c>
-      <c r="K89" s="7">
-        <v>46.444000000000003</v>
-      </c>
-      <c r="L89" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0439238653001464</v>
-      </c>
-      <c r="M89" s="2">
-        <v>401.78200400000003</v>
-      </c>
-      <c r="N89" s="2">
-        <v>220.08053999999998</v>
-      </c>
-      <c r="O89" s="2">
-        <v>181.70129399999999</v>
-      </c>
-      <c r="P89" s="2">
-        <v>355.54163900000003</v>
-      </c>
-      <c r="Q89" s="2">
-        <v>93.098927000000018</v>
-      </c>
-      <c r="R89" s="2">
-        <v>262.44285100000008</v>
-      </c>
-      <c r="S89" s="2">
-        <v>1.130056116999562</v>
-      </c>
-      <c r="T89" s="2">
-        <v>12</v>
-      </c>
-      <c r="U89" s="2">
-        <v>5</v>
-      </c>
-      <c r="V89" s="2">
-        <v>0</v>
-      </c>
-      <c r="W89" s="2">
-        <v>17</v>
-      </c>
-      <c r="X89" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="2">
-        <v>9</v>
-      </c>
-      <c r="Z89" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="2">
-        <v>14</v>
-      </c>
-      <c r="AB89" s="2">
-        <v>0.82352941176470584</v>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="G89" s="2">
+        <v>3.5923913043478302</v>
+      </c>
+      <c r="H89" s="9">
+        <v>23.481999999999999</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J89" s="2">
+        <v>72</v>
+      </c>
+      <c r="K89" s="9">
+        <v>66.914000000000001</v>
+      </c>
+      <c r="L89" s="9">
+        <v>1.0760080102818543</v>
+      </c>
+      <c r="M89" s="9">
+        <v>171.45177000000001</v>
+      </c>
+      <c r="N89" s="9">
+        <v>110.238232</v>
+      </c>
+      <c r="O89" s="9">
+        <v>61.213506000000002</v>
+      </c>
+      <c r="P89" s="10">
+        <v>401.37350800000002</v>
+      </c>
+      <c r="Q89" s="10">
+        <v>213.85547299999999</v>
+      </c>
+      <c r="R89" s="10">
+        <v>187.518067</v>
+      </c>
+      <c r="S89" s="9">
+        <v>0.42716264671857718</v>
+      </c>
+      <c r="T89" s="9">
+        <v>3</v>
+      </c>
+      <c r="U89" s="9">
+        <v>1</v>
+      </c>
+      <c r="V89" s="9">
+        <v>2</v>
+      </c>
+      <c r="W89" s="9">
+        <v>6</v>
+      </c>
+      <c r="X89" s="9">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="9">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="9">
+        <v>2</v>
+      </c>
+      <c r="AA89" s="9">
+        <v>8</v>
+      </c>
+      <c r="AB89" s="9">
+        <v>1.3333333333333333</v>
       </c>
       <c r="AC89" s="11">
         <f t="shared" si="2"/>
-        <v>2.6495494294649973</v>
+        <v>2.0906586563848126</v>
       </c>
     </row>
     <row r="90" spans="1:29" ht="17">
-      <c r="A90" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B90" s="3">
-        <v>220</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D90" s="3">
-        <v>1470</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>67</v>
+      <c r="A90" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B90" s="2">
+        <v>1480</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D90" s="2">
+        <v>601</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="F90" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="G90" s="7">
-        <v>81.481481481481481</v>
-      </c>
-      <c r="H90" s="2">
-        <v>31.024000000000001</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="J90" s="7">
-        <v>56.567</v>
-      </c>
-      <c r="K90" s="7">
-        <v>55.347999999999999</v>
-      </c>
-      <c r="L90" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0220242827202428</v>
-      </c>
-      <c r="M90" s="2">
-        <v>489.53467200000006</v>
-      </c>
-      <c r="N90" s="2">
-        <v>159.10767099999998</v>
-      </c>
-      <c r="O90" s="2">
-        <v>330.42694800000004</v>
-      </c>
-      <c r="P90" s="2">
-        <v>479.61241899999999</v>
-      </c>
-      <c r="Q90" s="2">
-        <v>138.09142900000001</v>
-      </c>
-      <c r="R90" s="2">
-        <v>341.52099600000003</v>
-      </c>
-      <c r="S90" s="2">
-        <v>1.0206880652104215</v>
-      </c>
-      <c r="T90" s="2">
+        <v>55.4</v>
+      </c>
+      <c r="G90" s="2">
+        <v>10.848375451263538</v>
+      </c>
+      <c r="H90" s="9">
+        <v>-5.5229999999999997</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J90" s="2">
+        <v>72</v>
+      </c>
+      <c r="K90" s="9">
+        <v>33.145000000000003</v>
+      </c>
+      <c r="L90" s="9">
+        <v>2.1722733443958364</v>
+      </c>
+      <c r="M90" s="10">
+        <v>308.80267300000003</v>
+      </c>
+      <c r="N90" s="10">
+        <v>201.33283900000001</v>
+      </c>
+      <c r="O90" s="10">
+        <v>107.46975</v>
+      </c>
+      <c r="P90" s="10">
+        <v>541.30428400000005</v>
+      </c>
+      <c r="Q90" s="10">
+        <v>264.874482</v>
+      </c>
+      <c r="R90" s="10">
+        <v>276.42980499999999</v>
+      </c>
+      <c r="S90" s="9">
+        <v>0.57047890092072506</v>
+      </c>
+      <c r="T90" s="9">
+        <v>3</v>
+      </c>
+      <c r="U90" s="9">
         <v>7</v>
       </c>
-      <c r="U90" s="2">
-        <v>7</v>
-      </c>
-      <c r="V90" s="2">
-        <v>0</v>
-      </c>
-      <c r="W90" s="2">
+      <c r="V90" s="9">
+        <v>4</v>
+      </c>
+      <c r="W90" s="9">
         <v>14</v>
       </c>
-      <c r="X90" s="2">
-        <v>8</v>
-      </c>
-      <c r="Y90" s="2">
-        <v>3</v>
-      </c>
-      <c r="Z90" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA90" s="2">
+      <c r="X90" s="9">
+        <v>6</v>
+      </c>
+      <c r="Y90" s="9">
         <v>11</v>
       </c>
-      <c r="AB90" s="2">
-        <v>0.7857142857142857</v>
+      <c r="Z90" s="9">
+        <v>4</v>
+      </c>
+      <c r="AA90" s="9">
+        <v>21</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>1.5</v>
       </c>
       <c r="AC90" s="11">
         <f t="shared" si="2"/>
-        <v>2.7430019377836214</v>
+        <v>1.0704789009207252</v>
       </c>
     </row>
     <row r="91" spans="1:29" ht="17">
       <c r="A91" s="2" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="B91" s="2">
-        <v>1750</v>
+        <v>1480</v>
       </c>
       <c r="C91" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D91" s="2">
+        <v>2060</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D91" s="2">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="F91" s="2">
-        <v>18.399999999999999</v>
+        <v>5.04</v>
       </c>
       <c r="G91" s="2">
-        <v>3.5923913043478302</v>
+        <v>293.65079365079401</v>
       </c>
       <c r="H91" s="9">
-        <v>23.481999999999999</v>
+        <v>14.73</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J91" s="2">
         <v>72</v>
       </c>
       <c r="K91" s="9">
-        <v>66.914000000000001</v>
+        <v>54.209000000000003</v>
       </c>
       <c r="L91" s="9">
-        <v>1.0760080102818543</v>
-      </c>
-      <c r="M91" s="9">
-        <v>171.45177000000001</v>
-      </c>
-      <c r="N91" s="9">
-        <v>110.238232</v>
-      </c>
-      <c r="O91" s="9">
-        <v>61.213506000000002</v>
+        <v>1.3281927355236214</v>
+      </c>
+      <c r="M91" s="10">
+        <v>308.80267300000003</v>
+      </c>
+      <c r="N91" s="10">
+        <v>201.33283900000001</v>
+      </c>
+      <c r="O91" s="10">
+        <v>107.46975</v>
       </c>
       <c r="P91" s="10">
-        <v>401.37350800000002</v>
+        <v>320.9597</v>
       </c>
       <c r="Q91" s="10">
-        <v>213.85547299999999</v>
+        <v>180.52893700000001</v>
       </c>
       <c r="R91" s="10">
-        <v>187.518067</v>
+        <v>140.43079800000001</v>
       </c>
       <c r="S91" s="9">
-        <v>0.42716264671857718</v>
+        <v>0.96212288645583866</v>
       </c>
       <c r="T91" s="9">
         <v>3</v>
       </c>
       <c r="U91" s="9">
+        <v>7</v>
+      </c>
+      <c r="V91" s="9">
+        <v>4</v>
+      </c>
+      <c r="W91" s="9">
+        <v>14</v>
+      </c>
+      <c r="X91" s="10">
+        <v>2</v>
+      </c>
+      <c r="Y91" s="10">
+        <v>14</v>
+      </c>
+      <c r="Z91" s="10">
         <v>1</v>
       </c>
-      <c r="V91" s="9">
-        <v>2</v>
-      </c>
-      <c r="W91" s="9">
-        <v>6</v>
-      </c>
-      <c r="X91" s="9">
-        <v>3</v>
-      </c>
-      <c r="Y91" s="9">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="9">
-        <v>2</v>
-      </c>
-      <c r="AA91" s="9">
-        <v>8</v>
+      <c r="AA91" s="10">
+        <v>17</v>
       </c>
       <c r="AB91" s="9">
-        <v>1.3333333333333333</v>
+        <v>1.2142857142857142</v>
       </c>
       <c r="AC91" s="11">
         <f t="shared" si="2"/>
-        <v>2.0906586563848126</v>
+        <v>2.4196444366465029</v>
       </c>
     </row>
     <row r="92" spans="1:29" ht="17">
       <c r="A92" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B92" s="2">
         <v>1480</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D92" s="2">
-        <v>601</v>
+        <v>921</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F92" s="2">
-        <v>55.4</v>
+        <v>97.9</v>
       </c>
       <c r="G92" s="2">
-        <v>10.848375451263538</v>
+        <v>9.4075587334014301</v>
       </c>
       <c r="H92" s="9">
-        <v>-5.5229999999999997</v>
+        <v>27.146000000000001</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J92" s="2">
         <v>72</v>
       </c>
       <c r="K92" s="9">
-        <v>33.145000000000003</v>
+        <v>16.439</v>
       </c>
       <c r="L92" s="9">
-        <v>2.1722733443958364</v>
+        <v>4.3798284567187782</v>
       </c>
       <c r="M92" s="10">
         <v>308.80267300000003</v>
@@ -9568,16 +9558,16 @@
         <v>107.46975</v>
       </c>
       <c r="P92" s="10">
-        <v>541.30428400000005</v>
+        <v>268.55290300000001</v>
       </c>
       <c r="Q92" s="10">
-        <v>264.874482</v>
+        <v>185.45786000000001</v>
       </c>
       <c r="R92" s="10">
-        <v>276.42980499999999</v>
+        <v>83.095070000000007</v>
       </c>
       <c r="S92" s="9">
-        <v>0.57047890092072506</v>
+        <v>1.1498765031037479</v>
       </c>
       <c r="T92" s="9">
         <v>3</v>
@@ -9591,242 +9581,242 @@
       <c r="W92" s="9">
         <v>14</v>
       </c>
-      <c r="X92" s="9">
+      <c r="X92" s="10">
+        <v>3</v>
+      </c>
+      <c r="Y92" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z92" s="10">
+        <v>2</v>
+      </c>
+      <c r="AA92" s="10">
         <v>6</v>
       </c>
-      <c r="Y92" s="9">
-        <v>11</v>
-      </c>
-      <c r="Z92" s="9">
-        <v>4</v>
-      </c>
-      <c r="AA92" s="9">
-        <v>21</v>
-      </c>
       <c r="AB92" s="9">
-        <v>1.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AC92" s="11">
         <f t="shared" si="2"/>
-        <v>1.0704789009207252</v>
+        <v>1.3501234968962521</v>
       </c>
     </row>
     <row r="93" spans="1:29" ht="17">
       <c r="A93" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B93" s="2">
-        <v>1480</v>
+        <v>100</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D93" s="2">
-        <v>2060</v>
+        <v>105</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F93" s="2">
-        <v>5.04</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="G93" s="2">
-        <v>293.65079365079401</v>
+        <v>10.288065843621398</v>
       </c>
       <c r="H93" s="9">
-        <v>14.73</v>
+        <v>-5.258</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J93" s="2">
         <v>72</v>
       </c>
       <c r="K93" s="9">
-        <v>54.209000000000003</v>
+        <v>35.959000000000003</v>
       </c>
       <c r="L93" s="9">
-        <v>1.3281927355236214</v>
+        <v>2.0022803748713813</v>
       </c>
       <c r="M93" s="10">
-        <v>308.80267300000003</v>
+        <v>509.061894</v>
       </c>
       <c r="N93" s="10">
-        <v>201.33283900000001</v>
+        <v>304.09381500000001</v>
       </c>
       <c r="O93" s="10">
-        <v>107.46975</v>
+        <v>204.96811299999999</v>
       </c>
       <c r="P93" s="10">
-        <v>320.9597</v>
+        <v>404.02995700000002</v>
       </c>
       <c r="Q93" s="10">
-        <v>180.52893700000001</v>
+        <v>219.08395200000001</v>
       </c>
       <c r="R93" s="10">
-        <v>140.43079800000001</v>
+        <v>184.94590600000001</v>
       </c>
       <c r="S93" s="9">
-        <v>0.96212288645583866</v>
-      </c>
-      <c r="T93" s="9">
-        <v>3</v>
-      </c>
-      <c r="U93" s="9">
-        <v>7</v>
-      </c>
-      <c r="V93" s="9">
+        <v>1.2599607657310419</v>
+      </c>
+      <c r="T93" s="10">
+        <v>6</v>
+      </c>
+      <c r="U93" s="10">
+        <v>11</v>
+      </c>
+      <c r="V93" s="10">
         <v>4</v>
       </c>
       <c r="W93" s="9">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="X93" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y93" s="10">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Z93" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA93" s="10">
+        <v>5</v>
+      </c>
+      <c r="AA93" s="9">
         <v>17</v>
       </c>
       <c r="AB93" s="9">
-        <v>1.2142857142857142</v>
+        <v>0.80952380952380953</v>
       </c>
       <c r="AC93" s="11">
         <f t="shared" si="2"/>
-        <v>2.4196444366465029</v>
+        <v>1.5495630437927677</v>
       </c>
     </row>
     <row r="94" spans="1:29" ht="17">
       <c r="A94" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B94" s="2">
-        <v>1480</v>
+        <v>100</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="D94" s="2">
-        <v>921</v>
+        <v>497</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>196</v>
       </c>
       <c r="F94" s="2">
-        <v>97.9</v>
+        <v>55.2</v>
       </c>
       <c r="G94" s="2">
-        <v>9.4075587334014301</v>
+        <v>1.8115942028985506</v>
       </c>
       <c r="H94" s="9">
-        <v>27.146000000000001</v>
+        <v>2.2519999999999998</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J94" s="2">
         <v>72</v>
       </c>
       <c r="K94" s="9">
-        <v>16.439</v>
+        <v>51.399000000000001</v>
       </c>
       <c r="L94" s="9">
-        <v>4.3798284567187782</v>
+        <v>1.4008054631413063</v>
       </c>
       <c r="M94" s="10">
-        <v>308.80267300000003</v>
+        <v>509.061894</v>
       </c>
       <c r="N94" s="10">
-        <v>201.33283900000001</v>
+        <v>304.09381500000001</v>
       </c>
       <c r="O94" s="10">
-        <v>107.46975</v>
+        <v>204.96811299999999</v>
       </c>
       <c r="P94" s="10">
-        <v>268.55290300000001</v>
+        <v>514.78644799999995</v>
       </c>
       <c r="Q94" s="10">
-        <v>185.45786000000001</v>
+        <v>268.82490200000001</v>
       </c>
       <c r="R94" s="10">
-        <v>83.095070000000007</v>
+        <v>245.96151399999999</v>
       </c>
       <c r="S94" s="9">
-        <v>1.1498765031037479</v>
-      </c>
-      <c r="T94" s="9">
-        <v>3</v>
-      </c>
-      <c r="U94" s="9">
-        <v>7</v>
-      </c>
-      <c r="V94" s="9">
+        <v>0.98887974999683759</v>
+      </c>
+      <c r="T94" s="10">
+        <v>6</v>
+      </c>
+      <c r="U94" s="10">
+        <v>11</v>
+      </c>
+      <c r="V94" s="10">
         <v>4</v>
       </c>
       <c r="W94" s="9">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="X94" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Y94" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z94" s="10">
         <v>2</v>
       </c>
-      <c r="AA94" s="10">
-        <v>6</v>
+      <c r="AA94" s="9">
+        <v>15</v>
       </c>
       <c r="AB94" s="9">
-        <v>0.42857142857142855</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AC94" s="11">
         <f t="shared" si="2"/>
-        <v>1.3501234968962521</v>
+        <v>2.3023600011412455</v>
       </c>
     </row>
     <row r="95" spans="1:29" ht="17">
       <c r="A95" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B95" s="2">
         <v>100</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="D95" s="2">
-        <v>105</v>
+        <v>601</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F95" s="2">
-        <v>9.7200000000000006</v>
+        <v>26.8</v>
       </c>
       <c r="G95" s="2">
-        <v>10.288065843621398</v>
+        <v>3.7313432835820897</v>
       </c>
       <c r="H95" s="9">
-        <v>-5.258</v>
+        <v>11.231999999999999</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J95" s="2">
         <v>72</v>
       </c>
       <c r="K95" s="9">
-        <v>35.959000000000003</v>
+        <v>45.908000000000001</v>
       </c>
       <c r="L95" s="9">
-        <v>2.0022803748713813</v>
+        <v>1.5683540995033545</v>
       </c>
       <c r="M95" s="10">
         <v>509.061894</v>
@@ -9838,16 +9828,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P95" s="10">
-        <v>404.02995700000002</v>
+        <v>194.02388099999999</v>
       </c>
       <c r="Q95" s="10">
-        <v>219.08395200000001</v>
+        <v>79.629563000000005</v>
       </c>
       <c r="R95" s="10">
-        <v>184.94590600000001</v>
+        <v>114.394385</v>
       </c>
       <c r="S95" s="9">
-        <v>1.2599607657310419</v>
+        <v>2.6237074084710224</v>
       </c>
       <c r="T95" s="10">
         <v>6</v>
@@ -9862,61 +9852,61 @@
         <v>21</v>
       </c>
       <c r="X95" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y95" s="10">
+        <v>2</v>
+      </c>
+      <c r="Z95" s="10">
+        <v>1</v>
+      </c>
+      <c r="AA95" s="9">
         <v>4</v>
       </c>
-      <c r="Y95" s="10">
-        <v>8</v>
-      </c>
-      <c r="Z95" s="10">
-        <v>5</v>
-      </c>
-      <c r="AA95" s="9">
-        <v>17</v>
-      </c>
       <c r="AB95" s="9">
-        <v>0.80952380952380953</v>
+        <v>0.19047619047619047</v>
       </c>
       <c r="AC95" s="11">
         <f t="shared" si="2"/>
-        <v>1.5495630437927677</v>
+        <v>1.4316459004966455</v>
       </c>
     </row>
     <row r="96" spans="1:29" ht="17">
       <c r="A96" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B96" s="2">
         <v>100</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D96" s="2">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F96" s="2">
-        <v>55.2</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="G96" s="2">
-        <v>1.8115942028985506</v>
+        <v>2.8409090909090908</v>
       </c>
       <c r="H96" s="9">
-        <v>2.2519999999999998</v>
+        <v>6.12</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J96" s="2">
         <v>72</v>
       </c>
       <c r="K96" s="9">
-        <v>51.399000000000001</v>
+        <v>63.408999999999999</v>
       </c>
       <c r="L96" s="9">
-        <v>1.4008054631413063</v>
+        <v>1.1354854989039411</v>
       </c>
       <c r="M96" s="10">
         <v>509.061894</v>
@@ -9928,16 +9918,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P96" s="10">
-        <v>514.78644799999995</v>
+        <v>548.452405</v>
       </c>
       <c r="Q96" s="10">
-        <v>268.82490200000001</v>
+        <v>272.29945600000002</v>
       </c>
       <c r="R96" s="10">
-        <v>245.96151399999999</v>
+        <v>276.15266400000002</v>
       </c>
       <c r="S96" s="9">
-        <v>0.98887974999683759</v>
+        <v>0.92817879793963165</v>
       </c>
       <c r="T96" s="10">
         <v>6</v>
@@ -9955,58 +9945,58 @@
         <v>9</v>
       </c>
       <c r="Y96" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z96" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA96" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB96" s="9">
-        <v>0.7142857142857143</v>
+        <v>0.76190476190476186</v>
       </c>
       <c r="AC96" s="11">
         <f t="shared" si="2"/>
-        <v>2.3023600011412455</v>
+        <v>2.5545980609404522</v>
       </c>
     </row>
     <row r="97" spans="1:29" ht="17">
       <c r="A97" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B97" s="2">
         <v>100</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D97" s="2">
-        <v>601</v>
+        <v>225</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F97" s="2">
-        <v>26.8</v>
+        <v>15.7</v>
       </c>
       <c r="G97" s="2">
-        <v>3.7313432835820897</v>
+        <v>6.369426751592357</v>
       </c>
       <c r="H97" s="9">
-        <v>11.231999999999999</v>
+        <v>31.081</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J97" s="2">
         <v>72</v>
       </c>
       <c r="K97" s="9">
-        <v>45.908000000000001</v>
+        <v>74.661000000000001</v>
       </c>
       <c r="L97" s="9">
-        <v>1.5683540995033545</v>
+        <v>0.96435890223811627</v>
       </c>
       <c r="M97" s="10">
         <v>509.061894</v>
@@ -10018,16 +10008,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P97" s="10">
-        <v>194.02388099999999</v>
+        <v>324.99903799999998</v>
       </c>
       <c r="Q97" s="10">
-        <v>79.629563000000005</v>
+        <v>195.09350000000001</v>
       </c>
       <c r="R97" s="10">
-        <v>114.394385</v>
+        <v>129.90543299999999</v>
       </c>
       <c r="S97" s="9">
-        <v>2.6237074084710224</v>
+        <v>1.5663489256235892</v>
       </c>
       <c r="T97" s="10">
         <v>6</v>
@@ -10042,61 +10032,61 @@
         <v>21</v>
       </c>
       <c r="X97" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y97" s="10">
+        <v>3</v>
+      </c>
+      <c r="Z97" s="10">
         <v>2</v>
       </c>
-      <c r="Z97" s="10">
-        <v>1</v>
-      </c>
       <c r="AA97" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AB97" s="9">
-        <v>0.19047619047619047</v>
+        <v>0.47619047619047616</v>
       </c>
       <c r="AC97" s="11">
         <f t="shared" si="2"/>
-        <v>1.4316459004966455</v>
+        <v>1.9643589022381163</v>
       </c>
     </row>
     <row r="98" spans="1:29" ht="17">
       <c r="A98" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B98" s="2">
         <v>100</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D98" s="2">
-        <v>565</v>
+        <v>801</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F98" s="2">
-        <v>35.200000000000003</v>
+        <v>158</v>
       </c>
       <c r="G98" s="2">
-        <v>2.8409090909090908</v>
+        <v>0.63291139240506333</v>
       </c>
       <c r="H98" s="9">
-        <v>6.12</v>
+        <v>15.066000000000001</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J98" s="2">
         <v>72</v>
       </c>
       <c r="K98" s="9">
-        <v>63.408999999999999</v>
+        <v>72.995999999999995</v>
       </c>
       <c r="L98" s="9">
-        <v>1.1354854989039411</v>
+        <v>0.98635541673516358</v>
       </c>
       <c r="M98" s="10">
         <v>509.061894</v>
@@ -10108,16 +10098,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P98" s="10">
-        <v>548.452405</v>
+        <v>352.63704300000001</v>
       </c>
       <c r="Q98" s="10">
-        <v>272.29945600000002</v>
+        <v>187.83172200000001</v>
       </c>
       <c r="R98" s="10">
-        <v>276.15266400000002</v>
+        <v>164.805374</v>
       </c>
       <c r="S98" s="9">
-        <v>0.92817879793963165</v>
+        <v>1.443585987646794</v>
       </c>
       <c r="T98" s="10">
         <v>6</v>
@@ -10132,151 +10122,151 @@
         <v>21</v>
       </c>
       <c r="X98" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y98" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z98" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA98" s="9">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AB98" s="9">
-        <v>0.76190476190476186</v>
+        <v>0.52380952380952384</v>
       </c>
       <c r="AC98" s="11">
         <f t="shared" si="2"/>
-        <v>2.5545980609404522</v>
+        <v>2.0665789528978933</v>
       </c>
     </row>
     <row r="99" spans="1:29" ht="17">
       <c r="A99" s="2" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="B99" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D99" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F99" s="2">
-        <v>15.7</v>
+        <v>113</v>
       </c>
       <c r="G99" s="2">
-        <v>6.369426751592357</v>
+        <v>1.9557522123893805</v>
       </c>
       <c r="H99" s="9">
-        <v>31.081</v>
+        <v>7.7590000000000003</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J99" s="2">
         <v>72</v>
       </c>
       <c r="K99" s="9">
-        <v>74.661000000000001</v>
+        <v>41.021000000000001</v>
       </c>
       <c r="L99" s="9">
-        <v>0.96435890223811627</v>
+        <v>1.7551985568367421</v>
       </c>
       <c r="M99" s="10">
-        <v>509.061894</v>
+        <v>328.36152499999997</v>
       </c>
       <c r="N99" s="10">
-        <v>304.09381500000001</v>
+        <v>200.67168100000001</v>
       </c>
       <c r="O99" s="10">
-        <v>204.96811299999999</v>
+        <v>127.689595</v>
       </c>
       <c r="P99" s="10">
-        <v>324.99903799999998</v>
+        <v>387.54889100000003</v>
       </c>
       <c r="Q99" s="10">
-        <v>195.09350000000001</v>
+        <v>221.91251700000001</v>
       </c>
       <c r="R99" s="10">
-        <v>129.90543299999999</v>
+        <v>165.63628199999999</v>
       </c>
       <c r="S99" s="9">
-        <v>1.5663489256235892</v>
+        <v>0.84727767934704257</v>
       </c>
       <c r="T99" s="10">
+        <v>3</v>
+      </c>
+      <c r="U99" s="10">
+        <v>8</v>
+      </c>
+      <c r="V99" s="10">
+        <v>1</v>
+      </c>
+      <c r="W99" s="9">
+        <v>12</v>
+      </c>
+      <c r="X99" s="10">
         <v>6</v>
       </c>
-      <c r="U99" s="10">
-        <v>11</v>
-      </c>
-      <c r="V99" s="10">
-        <v>4</v>
-      </c>
-      <c r="W99" s="9">
-        <v>21</v>
-      </c>
-      <c r="X99" s="10">
-        <v>5</v>
-      </c>
       <c r="Y99" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z99" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA99" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB99" s="9">
-        <v>0.47619047619047616</v>
+        <v>0.75</v>
       </c>
       <c r="AC99" s="11">
         <f t="shared" si="2"/>
-        <v>1.9643589022381163</v>
+        <v>1.8420791225103006</v>
       </c>
     </row>
     <row r="100" spans="1:29" ht="17">
       <c r="A100" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B100" s="2">
         <v>100</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="D100" s="2">
-        <v>801</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F100" s="2">
-        <v>158</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="G100" s="2">
-        <v>0.63291139240506333</v>
+        <v>0.28164251207729468</v>
       </c>
       <c r="H100" s="9">
-        <v>15.066000000000001</v>
+        <v>9.6210000000000004</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J100" s="2">
         <v>72</v>
       </c>
       <c r="K100" s="9">
-        <v>72.995999999999995</v>
+        <v>60.319000000000003</v>
       </c>
       <c r="L100" s="9">
-        <v>0.98635541673516358</v>
+        <v>1.1936537409439811</v>
       </c>
       <c r="M100" s="10">
         <v>509.061894</v>
@@ -10287,17 +10277,17 @@
       <c r="O100" s="10">
         <v>204.96811299999999</v>
       </c>
-      <c r="P100" s="10">
-        <v>352.63704300000001</v>
-      </c>
-      <c r="Q100" s="10">
-        <v>187.83172200000001</v>
-      </c>
-      <c r="R100" s="10">
-        <v>164.805374</v>
+      <c r="P100" s="9">
+        <v>467.95458200000007</v>
+      </c>
+      <c r="Q100" s="9">
+        <v>266.86430700000005</v>
+      </c>
+      <c r="R100" s="9">
+        <v>201.09016000000003</v>
       </c>
       <c r="S100" s="9">
-        <v>1.443585987646794</v>
+        <v>1.0878446618137825</v>
       </c>
       <c r="T100" s="10">
         <v>6</v>
@@ -10311,562 +10301,382 @@
       <c r="W100" s="9">
         <v>21</v>
       </c>
-      <c r="X100" s="10">
-        <v>6</v>
-      </c>
-      <c r="Y100" s="10">
-        <v>3</v>
-      </c>
-      <c r="Z100" s="10">
-        <v>2</v>
+      <c r="X100" s="9">
+        <v>9</v>
+      </c>
+      <c r="Y100" s="9">
+        <v>4</v>
+      </c>
+      <c r="Z100" s="9">
+        <v>1</v>
       </c>
       <c r="AA100" s="9">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AB100" s="9">
-        <v>0.52380952380952384</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AC100" s="11">
         <f t="shared" si="2"/>
-        <v>2.0665789528978933</v>
+        <v>2.3851682639089029</v>
       </c>
     </row>
     <row r="101" spans="1:29" ht="17">
       <c r="A101" s="2" t="s">
-        <v>208</v>
+        <v>125</v>
       </c>
       <c r="B101" s="2">
-        <v>259</v>
+        <v>100</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D101" s="2">
+        <v>1750</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D101" s="2">
-        <v>221</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="F101" s="2">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G101" s="2">
-        <v>1.9557522123893805</v>
+        <v>0.91743119266055051</v>
       </c>
       <c r="H101" s="9">
-        <v>7.7590000000000003</v>
+        <v>11.367000000000001</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J101" s="2">
         <v>72</v>
       </c>
       <c r="K101" s="9">
-        <v>41.021000000000001</v>
+        <v>31.901</v>
       </c>
       <c r="L101" s="9">
-        <v>1.7551985568367421</v>
+        <v>2.2569825397322969</v>
       </c>
       <c r="M101" s="10">
-        <v>328.36152499999997</v>
+        <v>509.061894</v>
       </c>
       <c r="N101" s="10">
-        <v>200.67168100000001</v>
+        <v>304.09381500000001</v>
       </c>
       <c r="O101" s="10">
-        <v>127.689595</v>
-      </c>
-      <c r="P101" s="10">
-        <v>387.54889100000003</v>
-      </c>
-      <c r="Q101" s="10">
-        <v>221.91251700000001</v>
-      </c>
-      <c r="R101" s="10">
-        <v>165.63628199999999</v>
+        <v>204.96811299999999</v>
+      </c>
+      <c r="P101" s="9">
+        <v>171.45177000000001</v>
+      </c>
+      <c r="Q101" s="9">
+        <v>110.238232</v>
+      </c>
+      <c r="R101" s="9">
+        <v>61.213506000000002</v>
       </c>
       <c r="S101" s="9">
-        <v>0.84727767934704257</v>
+        <v>2.9691259180351417</v>
       </c>
       <c r="T101" s="10">
+        <v>6</v>
+      </c>
+      <c r="U101" s="10">
+        <v>11</v>
+      </c>
+      <c r="V101" s="10">
+        <v>4</v>
+      </c>
+      <c r="W101" s="9">
+        <v>21</v>
+      </c>
+      <c r="X101" s="9">
         <v>3</v>
       </c>
-      <c r="U101" s="10">
-        <v>8</v>
-      </c>
-      <c r="V101" s="10">
+      <c r="Y101" s="9">
         <v>1</v>
       </c>
-      <c r="W101" s="9">
-        <v>12</v>
-      </c>
-      <c r="X101" s="10">
+      <c r="Z101" s="9">
+        <v>2</v>
+      </c>
+      <c r="AA101" s="9">
         <v>6</v>
       </c>
-      <c r="Y101" s="10">
-        <v>2</v>
-      </c>
-      <c r="Z101" s="10">
+      <c r="AB101" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AC101" s="11">
+        <f t="shared" ref="AC101:AC104" si="5">(1-MIN(ABS(L101-1),1))+(1-MIN(ABS(S101-1),0.5))+(1-MIN(ABS(AB101-1),0.5))</f>
         <v>1</v>
-      </c>
-      <c r="AA101" s="9">
-        <v>9</v>
-      </c>
-      <c r="AB101" s="9">
-        <v>0.75</v>
-      </c>
-      <c r="AC101" s="11">
-        <f t="shared" si="2"/>
-        <v>1.8420791225103006</v>
       </c>
     </row>
     <row r="102" spans="1:29" ht="17">
       <c r="A102" s="2" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="B102" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="D102" s="2">
-        <v>0.58299999999999996</v>
+        <v>4370</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F102" s="2">
-        <v>2.0699999999999998</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="G102" s="2">
-        <v>0.28164251207729468</v>
+        <v>3.4952766531713904</v>
       </c>
       <c r="H102" s="9">
-        <v>9.6210000000000004</v>
+        <v>-7.633</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J102" s="2">
         <v>72</v>
       </c>
       <c r="K102" s="9">
-        <v>60.319000000000003</v>
+        <v>23.245999999999999</v>
       </c>
       <c r="L102" s="9">
-        <v>1.1936537409439811</v>
+        <v>3.0973070635808311</v>
       </c>
       <c r="M102" s="10">
-        <v>509.061894</v>
+        <v>328.36152499999997</v>
       </c>
       <c r="N102" s="10">
-        <v>304.09381500000001</v>
+        <v>200.67168100000001</v>
       </c>
       <c r="O102" s="10">
-        <v>204.96811299999999</v>
+        <v>127.689595</v>
       </c>
       <c r="P102" s="9">
-        <v>467.95458200000007</v>
+        <v>167.93623199999999</v>
       </c>
       <c r="Q102" s="9">
-        <v>266.86430700000005</v>
+        <v>97.028190999999993</v>
       </c>
       <c r="R102" s="9">
-        <v>201.09016000000003</v>
+        <v>70.907809999999998</v>
       </c>
       <c r="S102" s="9">
-        <v>1.0878446618137825</v>
+        <v>1.95527505345005</v>
       </c>
       <c r="T102" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U102" s="10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V102" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="X102" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y102" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.16666666699999999</v>
+      </c>
+      <c r="AC102" s="11">
+        <f t="shared" si="5"/>
         <v>1</v>
-      </c>
-      <c r="AA102" s="9">
-        <v>14</v>
-      </c>
-      <c r="AB102" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AC102" s="11">
-        <f t="shared" si="2"/>
-        <v>2.3851682639089029</v>
       </c>
     </row>
     <row r="103" spans="1:29" ht="17">
       <c r="A103" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B103" s="2">
-        <v>100</v>
+        <v>4370</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>191</v>
+        <v>124</v>
       </c>
       <c r="D103" s="2">
-        <v>1750</v>
+        <v>921</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F103" s="2">
-        <v>109</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="G103" s="2">
-        <v>0.91743119266055051</v>
+        <v>13.870481927710841</v>
       </c>
       <c r="H103" s="9">
-        <v>11.367000000000001</v>
+        <v>38.121000000000002</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J103" s="2">
         <v>72</v>
       </c>
       <c r="K103" s="9">
-        <v>31.901</v>
+        <v>52.271000000000001</v>
       </c>
       <c r="L103" s="9">
-        <v>2.2569825397322969</v>
-      </c>
-      <c r="M103" s="10">
-        <v>509.061894</v>
-      </c>
-      <c r="N103" s="10">
-        <v>304.09381500000001</v>
-      </c>
-      <c r="O103" s="10">
-        <v>204.96811299999999</v>
-      </c>
-      <c r="P103" s="9">
-        <v>171.45177000000001</v>
-      </c>
-      <c r="Q103" s="9">
-        <v>110.238232</v>
-      </c>
-      <c r="R103" s="9">
-        <v>61.213506000000002</v>
+        <v>1.3774368196514319</v>
+      </c>
+      <c r="M103" s="9">
+        <v>167.93623199999999</v>
+      </c>
+      <c r="N103" s="9">
+        <v>97.028190999999993</v>
+      </c>
+      <c r="O103" s="9">
+        <v>70.907809999999998</v>
+      </c>
+      <c r="P103" s="10">
+        <v>268.55290300000001</v>
+      </c>
+      <c r="Q103" s="10">
+        <v>185.45786000000001</v>
+      </c>
+      <c r="R103" s="10">
+        <v>83.095070000000007</v>
       </c>
       <c r="S103" s="9">
-        <v>2.9691259180351417</v>
-      </c>
-      <c r="T103" s="10">
+        <v>0.62533761550885181</v>
+      </c>
+      <c r="T103" s="9">
+        <v>2</v>
+      </c>
+      <c r="U103" s="9">
+        <v>0</v>
+      </c>
+      <c r="V103" s="9">
+        <v>0</v>
+      </c>
+      <c r="W103" s="9">
+        <v>2</v>
+      </c>
+      <c r="X103" s="10">
+        <v>3</v>
+      </c>
+      <c r="Y103" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z103" s="10">
+        <v>2</v>
+      </c>
+      <c r="AA103" s="10">
         <v>6</v>
       </c>
-      <c r="U103" s="10">
-        <v>11</v>
-      </c>
-      <c r="V103" s="10">
-        <v>4</v>
-      </c>
-      <c r="W103" s="9">
-        <v>21</v>
-      </c>
-      <c r="X103" s="9">
+      <c r="AB103" s="9">
         <v>3</v>
       </c>
-      <c r="Y103" s="9">
-        <v>1</v>
-      </c>
-      <c r="Z103" s="9">
-        <v>2</v>
-      </c>
-      <c r="AA103" s="9">
-        <v>6</v>
-      </c>
-      <c r="AB103" s="9">
-        <v>0.2857142857142857</v>
-      </c>
       <c r="AC103" s="11">
-        <f t="shared" ref="AC103:AC106" si="5">(1-MIN(ABS(L103-1),1))+(1-MIN(ABS(S103-1),0.5))+(1-MIN(ABS(AB103-1),0.5))</f>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>1.74790079585742</v>
       </c>
     </row>
     <row r="104" spans="1:29" ht="17">
       <c r="A104" s="2" t="s">
-        <v>208</v>
+        <v>127</v>
       </c>
       <c r="B104" s="2">
-        <v>259</v>
+        <v>4370</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D104" s="2">
-        <v>4370</v>
+        <v>2060</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F104" s="2">
-        <v>74.099999999999994</v>
+        <v>71.3</v>
       </c>
       <c r="G104" s="2">
-        <v>3.4952766531713904</v>
+        <v>28.892005610098177</v>
       </c>
       <c r="H104" s="9">
-        <v>-7.633</v>
+        <v>-6.1219999999999999</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J104" s="2">
         <v>72</v>
       </c>
       <c r="K104" s="9">
-        <v>23.245999999999999</v>
+        <v>30.571999999999999</v>
       </c>
       <c r="L104" s="9">
-        <v>3.0973070635808311</v>
-      </c>
-      <c r="M104" s="10">
-        <v>328.36152499999997</v>
-      </c>
-      <c r="N104" s="10">
-        <v>200.67168100000001</v>
-      </c>
-      <c r="O104" s="10">
-        <v>127.689595</v>
-      </c>
-      <c r="P104" s="9">
+        <v>2.355096166426796</v>
+      </c>
+      <c r="M104" s="9">
         <v>167.93623199999999</v>
       </c>
-      <c r="Q104" s="9">
+      <c r="N104" s="9">
         <v>97.028190999999993</v>
       </c>
-      <c r="R104" s="9">
+      <c r="O104" s="9">
         <v>70.907809999999998</v>
       </c>
+      <c r="P104" s="10">
+        <v>320.9597</v>
+      </c>
+      <c r="Q104" s="10">
+        <v>180.52893700000001</v>
+      </c>
+      <c r="R104" s="10">
+        <v>140.43079800000001</v>
+      </c>
       <c r="S104" s="9">
-        <v>1.95527505345005</v>
-      </c>
-      <c r="T104" s="10">
-        <v>3</v>
-      </c>
-      <c r="U104" s="10">
-        <v>8</v>
-      </c>
-      <c r="V104" s="10">
+        <v>0.52323152096665093</v>
+      </c>
+      <c r="T104" s="9">
+        <v>2</v>
+      </c>
+      <c r="U104" s="9">
+        <v>0</v>
+      </c>
+      <c r="V104" s="9">
+        <v>0</v>
+      </c>
+      <c r="W104" s="9">
+        <v>2</v>
+      </c>
+      <c r="X104" s="10">
+        <v>2</v>
+      </c>
+      <c r="Y104" s="10">
+        <v>14</v>
+      </c>
+      <c r="Z104" s="10">
         <v>1</v>
       </c>
-      <c r="W104" s="9">
-        <v>12</v>
-      </c>
-      <c r="X104" s="9">
-        <v>2</v>
-      </c>
-      <c r="Y104" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z104" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA104" s="9">
-        <v>2</v>
+      <c r="AA104" s="10">
+        <v>17</v>
       </c>
       <c r="AB104" s="9">
-        <v>0.16666666699999999</v>
+        <v>8.5</v>
       </c>
       <c r="AC104" s="11">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:29" ht="17">
-      <c r="A105" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B105" s="2">
-        <v>4370</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D105" s="2">
-        <v>921</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F105" s="2">
-        <v>66.400000000000006</v>
-      </c>
-      <c r="G105" s="2">
-        <v>13.870481927710841</v>
-      </c>
-      <c r="H105" s="9">
-        <v>38.121000000000002</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="J105" s="2">
-        <v>72</v>
-      </c>
-      <c r="K105" s="9">
-        <v>52.271000000000001</v>
-      </c>
-      <c r="L105" s="9">
-        <v>1.3774368196514319</v>
-      </c>
-      <c r="M105" s="9">
-        <v>167.93623199999999</v>
-      </c>
-      <c r="N105" s="9">
-        <v>97.028190999999993</v>
-      </c>
-      <c r="O105" s="9">
-        <v>70.907809999999998</v>
-      </c>
-      <c r="P105" s="10">
-        <v>268.55290300000001</v>
-      </c>
-      <c r="Q105" s="10">
-        <v>185.45786000000001</v>
-      </c>
-      <c r="R105" s="10">
-        <v>83.095070000000007</v>
-      </c>
-      <c r="S105" s="9">
-        <v>0.62533761550885181</v>
-      </c>
-      <c r="T105" s="9">
-        <v>2</v>
-      </c>
-      <c r="U105" s="9">
-        <v>0</v>
-      </c>
-      <c r="V105" s="9">
-        <v>0</v>
-      </c>
-      <c r="W105" s="9">
-        <v>2</v>
-      </c>
-      <c r="X105" s="10">
-        <v>3</v>
-      </c>
-      <c r="Y105" s="10">
-        <v>1</v>
-      </c>
-      <c r="Z105" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA105" s="10">
-        <v>6</v>
-      </c>
-      <c r="AB105" s="9">
-        <v>3</v>
-      </c>
-      <c r="AC105" s="11">
-        <f t="shared" si="5"/>
-        <v>1.74790079585742</v>
-      </c>
-    </row>
-    <row r="106" spans="1:29" ht="17">
-      <c r="A106" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B106" s="2">
-        <v>4370</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D106" s="2">
-        <v>2060</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F106" s="2">
-        <v>71.3</v>
-      </c>
-      <c r="G106" s="2">
-        <v>28.892005610098177</v>
-      </c>
-      <c r="H106" s="9">
-        <v>-6.1219999999999999</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="J106" s="2">
-        <v>72</v>
-      </c>
-      <c r="K106" s="9">
-        <v>30.571999999999999</v>
-      </c>
-      <c r="L106" s="9">
-        <v>2.355096166426796</v>
-      </c>
-      <c r="M106" s="9">
-        <v>167.93623199999999</v>
-      </c>
-      <c r="N106" s="9">
-        <v>97.028190999999993</v>
-      </c>
-      <c r="O106" s="9">
-        <v>70.907809999999998</v>
-      </c>
-      <c r="P106" s="10">
-        <v>320.9597</v>
-      </c>
-      <c r="Q106" s="10">
-        <v>180.52893700000001</v>
-      </c>
-      <c r="R106" s="10">
-        <v>140.43079800000001</v>
-      </c>
-      <c r="S106" s="9">
-        <v>0.52323152096665093</v>
-      </c>
-      <c r="T106" s="9">
-        <v>2</v>
-      </c>
-      <c r="U106" s="9">
-        <v>0</v>
-      </c>
-      <c r="V106" s="9">
-        <v>0</v>
-      </c>
-      <c r="W106" s="9">
-        <v>2</v>
-      </c>
-      <c r="X106" s="10">
-        <v>2</v>
-      </c>
-      <c r="Y106" s="10">
-        <v>14</v>
-      </c>
-      <c r="Z106" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA106" s="10">
-        <v>17</v>
-      </c>
-      <c r="AB106" s="9">
-        <v>8.5</v>
-      </c>
-      <c r="AC106" s="11">
         <f t="shared" si="5"/>
         <v>1.0232315209666509</v>
       </c>

--- a/data/ABLE Dataset.xlsx
+++ b/data/ABLE Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BonoGONG/Desktop/8.Paper_draft/Paper_materials/Version13_full_NC/4.Github_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5FD740-3432-2743-9DD1-28A4D4D320BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EAFED2-E5BE-DF42-87FB-A6C0F5314B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-76800" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{0674E527-E1AB-E348-9FF3-CA6262F7D631}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="237">
   <si>
     <t>7D12–9G8</t>
   </si>
@@ -160,9 +160,6 @@
     <t>BBsR4</t>
   </si>
   <si>
-    <t>BBsR5</t>
-  </si>
-  <si>
     <t>BBsR6</t>
   </si>
   <si>
@@ -405,10 +402,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>n/a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BsS29</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -450,9 +443,6 @@
   </si>
   <si>
     <t>S9R4P2H5</t>
-  </si>
-  <si>
-    <t>S9R3C2</t>
   </si>
   <si>
     <t>S9R3C3</t>
@@ -1279,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25302E3-D780-C043-8AFB-452B651797D6}">
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
@@ -1316,102 +1306,102 @@
   <sheetData>
     <row r="1" spans="1:29" ht="18">
       <c r="A1" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="P1" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="T1" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC1" s="7" t="s">
         <v>236</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="17">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="2">
         <v>10.4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2">
         <v>14.4</v>
@@ -1429,7 +1419,7 @@
         <v>28.285</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J2" s="2">
         <v>36</v>
@@ -1489,19 +1479,19 @@
         <v>0.82608695652173914</v>
       </c>
       <c r="AC2" s="11">
-        <f t="shared" ref="AC2:AC51" si="0">(1-MIN(ABS(L2-1),1))+(1-MIN(ABS(S2-1),0.5))+(1-MIN(ABS(AB2-1),0.5))</f>
+        <f t="shared" ref="AC2:AC50" si="0">(1-MIN(ABS(L2-1),1))+(1-MIN(ABS(S2-1),0.5))+(1-MIN(ABS(AB2-1),0.5))</f>
         <v>2.1542681774571801</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="17">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="2">
         <v>14.4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2">
         <v>10.4</v>
@@ -1519,7 +1509,7 @@
         <v>28.285</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J3" s="2">
         <v>36</v>
@@ -1585,13 +1575,13 @@
     </row>
     <row r="4" spans="1:29" ht="17">
       <c r="A4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" s="2">
         <v>2.6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2">
         <v>16.3</v>
@@ -1609,7 +1599,7 @@
         <v>3.7429999999999999</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J4" s="2">
         <v>54</v>
@@ -1675,13 +1665,13 @@
     </row>
     <row r="5" spans="1:29" ht="17">
       <c r="A5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2">
         <v>2.6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2">
         <v>3.31</v>
@@ -1699,7 +1689,7 @@
         <v>14.116</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J5" s="2">
         <v>54</v>
@@ -1765,13 +1755,13 @@
     </row>
     <row r="6" spans="1:29" ht="17">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" s="2">
         <v>8.6880000000000006</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" s="2">
         <v>2.6309999999999998</v>
@@ -1789,7 +1779,7 @@
         <v>22.439</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J6" s="2">
         <v>121.80500000000001</v>
@@ -1855,13 +1845,13 @@
     </row>
     <row r="7" spans="1:29" ht="17">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="2">
         <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2">
         <v>891</v>
@@ -1879,7 +1869,7 @@
         <v>2.4180000000000001</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J7" s="2">
         <v>72</v>
@@ -1945,13 +1935,13 @@
     </row>
     <row r="8" spans="1:29" ht="17">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
         <v>6.61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" s="2">
         <v>891</v>
@@ -1969,7 +1959,7 @@
         <v>2.859</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J8" s="2">
         <v>72</v>
@@ -2035,13 +2025,13 @@
     </row>
     <row r="9" spans="1:29" ht="17">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2">
         <v>6.61</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" s="2">
         <v>112</v>
@@ -2059,7 +2049,7 @@
         <v>-1.6919999999999999</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J9" s="2">
         <v>72</v>
@@ -2125,13 +2115,13 @@
     </row>
     <row r="10" spans="1:29" ht="17">
       <c r="A10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2">
         <v>0.3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" s="2">
         <v>32.299999999999997</v>
@@ -2149,7 +2139,7 @@
         <v>8.6029999999999998</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J10" s="2">
         <v>72</v>
@@ -2215,13 +2205,13 @@
     </row>
     <row r="11" spans="1:29" ht="17">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2">
         <v>0.3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2">
         <v>3.1</v>
@@ -2239,7 +2229,7 @@
         <v>6.4989999999999997</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J11" s="2">
         <v>72</v>
@@ -2305,13 +2295,13 @@
     </row>
     <row r="12" spans="1:29" ht="17">
       <c r="A12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="2">
         <v>0.3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2">
         <v>18</v>
@@ -2329,7 +2319,7 @@
         <v>20.423999999999999</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J12" s="2">
         <v>72</v>
@@ -2395,13 +2385,13 @@
     </row>
     <row r="13" spans="1:29" ht="17">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2">
         <v>0.3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" s="2">
         <v>27.3</v>
@@ -2419,7 +2409,7 @@
         <v>10.417999999999999</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J13" s="2">
         <v>72</v>
@@ -2485,13 +2475,13 @@
     </row>
     <row r="14" spans="1:29" ht="17">
       <c r="A14" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="2">
         <v>3.85</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" s="2">
         <v>1.45</v>
@@ -2509,7 +2499,7 @@
         <v>33.926000000000002</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J14" s="2">
         <v>36</v>
@@ -2575,13 +2565,13 @@
     </row>
     <row r="15" spans="1:29" ht="17">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2">
         <v>6.02</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D15" s="2">
         <v>55.44</v>
@@ -2599,7 +2589,7 @@
         <v>40.637</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J15" s="2">
         <v>54</v>
@@ -2665,13 +2655,13 @@
     </row>
     <row r="16" spans="1:29" ht="17">
       <c r="A16" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B16" s="2">
         <v>20.52</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D16" s="2">
         <v>55.44</v>
@@ -2689,7 +2679,7 @@
         <v>17.477</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J16" s="2">
         <v>54</v>
@@ -2755,13 +2745,13 @@
     </row>
     <row r="17" spans="1:29" ht="17">
       <c r="A17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" s="2">
         <v>15.194000000000001</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17" s="2">
         <v>5.7539999999999996</v>
@@ -2779,7 +2769,7 @@
         <v>6.7009999999999996</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J17" s="2">
         <v>72</v>
@@ -2845,13 +2835,13 @@
     </row>
     <row r="18" spans="1:29" ht="17">
       <c r="A18" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B18" s="2">
         <v>0.23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" s="2">
         <v>5.0000000000000001E-3</v>
@@ -2869,7 +2859,7 @@
         <v>-2.1539999999999999</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J18" s="2">
         <v>54</v>
@@ -2935,13 +2925,13 @@
     </row>
     <row r="19" spans="1:29" ht="17">
       <c r="A19" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B19" s="2">
         <v>2720</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D19" s="2">
         <v>60.3</v>
@@ -2959,7 +2949,7 @@
         <v>19.088000000000001</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J19" s="2">
         <v>54</v>
@@ -3025,13 +3015,13 @@
     </row>
     <row r="20" spans="1:29" ht="17">
       <c r="A20" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20" s="2">
         <v>429</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="2">
         <v>2720</v>
@@ -3049,7 +3039,7 @@
         <v>19.111999999999998</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J20" s="2">
         <v>54</v>
@@ -3115,13 +3105,13 @@
     </row>
     <row r="21" spans="1:29" ht="17">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B21" s="2">
         <v>429</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" s="2">
         <v>60.3</v>
@@ -3139,7 +3129,7 @@
         <v>-1.4279999999999999</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J21" s="2">
         <v>54</v>
@@ -3205,13 +3195,13 @@
     </row>
     <row r="22" spans="1:29" ht="17">
       <c r="A22" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" s="2">
         <v>429</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D22" s="2">
         <v>38.5</v>
@@ -3229,7 +3219,7 @@
         <v>-1.712</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J22" s="2">
         <v>54</v>
@@ -3295,13 +3285,13 @@
     </row>
     <row r="23" spans="1:29" ht="17">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2">
         <v>38.5</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D23" s="2">
         <v>60.3</v>
@@ -3319,7 +3309,7 @@
         <v>7.02</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J23" s="2">
         <v>54</v>
@@ -3385,13 +3375,13 @@
     </row>
     <row r="24" spans="1:29" ht="17">
       <c r="A24" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="2">
         <v>0.72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" s="2">
         <v>5.0000000000000001E-3</v>
@@ -3409,7 +3399,7 @@
         <v>3.681</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J24" s="2">
         <v>54</v>
@@ -3475,13 +3465,13 @@
     </row>
     <row r="25" spans="1:29" ht="17">
       <c r="A25" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2">
         <v>0.11</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25" s="2">
         <v>0.23</v>
@@ -3499,7 +3489,7 @@
         <v>26.31</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J25" s="2">
         <v>54</v>
@@ -3565,13 +3555,13 @@
     </row>
     <row r="26" spans="1:29" ht="17">
       <c r="A26" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="2">
         <v>0.34100000000000003</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D26" s="2">
         <v>0.35499999999999998</v>
@@ -3589,7 +3579,7 @@
         <v>14.042</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="J26" s="2">
         <v>110.86799999999999</v>
@@ -3655,13 +3645,13 @@
     </row>
     <row r="27" spans="1:29" ht="17">
       <c r="A27" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="2">
         <v>3.86</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D27" s="2">
         <v>4.2</v>
@@ -3679,7 +3669,7 @@
         <v>5.8849999999999998</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J27" s="2">
         <v>54</v>
@@ -3745,13 +3735,13 @@
     </row>
     <row r="28" spans="1:29" ht="17">
       <c r="A28" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="2">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D28" s="2">
         <v>27</v>
@@ -3769,7 +3759,7 @@
         <v>-2.15</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J28" s="2">
         <v>108</v>
@@ -3835,19 +3825,19 @@
     </row>
     <row r="29" spans="1:29" ht="17">
       <c r="A29" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B29" s="3">
         <v>47.1</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D29" s="3">
         <v>85.7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F29" s="3">
         <v>0.56999999999999995</v>
@@ -3859,7 +3849,7 @@
         <v>7.9550000000000001</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J29" s="3">
         <v>22.091000000000001</v>
@@ -3926,13 +3916,13 @@
     </row>
     <row r="30" spans="1:29" ht="17">
       <c r="A30" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B30" s="2">
         <v>1.6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D30" s="2">
         <v>2.2999999999999998</v>
@@ -3950,7 +3940,7 @@
         <v>17.094000000000001</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J30" s="2">
         <v>36</v>
@@ -4016,13 +4006,13 @@
     </row>
     <row r="31" spans="1:29" ht="17">
       <c r="A31" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2">
         <v>1.86</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D31" s="2">
         <v>8.92</v>
@@ -4040,7 +4030,7 @@
         <v>5.0880000000000001</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J31" s="2">
         <v>54</v>
@@ -4106,13 +4096,13 @@
     </row>
     <row r="32" spans="1:29" ht="17">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B32" s="2">
         <v>8.92</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D32" s="2">
         <v>1.86</v>
@@ -4130,7 +4120,7 @@
         <v>5.0880000000000001</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J32" s="2">
         <v>54</v>
@@ -4196,13 +4186,13 @@
     </row>
     <row r="33" spans="1:29" ht="17">
       <c r="A33" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B33" s="2">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D33" s="2">
         <v>0.13</v>
@@ -4220,7 +4210,7 @@
         <v>56.042999999999999</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J33" s="2">
         <v>54</v>
@@ -4286,13 +4276,13 @@
     </row>
     <row r="34" spans="1:29" ht="17">
       <c r="A34" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B34" s="2">
         <v>16.7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D34" s="2">
         <v>70</v>
@@ -4310,7 +4300,7 @@
         <v>16.52</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J34" s="2">
         <v>72</v>
@@ -4376,13 +4366,13 @@
     </row>
     <row r="35" spans="1:29" ht="17">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2">
         <v>867.3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D35" s="2">
         <v>209.8</v>
@@ -4400,7 +4390,7 @@
         <v>-26.19</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J35" s="2">
         <v>72</v>
@@ -4466,13 +4456,13 @@
     </row>
     <row r="36" spans="1:29" ht="17">
       <c r="A36" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B36" s="2">
         <v>867.3</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D36" s="2">
         <v>101.7</v>
@@ -4490,7 +4480,7 @@
         <v>-27.199000000000002</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J36" s="2">
         <v>72</v>
@@ -4556,13 +4546,13 @@
     </row>
     <row r="37" spans="1:29" ht="17">
       <c r="A37" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B37" s="2">
         <v>867.3</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D37" s="2">
         <v>19.100000000000001</v>
@@ -4580,7 +4570,7 @@
         <v>71.206999999999994</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J37" s="2">
         <v>72</v>
@@ -4646,13 +4636,13 @@
     </row>
     <row r="38" spans="1:29" ht="17">
       <c r="A38" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B38" s="2">
         <v>209.8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D38" s="2">
         <v>101.7</v>
@@ -4670,7 +4660,7 @@
         <v>-20.690999999999999</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J38" s="2">
         <v>72</v>
@@ -4736,13 +4726,13 @@
     </row>
     <row r="39" spans="1:29" ht="17">
       <c r="A39" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" s="2">
         <v>209.8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D39" s="2">
         <v>19.100000000000001</v>
@@ -4760,7 +4750,7 @@
         <v>53.537999999999997</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J39" s="2">
         <v>72</v>
@@ -4826,13 +4816,13 @@
     </row>
     <row r="40" spans="1:29" ht="17">
       <c r="A40" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B40" s="2">
         <v>37.300000000000004</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D40" s="2">
         <v>113</v>
@@ -4850,7 +4840,7 @@
         <v>7.7050000000000001</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J40" s="2">
         <v>90</v>
@@ -4916,13 +4906,13 @@
     </row>
     <row r="41" spans="1:29" ht="17">
       <c r="A41" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B41" s="2">
         <v>37.300000000000004</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D41" s="2">
         <v>48.6</v>
@@ -4940,7 +4930,7 @@
         <v>5.0250000000000004</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J41" s="2">
         <v>90</v>
@@ -5006,13 +4996,13 @@
     </row>
     <row r="42" spans="1:29" ht="17">
       <c r="A42" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B42" s="2">
         <v>37.300000000000004</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D42" s="2">
         <v>1480</v>
@@ -5030,7 +5020,7 @@
         <v>6.9109999999999996</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J42" s="2">
         <v>90</v>
@@ -5096,130 +5086,130 @@
     </row>
     <row r="43" spans="1:29" ht="17">
       <c r="A43" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
+      </c>
+      <c r="B43" s="2">
+        <v>113</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D43" s="2">
-        <v>113</v>
+        <v>52.4</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F43" s="2">
-        <v>34</v>
+        <v>32.199999999999996</v>
       </c>
       <c r="G43" s="2">
-        <v>3.3235294117647061</v>
+        <v>1.627329192546584</v>
       </c>
       <c r="H43" s="2">
-        <v>15.272</v>
+        <v>2.2389999999999999</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J43" s="2">
         <v>90</v>
       </c>
       <c r="K43" s="3">
-        <v>43.406999999999996</v>
+        <v>30.295999999999999</v>
       </c>
       <c r="L43" s="2">
-        <v>2.0733982998133942</v>
+        <v>2.9706891998943754</v>
       </c>
       <c r="M43" s="2">
-        <v>268.06335800000005</v>
+        <v>326.98653399999995</v>
       </c>
       <c r="N43" s="2">
-        <v>188.29208800000001</v>
+        <v>186.83260499999997</v>
       </c>
       <c r="O43" s="2">
-        <v>79.771364000000005</v>
+        <v>140.15379000000001</v>
       </c>
       <c r="P43" s="2">
-        <v>326.98653399999995</v>
+        <v>321.742636</v>
       </c>
       <c r="Q43" s="2">
-        <v>186.83260499999997</v>
+        <v>166.35480000000001</v>
       </c>
       <c r="R43" s="2">
-        <v>140.15379000000001</v>
+        <v>155.38779900000003</v>
       </c>
       <c r="S43" s="2">
-        <v>0.81979938048458012</v>
+        <v>1.0162984243095463</v>
       </c>
       <c r="T43" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U43" s="2">
         <v>2</v>
       </c>
       <c r="V43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="2">
         <v>7</v>
       </c>
       <c r="X43" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y43" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AB43" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AC43" s="11">
         <f t="shared" si="0"/>
-        <v>1.81979938048458</v>
+        <v>1.4837015756904537</v>
       </c>
     </row>
     <row r="44" spans="1:29" ht="17">
       <c r="A44" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B44" s="2">
         <v>113</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D44" s="2">
-        <v>52.4</v>
+        <v>462</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F44" s="2">
-        <v>32.199999999999996</v>
+        <v>42.1</v>
       </c>
       <c r="G44" s="2">
-        <v>1.627329192546584</v>
+        <v>2.6840855106888362</v>
       </c>
       <c r="H44" s="2">
-        <v>2.2389999999999999</v>
+        <v>4.0490000000000004</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J44" s="2">
         <v>90</v>
       </c>
       <c r="K44" s="3">
-        <v>30.295999999999999</v>
+        <v>43.642000000000003</v>
       </c>
       <c r="L44" s="2">
-        <v>2.9706891998943754</v>
+        <v>2.0622336281563629</v>
       </c>
       <c r="M44" s="2">
         <v>326.98653399999995</v>
@@ -5231,16 +5221,16 @@
         <v>140.15379000000001</v>
       </c>
       <c r="P44" s="2">
-        <v>321.742636</v>
+        <v>307.24645099999998</v>
       </c>
       <c r="Q44" s="2">
-        <v>166.35480000000001</v>
+        <v>175.95613999999998</v>
       </c>
       <c r="R44" s="2">
-        <v>155.38779900000003</v>
+        <v>131.290188</v>
       </c>
       <c r="S44" s="2">
-        <v>1.0162984243095463</v>
+        <v>1.0642483678355001</v>
       </c>
       <c r="T44" s="2">
         <v>4</v>
@@ -5255,61 +5245,61 @@
         <v>7</v>
       </c>
       <c r="X44" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y44" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z44" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA44" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB44" s="2">
-        <v>0.5</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="AC44" s="11">
         <f t="shared" si="0"/>
-        <v>1.4837015756904537</v>
+        <v>1.4742131706260384</v>
       </c>
     </row>
     <row r="45" spans="1:29" ht="17">
       <c r="A45" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B45" s="2">
         <v>113</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D45" s="2">
-        <v>462</v>
+        <v>114</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F45" s="2">
-        <v>42.1</v>
+        <v>115</v>
       </c>
       <c r="G45" s="2">
-        <v>2.6840855106888362</v>
+        <v>0.9826086956521739</v>
       </c>
       <c r="H45" s="2">
-        <v>4.0490000000000004</v>
+        <v>11.583</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J45" s="2">
         <v>90</v>
       </c>
       <c r="K45" s="3">
-        <v>43.642000000000003</v>
+        <v>15.207000000000001</v>
       </c>
       <c r="L45" s="2">
-        <v>2.0622336281563629</v>
+        <v>5.9183270862102972</v>
       </c>
       <c r="M45" s="2">
         <v>326.98653399999995</v>
@@ -5321,16 +5311,16 @@
         <v>140.15379000000001</v>
       </c>
       <c r="P45" s="2">
-        <v>307.24645099999998</v>
+        <v>321.49026300000003</v>
       </c>
       <c r="Q45" s="2">
-        <v>175.95613999999998</v>
+        <v>171.64188399999998</v>
       </c>
       <c r="R45" s="2">
-        <v>131.290188</v>
+        <v>149.84830299999999</v>
       </c>
       <c r="S45" s="2">
-        <v>1.0642483678355001</v>
+        <v>1.0170962285100371</v>
       </c>
       <c r="T45" s="2">
         <v>4</v>
@@ -5348,58 +5338,58 @@
         <v>4</v>
       </c>
       <c r="Y45" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z45" s="2">
         <v>2</v>
       </c>
       <c r="AA45" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AB45" s="2">
-        <v>0.53846153846153844</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="AC45" s="11">
         <f t="shared" si="0"/>
-        <v>1.4742131706260384</v>
+        <v>1.6192674078535991</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="17">
       <c r="A46" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B46" s="2">
+        <v>131</v>
+      </c>
+      <c r="B46" s="4">
         <v>113</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="2">
-        <v>114</v>
-      </c>
-      <c r="E46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="4">
+        <v>78.5</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F46" s="2">
-        <v>115</v>
+      <c r="F46" s="4">
+        <v>165</v>
       </c>
       <c r="G46" s="2">
-        <v>0.9826086956521739</v>
+        <v>0.47575757575757577</v>
       </c>
       <c r="H46" s="2">
-        <v>11.583</v>
+        <v>21.332000000000001</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J46" s="2">
         <v>90</v>
       </c>
       <c r="K46" s="3">
-        <v>15.207000000000001</v>
+        <v>47.981000000000002</v>
       </c>
       <c r="L46" s="2">
-        <v>5.9183270862102972</v>
+        <v>1.875742481398887</v>
       </c>
       <c r="M46" s="2">
         <v>326.98653399999995</v>
@@ -5411,16 +5401,16 @@
         <v>140.15379000000001</v>
       </c>
       <c r="P46" s="2">
-        <v>321.49026300000003</v>
+        <v>343.01589000000001</v>
       </c>
       <c r="Q46" s="2">
-        <v>171.64188399999998</v>
+        <v>187.35122699999999</v>
       </c>
       <c r="R46" s="2">
-        <v>149.84830299999999</v>
+        <v>155.66504900000001</v>
       </c>
       <c r="S46" s="2">
-        <v>1.0170962285100371</v>
+        <v>0.95326934854242451</v>
       </c>
       <c r="T46" s="2">
         <v>4</v>
@@ -5435,61 +5425,61 @@
         <v>7</v>
       </c>
       <c r="X46" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y46" s="2">
         <v>5</v>
       </c>
       <c r="Z46" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB46" s="2">
-        <v>0.63636363636363635</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="AC46" s="11">
         <f t="shared" si="0"/>
-        <v>1.6192674078535991</v>
+        <v>1.615988405605076</v>
       </c>
     </row>
     <row r="47" spans="1:29" ht="17">
       <c r="A47" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B47" s="4">
+        <v>131</v>
+      </c>
+      <c r="B47" s="2">
         <v>113</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="4">
-        <v>78.5</v>
-      </c>
-      <c r="E47" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="2">
+        <v>1480</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F47" s="4">
-        <v>165</v>
+      <c r="F47" s="2">
+        <v>51.3</v>
       </c>
       <c r="G47" s="2">
-        <v>0.47575757575757577</v>
+        <v>2.202729044834308</v>
       </c>
       <c r="H47" s="2">
-        <v>21.332000000000001</v>
+        <v>7.1079999999999997</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J47" s="2">
         <v>90</v>
       </c>
       <c r="K47" s="3">
-        <v>47.981000000000002</v>
+        <v>51.982999999999997</v>
       </c>
       <c r="L47" s="2">
-        <v>1.875742481398887</v>
+        <v>1.7313352442144547</v>
       </c>
       <c r="M47" s="2">
         <v>326.98653399999995</v>
@@ -5501,16 +5491,16 @@
         <v>140.15379000000001</v>
       </c>
       <c r="P47" s="2">
-        <v>343.01589000000001</v>
+        <v>110.80412099999999</v>
       </c>
       <c r="Q47" s="2">
-        <v>187.35122699999999</v>
+        <v>91.13821999999999</v>
       </c>
       <c r="R47" s="2">
-        <v>155.66504900000001</v>
+        <v>19.665854</v>
       </c>
       <c r="S47" s="2">
-        <v>0.95326934854242451</v>
+        <v>2.9510322454523146</v>
       </c>
       <c r="T47" s="2">
         <v>4</v>
@@ -5525,61 +5515,61 @@
         <v>7</v>
       </c>
       <c r="X47" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y47" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="2">
         <v>0</v>
       </c>
       <c r="AA47" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AB47" s="2">
-        <v>0.53846153846153844</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="AC47" s="11">
         <f t="shared" si="0"/>
-        <v>1.615988405605076</v>
+        <v>1.2686647557855453</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="17">
       <c r="A48" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B48" s="2">
         <v>113</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D48" s="2">
-        <v>1480</v>
+        <v>3000</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F48" s="2">
-        <v>51.3</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="G48" s="2">
-        <v>2.202729044834308</v>
+        <v>1.401985111662531</v>
       </c>
       <c r="H48" s="2">
-        <v>7.1079999999999997</v>
+        <v>6.3029999999999999</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J48" s="2">
         <v>90</v>
       </c>
       <c r="K48" s="3">
-        <v>51.982999999999997</v>
+        <v>48.039000000000001</v>
       </c>
       <c r="L48" s="2">
-        <v>1.7313352442144547</v>
+        <v>1.8734777992880784</v>
       </c>
       <c r="M48" s="2">
         <v>326.98653399999995</v>
@@ -5591,16 +5581,16 @@
         <v>140.15379000000001</v>
       </c>
       <c r="P48" s="2">
-        <v>110.80412099999999</v>
+        <v>258.476448</v>
       </c>
       <c r="Q48" s="2">
-        <v>91.13821999999999</v>
+        <v>157.37730500000006</v>
       </c>
       <c r="R48" s="2">
-        <v>19.665854</v>
+        <v>101.099051</v>
       </c>
       <c r="S48" s="2">
-        <v>2.9510322454523146</v>
+        <v>1.2650534953188459</v>
       </c>
       <c r="T48" s="2">
         <v>4</v>
@@ -5615,124 +5605,124 @@
         <v>7</v>
       </c>
       <c r="X48" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y48" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA48" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB48" s="2">
-        <v>2.3333333333333335</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="AC48" s="11">
         <f t="shared" si="0"/>
-        <v>1.2686647557855453</v>
+        <v>1.6392464831708535</v>
       </c>
     </row>
     <row r="49" spans="1:29" ht="17">
       <c r="A49" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B49" s="2">
-        <v>113</v>
+        <v>52.4</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D49" s="2">
-        <v>3000</v>
+        <v>35.1</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F49" s="2">
-        <v>80.599999999999994</v>
+        <v>59.2</v>
       </c>
       <c r="G49" s="2">
-        <v>1.401985111662531</v>
+        <v>0.59290540540540537</v>
       </c>
       <c r="H49" s="2">
-        <v>6.3029999999999999</v>
+        <v>13.598000000000001</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J49" s="2">
         <v>90</v>
       </c>
       <c r="K49" s="3">
-        <v>48.039000000000001</v>
+        <v>73.688999999999993</v>
       </c>
       <c r="L49" s="2">
-        <v>1.8734777992880784</v>
+        <v>1.221349183731629</v>
       </c>
       <c r="M49" s="2">
-        <v>326.98653399999995</v>
+        <v>321.742636</v>
       </c>
       <c r="N49" s="2">
-        <v>186.83260499999997</v>
+        <v>166.35480000000001</v>
       </c>
       <c r="O49" s="2">
-        <v>140.15379000000001</v>
+        <v>155.38779900000003</v>
       </c>
       <c r="P49" s="2">
-        <v>258.476448</v>
+        <v>221.50471499999998</v>
       </c>
       <c r="Q49" s="2">
-        <v>157.37730500000006</v>
+        <v>118.743904</v>
       </c>
       <c r="R49" s="2">
-        <v>101.099051</v>
+        <v>102.760969</v>
       </c>
       <c r="S49" s="2">
-        <v>1.2650534953188459</v>
+        <v>1.4525317711634267</v>
       </c>
       <c r="T49" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U49" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="X49" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y49" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z49" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA49" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AB49" s="2">
-        <v>0.77777777777777779</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="AC49" s="11">
         <f t="shared" si="0"/>
-        <v>1.6392464831708535</v>
+        <v>2.1594523784382775</v>
       </c>
     </row>
     <row r="50" spans="1:29" ht="17">
       <c r="A50" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B50" s="2">
-        <v>52.4</v>
+        <v>462</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D50" s="2">
         <v>35.1</v>
@@ -5741,34 +5731,34 @@
         <v>46</v>
       </c>
       <c r="F50" s="2">
-        <v>59.2</v>
+        <v>67.2</v>
       </c>
       <c r="G50" s="2">
-        <v>0.59290540540540537</v>
+        <v>0.5223214285714286</v>
       </c>
       <c r="H50" s="2">
-        <v>13.598000000000001</v>
+        <v>-28.074000000000002</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J50" s="2">
         <v>90</v>
       </c>
       <c r="K50" s="3">
-        <v>73.688999999999993</v>
+        <v>33.42</v>
       </c>
       <c r="L50" s="2">
-        <v>1.221349183731629</v>
+        <v>2.6929982046678633</v>
       </c>
       <c r="M50" s="2">
-        <v>321.742636</v>
+        <v>307.24645099999998</v>
       </c>
       <c r="N50" s="2">
-        <v>166.35480000000001</v>
+        <v>175.95613999999998</v>
       </c>
       <c r="O50" s="2">
-        <v>155.38779900000003</v>
+        <v>131.290188</v>
       </c>
       <c r="P50" s="2">
         <v>221.50471499999998</v>
@@ -5780,19 +5770,19 @@
         <v>102.760969</v>
       </c>
       <c r="S50" s="2">
-        <v>1.4525317711634267</v>
+        <v>1.3870876337779086</v>
       </c>
       <c r="T50" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U50" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V50" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W50" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X50" s="2">
         <v>3</v>
@@ -5807,49 +5797,49 @@
         <v>12</v>
       </c>
       <c r="AB50" s="2">
-        <v>1.1666666666666667</v>
+        <v>1.0833333333333333</v>
       </c>
       <c r="AC50" s="11">
         <f t="shared" si="0"/>
-        <v>2.1594523784382775</v>
+        <v>1.5295790328887582</v>
       </c>
     </row>
     <row r="51" spans="1:29" ht="17">
-      <c r="A51" s="4" t="s">
-        <v>136</v>
+      <c r="A51" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="B51" s="2">
         <v>462</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>140</v>
+      <c r="C51" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="D51" s="2">
-        <v>35.1</v>
+        <v>1180</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F51" s="2">
-        <v>67.2</v>
+        <v>99.9</v>
       </c>
       <c r="G51" s="2">
-        <v>0.5223214285714286</v>
+        <v>4.6246246246246248</v>
       </c>
       <c r="H51" s="2">
-        <v>-28.074000000000002</v>
+        <v>-5.2720000000000002</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J51" s="2">
         <v>90</v>
       </c>
       <c r="K51" s="3">
-        <v>33.42</v>
+        <v>56.098999999999997</v>
       </c>
       <c r="L51" s="2">
-        <v>2.6929982046678633</v>
+        <v>1.6043066721331931</v>
       </c>
       <c r="M51" s="2">
         <v>307.24645099999998</v>
@@ -5861,16 +5851,16 @@
         <v>131.290188</v>
       </c>
       <c r="P51" s="2">
-        <v>221.50471499999998</v>
+        <v>307.27678800000001</v>
       </c>
       <c r="Q51" s="2">
-        <v>118.743904</v>
+        <v>171.27784100000002</v>
       </c>
       <c r="R51" s="2">
-        <v>102.760969</v>
+        <v>135.99903099999997</v>
       </c>
       <c r="S51" s="2">
-        <v>1.3870876337779086</v>
+        <v>0.99990127142307916</v>
       </c>
       <c r="T51" s="2">
         <v>4</v>
@@ -5885,61 +5875,61 @@
         <v>13</v>
       </c>
       <c r="X51" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y51" s="2">
         <v>6</v>
       </c>
       <c r="Z51" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA51" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB51" s="2">
-        <v>1.0833333333333333</v>
+        <v>1</v>
       </c>
       <c r="AC51" s="11">
-        <f t="shared" si="0"/>
-        <v>1.5295790328887582</v>
+        <f t="shared" ref="AC51:AC99" si="2">(1-MIN(ABS(L51-1),1))+(1-MIN(ABS(S51-1),0.5))+(1-MIN(ABS(AB51-1),0.5))</f>
+        <v>2.3955945992898862</v>
       </c>
     </row>
     <row r="52" spans="1:29" ht="17">
-      <c r="A52" s="2" t="s">
-        <v>136</v>
+      <c r="A52" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="B52" s="2">
         <v>462</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>141</v>
+      <c r="C52" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="D52" s="2">
-        <v>1180</v>
+        <v>3000</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F52" s="2">
-        <v>99.9</v>
+        <v>27.4</v>
       </c>
       <c r="G52" s="2">
-        <v>4.6246246246246248</v>
+        <v>16.861313868613138</v>
       </c>
       <c r="H52" s="2">
-        <v>-5.2720000000000002</v>
+        <v>13.241</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J52" s="2">
         <v>90</v>
       </c>
       <c r="K52" s="3">
-        <v>56.098999999999997</v>
+        <v>50.314</v>
       </c>
       <c r="L52" s="2">
-        <v>1.6043066721331931</v>
+        <v>1.7887665460905513</v>
       </c>
       <c r="M52" s="2">
         <v>307.24645099999998</v>
@@ -5951,16 +5941,16 @@
         <v>131.290188</v>
       </c>
       <c r="P52" s="2">
-        <v>307.27678800000001</v>
+        <v>258.476448</v>
       </c>
       <c r="Q52" s="2">
-        <v>171.27784100000002</v>
+        <v>157.37730500000006</v>
       </c>
       <c r="R52" s="2">
-        <v>135.99903099999997</v>
+        <v>101.099051</v>
       </c>
       <c r="S52" s="2">
-        <v>0.99990127142307916</v>
+        <v>1.1886825796987119</v>
       </c>
       <c r="T52" s="2">
         <v>4</v>
@@ -5975,118 +5965,118 @@
         <v>13</v>
       </c>
       <c r="X52" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y52" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA52" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AB52" s="2">
-        <v>1</v>
+        <v>1.4444444444444444</v>
       </c>
       <c r="AC52" s="11">
-        <f t="shared" ref="AC52:AC100" si="2">(1-MIN(ABS(L52-1),1))+(1-MIN(ABS(S52-1),0.5))+(1-MIN(ABS(AB52-1),0.5))</f>
-        <v>2.3955945992898862</v>
+        <f t="shared" si="2"/>
+        <v>1.5781064297662923</v>
       </c>
     </row>
     <row r="53" spans="1:29" ht="17">
       <c r="A53" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B53" s="2">
-        <v>462</v>
+        <v>35.1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D53" s="2">
-        <v>3000</v>
+        <v>113</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F53" s="2">
-        <v>27.4</v>
+        <v>56.3</v>
       </c>
       <c r="G53" s="2">
-        <v>16.861313868613138</v>
+        <v>0.62344582593250453</v>
       </c>
       <c r="H53" s="2">
-        <v>13.241</v>
+        <v>8.77</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J53" s="2">
         <v>90</v>
       </c>
       <c r="K53" s="3">
-        <v>50.314</v>
+        <v>34.212000000000003</v>
       </c>
       <c r="L53" s="2">
-        <v>1.7887665460905513</v>
+        <v>2.6306559102069449</v>
       </c>
       <c r="M53" s="2">
-        <v>307.24645099999998</v>
+        <v>221.50471499999998</v>
       </c>
       <c r="N53" s="2">
-        <v>175.95613999999998</v>
+        <v>118.743904</v>
       </c>
       <c r="O53" s="2">
-        <v>131.290188</v>
+        <v>102.760969</v>
       </c>
       <c r="P53" s="2">
-        <v>258.476448</v>
+        <v>326.98653399999995</v>
       </c>
       <c r="Q53" s="2">
-        <v>157.37730500000006</v>
+        <v>186.83260499999997</v>
       </c>
       <c r="R53" s="2">
-        <v>101.099051</v>
+        <v>140.15379000000001</v>
       </c>
       <c r="S53" s="2">
-        <v>1.1886825796987119</v>
+        <v>0.67741234567170283</v>
       </c>
       <c r="T53" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U53" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V53" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X53" s="2">
         <v>4</v>
       </c>
       <c r="Y53" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z53" s="2">
         <v>1</v>
       </c>
       <c r="AA53" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB53" s="2">
-        <v>1.4444444444444444</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="AC53" s="11">
         <f t="shared" si="2"/>
-        <v>1.5781064297662923</v>
+        <v>1.1774123456717027</v>
       </c>
     </row>
     <row r="54" spans="1:29" ht="17">
       <c r="A54" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B54" s="2">
         <v>35.1</v>
@@ -6095,31 +6085,31 @@
         <v>134</v>
       </c>
       <c r="D54" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F54" s="2">
-        <v>56.3</v>
+        <v>11.1</v>
       </c>
       <c r="G54" s="2">
-        <v>0.62344582593250453</v>
+        <v>3.1621621621621623</v>
       </c>
       <c r="H54" s="2">
-        <v>8.77</v>
+        <v>-2.9529999999999998</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J54" s="2">
         <v>90</v>
       </c>
       <c r="K54" s="3">
-        <v>34.212000000000003</v>
+        <v>29.207999999999998</v>
       </c>
       <c r="L54" s="2">
-        <v>2.6306559102069449</v>
+        <v>3.0813475760065736</v>
       </c>
       <c r="M54" s="2">
         <v>221.50471499999998</v>
@@ -6131,16 +6121,16 @@
         <v>102.760969</v>
       </c>
       <c r="P54" s="2">
-        <v>326.98653399999995</v>
+        <v>321.49026300000003</v>
       </c>
       <c r="Q54" s="2">
-        <v>186.83260499999997</v>
+        <v>171.64188399999998</v>
       </c>
       <c r="R54" s="2">
-        <v>140.15379000000001</v>
+        <v>149.84830299999999</v>
       </c>
       <c r="S54" s="2">
-        <v>0.67741234567170283</v>
+        <v>0.68899354192882645</v>
       </c>
       <c r="T54" s="2">
         <v>3</v>
@@ -6158,58 +6148,58 @@
         <v>4</v>
       </c>
       <c r="Y54" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="2">
         <v>2</v>
       </c>
-      <c r="Z54" s="2">
-        <v>1</v>
-      </c>
       <c r="AA54" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AB54" s="2">
-        <v>1.7142857142857142</v>
+        <v>1.0909090909090908</v>
       </c>
       <c r="AC54" s="11">
         <f t="shared" si="2"/>
-        <v>1.1774123456717027</v>
+        <v>1.5980844510197356</v>
       </c>
     </row>
     <row r="55" spans="1:29" ht="17">
       <c r="A55" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B55" s="2">
         <v>35.1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D55" s="2">
-        <v>114</v>
+        <v>48.6</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F55" s="2">
-        <v>11.1</v>
+        <v>7.03</v>
       </c>
       <c r="G55" s="2">
-        <v>3.1621621621621623</v>
+        <v>4.9928876244665714</v>
       </c>
       <c r="H55" s="2">
-        <v>-2.9529999999999998</v>
+        <v>-2.1920000000000002</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J55" s="2">
         <v>90</v>
       </c>
       <c r="K55" s="3">
-        <v>29.207999999999998</v>
+        <v>18.936</v>
       </c>
       <c r="L55" s="2">
-        <v>3.0813475760065736</v>
+        <v>4.752851711026616</v>
       </c>
       <c r="M55" s="2">
         <v>221.50471499999998</v>
@@ -6221,16 +6211,16 @@
         <v>102.760969</v>
       </c>
       <c r="P55" s="2">
-        <v>321.49026300000003</v>
+        <v>263.52982700000001</v>
       </c>
       <c r="Q55" s="2">
-        <v>171.64188399999998</v>
+        <v>113.404679</v>
       </c>
       <c r="R55" s="2">
-        <v>149.84830299999999</v>
+        <v>150.12524500000001</v>
       </c>
       <c r="S55" s="2">
-        <v>0.68899354192882645</v>
+        <v>0.84052996020067194</v>
       </c>
       <c r="T55" s="2">
         <v>3</v>
@@ -6245,151 +6235,151 @@
         <v>12</v>
       </c>
       <c r="X55" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y55" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA55" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AB55" s="2">
-        <v>1.0909090909090908</v>
+        <v>1.5</v>
       </c>
       <c r="AC55" s="11">
         <f t="shared" si="2"/>
-        <v>1.5980844510197356</v>
+        <v>1.3405299602006719</v>
       </c>
     </row>
     <row r="56" spans="1:29" ht="17">
-      <c r="A56" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B56" s="2">
-        <v>35.1</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D56" s="2">
-        <v>48.6</v>
+      <c r="A56" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="5">
+        <v>114</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D56" s="5">
+        <v>52.4</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F56" s="2">
-        <v>7.03</v>
+        <v>140</v>
       </c>
       <c r="G56" s="2">
-        <v>4.9928876244665714</v>
+        <v>0.37428571428571428</v>
       </c>
       <c r="H56" s="2">
-        <v>-2.1920000000000002</v>
+        <v>9.0120000000000005</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J56" s="2">
         <v>90</v>
       </c>
       <c r="K56" s="3">
-        <v>18.936</v>
+        <v>52.933</v>
       </c>
       <c r="L56" s="2">
-        <v>4.752851711026616</v>
+        <v>1.7002625961120661</v>
       </c>
       <c r="M56" s="2">
-        <v>221.50471499999998</v>
+        <v>321.49026300000003</v>
       </c>
       <c r="N56" s="2">
-        <v>118.743904</v>
+        <v>171.64188399999998</v>
       </c>
       <c r="O56" s="2">
-        <v>102.760969</v>
+        <v>149.84830299999999</v>
       </c>
       <c r="P56" s="2">
-        <v>263.52982700000001</v>
+        <v>321.742636</v>
       </c>
       <c r="Q56" s="2">
-        <v>113.404679</v>
+        <v>166.35480000000001</v>
       </c>
       <c r="R56" s="2">
-        <v>150.12524500000001</v>
+        <v>155.38779900000003</v>
       </c>
       <c r="S56" s="2">
-        <v>0.84052996020067194</v>
+        <v>0.99921560597893533</v>
       </c>
       <c r="T56" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U56" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V56" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W56" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X56" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y56" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA56" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AB56" s="2">
-        <v>1.5</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AC56" s="11">
         <f t="shared" si="2"/>
-        <v>1.3405299602006719</v>
+        <v>2.0846672955811547</v>
       </c>
     </row>
     <row r="57" spans="1:29" ht="17">
-      <c r="A57" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B57" s="5">
+      <c r="A57" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="2">
         <v>114</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D57" s="5">
-        <v>52.4</v>
+      <c r="C57" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D57" s="2">
+        <v>106</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F57" s="2">
-        <v>140</v>
+        <v>54.5</v>
       </c>
       <c r="G57" s="2">
-        <v>0.37428571428571428</v>
+        <v>1.9449541284403671</v>
       </c>
       <c r="H57" s="2">
-        <v>9.0120000000000005</v>
+        <v>11.065</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J57" s="2">
         <v>90</v>
       </c>
       <c r="K57" s="3">
-        <v>52.933</v>
+        <v>39.454000000000001</v>
       </c>
       <c r="L57" s="2">
-        <v>1.7002625961120661</v>
+        <v>2.2811375272469205</v>
       </c>
       <c r="M57" s="2">
         <v>321.49026300000003</v>
@@ -6401,16 +6391,16 @@
         <v>149.84830299999999</v>
       </c>
       <c r="P57" s="2">
-        <v>321.742636</v>
+        <v>306.06528300000002</v>
       </c>
       <c r="Q57" s="2">
-        <v>166.35480000000001</v>
+        <v>179.48367700000003</v>
       </c>
       <c r="R57" s="2">
-        <v>155.38779900000003</v>
+        <v>126.58147000000001</v>
       </c>
       <c r="S57" s="2">
-        <v>0.99921560597893533</v>
+        <v>1.050397679373521</v>
       </c>
       <c r="T57" s="2">
         <v>4</v>
@@ -6428,10 +6418,10 @@
         <v>5</v>
       </c>
       <c r="Y57" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" s="2">
         <v>14</v>
@@ -6441,45 +6431,45 @@
       </c>
       <c r="AC57" s="11">
         <f t="shared" si="2"/>
-        <v>2.0846672955811547</v>
+        <v>1.7353166063407648</v>
       </c>
     </row>
     <row r="58" spans="1:29" ht="17">
       <c r="A58" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B58" s="2">
         <v>114</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D58" s="2">
-        <v>106</v>
+        <v>1180</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F58" s="2">
-        <v>54.5</v>
+        <v>0.125</v>
       </c>
       <c r="G58" s="2">
-        <v>1.9449541284403671</v>
+        <v>912</v>
       </c>
       <c r="H58" s="2">
-        <v>11.065</v>
+        <v>-3.0539999999999998</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J58" s="2">
         <v>90</v>
       </c>
       <c r="K58" s="3">
-        <v>39.454000000000001</v>
+        <v>39.755000000000003</v>
       </c>
       <c r="L58" s="2">
-        <v>2.2811375272469205</v>
+        <v>2.2638661803546722</v>
       </c>
       <c r="M58" s="2">
         <v>321.49026300000003</v>
@@ -6491,16 +6481,16 @@
         <v>149.84830299999999</v>
       </c>
       <c r="P58" s="2">
-        <v>306.06528300000002</v>
+        <v>307.27678800000001</v>
       </c>
       <c r="Q58" s="2">
-        <v>179.48367700000003</v>
+        <v>171.27784100000002</v>
       </c>
       <c r="R58" s="2">
-        <v>126.58147000000001</v>
+        <v>135.99903099999997</v>
       </c>
       <c r="S58" s="2">
-        <v>1.050397679373521</v>
+        <v>1.0462562600075083</v>
       </c>
       <c r="T58" s="2">
         <v>4</v>
@@ -6515,61 +6505,61 @@
         <v>11</v>
       </c>
       <c r="X58" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y58" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB58" s="2">
-        <v>0.7857142857142857</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="AC58" s="11">
         <f t="shared" si="2"/>
-        <v>1.7353166063407648</v>
+        <v>1.7998975861463378</v>
       </c>
     </row>
     <row r="59" spans="1:29" ht="17">
       <c r="A59" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B59" s="2">
         <v>114</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D59" s="2">
-        <v>1180</v>
+        <v>3000</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>55</v>
       </c>
       <c r="F59" s="2">
-        <v>0.125</v>
+        <v>0.253</v>
       </c>
       <c r="G59" s="2">
-        <v>912</v>
+        <v>450.59288537549406</v>
       </c>
       <c r="H59" s="2">
-        <v>-3.0539999999999998</v>
+        <v>12.696</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J59" s="2">
         <v>90</v>
       </c>
       <c r="K59" s="3">
-        <v>39.755000000000003</v>
+        <v>45.518999999999998</v>
       </c>
       <c r="L59" s="2">
-        <v>2.2638661803546722</v>
+        <v>1.9771963355961248</v>
       </c>
       <c r="M59" s="2">
         <v>321.49026300000003</v>
@@ -6581,16 +6571,16 @@
         <v>149.84830299999999</v>
       </c>
       <c r="P59" s="2">
-        <v>307.27678800000001</v>
+        <v>258.476448</v>
       </c>
       <c r="Q59" s="2">
-        <v>171.27784100000002</v>
+        <v>157.37730500000006</v>
       </c>
       <c r="R59" s="2">
-        <v>135.99903099999997</v>
+        <v>101.099051</v>
       </c>
       <c r="S59" s="2">
-        <v>1.0462562600075083</v>
+        <v>1.2437893877278909</v>
       </c>
       <c r="T59" s="2">
         <v>4</v>
@@ -6605,151 +6595,151 @@
         <v>11</v>
       </c>
       <c r="X59" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y59" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA59" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AB59" s="2">
-        <v>0.84615384615384615</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="AC59" s="11">
         <f t="shared" si="2"/>
-        <v>1.7998975861463378</v>
+        <v>1.5567920544537619</v>
       </c>
     </row>
     <row r="60" spans="1:29" ht="17">
       <c r="A60" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B60" s="2">
-        <v>114</v>
+        <v>48.6</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D60" s="2">
-        <v>3000</v>
+        <v>1180</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F60" s="2">
-        <v>0.253</v>
+        <v>12.2</v>
       </c>
       <c r="G60" s="2">
-        <v>450.59288537549406</v>
+        <v>3.9836065573770494</v>
       </c>
       <c r="H60" s="2">
-        <v>12.696</v>
+        <v>20.206</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J60" s="2">
         <v>90</v>
       </c>
       <c r="K60" s="3">
-        <v>45.518999999999998</v>
+        <v>53.387</v>
       </c>
       <c r="L60" s="2">
-        <v>1.9771963355961248</v>
+        <v>1.6858036600670576</v>
       </c>
       <c r="M60" s="2">
-        <v>321.49026300000003</v>
+        <v>263.52982700000001</v>
       </c>
       <c r="N60" s="2">
-        <v>171.64188399999998</v>
+        <v>113.404679</v>
       </c>
       <c r="O60" s="2">
-        <v>149.84830299999999</v>
+        <v>150.12524500000001</v>
       </c>
       <c r="P60" s="2">
-        <v>258.476448</v>
+        <v>307.27678800000001</v>
       </c>
       <c r="Q60" s="2">
-        <v>157.37730500000006</v>
+        <v>171.27784100000002</v>
       </c>
       <c r="R60" s="2">
-        <v>101.099051</v>
+        <v>135.99903099999997</v>
       </c>
       <c r="S60" s="2">
-        <v>1.2437893877278909</v>
+        <v>0.85763011490474184</v>
       </c>
       <c r="T60" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U60" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V60" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W60" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="X60" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y60" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA60" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB60" s="2">
-        <v>1.2222222222222223</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="AC60" s="11">
         <f t="shared" si="2"/>
-        <v>1.5567920544537619</v>
+        <v>1.7872110702222996</v>
       </c>
     </row>
     <row r="61" spans="1:29" ht="17">
       <c r="A61" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B61" s="2">
         <v>48.6</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D61" s="2">
-        <v>1180</v>
+        <v>3000</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>57</v>
       </c>
       <c r="F61" s="2">
-        <v>12.2</v>
+        <v>216</v>
       </c>
       <c r="G61" s="2">
-        <v>3.9836065573770494</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="H61" s="2">
-        <v>20.206</v>
+        <v>-2.3959999999999999</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J61" s="2">
         <v>90</v>
       </c>
       <c r="K61" s="3">
-        <v>53.387</v>
+        <v>37.292999999999999</v>
       </c>
       <c r="L61" s="2">
-        <v>1.6858036600670576</v>
+        <v>2.4133215348724963</v>
       </c>
       <c r="M61" s="2">
         <v>263.52982700000001</v>
@@ -6761,16 +6751,16 @@
         <v>150.12524500000001</v>
       </c>
       <c r="P61" s="2">
-        <v>307.27678800000001</v>
+        <v>258.476448</v>
       </c>
       <c r="Q61" s="2">
-        <v>171.27784100000002</v>
+        <v>157.37730500000006</v>
       </c>
       <c r="R61" s="2">
-        <v>135.99903099999997</v>
+        <v>101.099051</v>
       </c>
       <c r="S61" s="2">
-        <v>0.85763011490474184</v>
+        <v>1.0195506361956816</v>
       </c>
       <c r="T61" s="2">
         <v>1</v>
@@ -6785,241 +6775,241 @@
         <v>8</v>
       </c>
       <c r="X61" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y61" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA61" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AB61" s="2">
-        <v>0.61538461538461542</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="AC61" s="11">
         <f t="shared" si="2"/>
-        <v>1.7872110702222996</v>
+        <v>1.8693382526932072</v>
       </c>
     </row>
     <row r="62" spans="1:29" ht="17">
       <c r="A62" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B62" s="2">
-        <v>48.6</v>
+        <v>1180</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D62" s="2">
-        <v>3000</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F62" s="2">
-        <v>216</v>
+        <v>123</v>
       </c>
       <c r="G62" s="2">
-        <v>0.22500000000000001</v>
+        <v>0.91869918699186992</v>
       </c>
       <c r="H62" s="2">
-        <v>-2.3959999999999999</v>
+        <v>18.169</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J62" s="2">
         <v>90</v>
       </c>
       <c r="K62" s="3">
-        <v>37.292999999999999</v>
+        <v>47.44</v>
       </c>
       <c r="L62" s="2">
-        <v>2.4133215348724963</v>
+        <v>1.897133220910624</v>
       </c>
       <c r="M62" s="2">
-        <v>263.52982700000001</v>
+        <v>307.27678800000001</v>
       </c>
       <c r="N62" s="2">
-        <v>113.404679</v>
+        <v>171.27784100000002</v>
       </c>
       <c r="O62" s="2">
-        <v>150.12524500000001</v>
+        <v>135.99903099999997</v>
       </c>
       <c r="P62" s="2">
-        <v>258.476448</v>
+        <v>326.98653399999995</v>
       </c>
       <c r="Q62" s="2">
-        <v>157.37730500000006</v>
+        <v>186.83260499999997</v>
       </c>
       <c r="R62" s="2">
-        <v>101.099051</v>
+        <v>140.15379000000001</v>
       </c>
       <c r="S62" s="2">
-        <v>1.0195506361956816</v>
+        <v>0.93972306517062887</v>
       </c>
       <c r="T62" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U62" s="2">
         <v>6</v>
       </c>
       <c r="V62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W62" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="X62" s="2">
         <v>4</v>
       </c>
       <c r="Y62" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z62" s="2">
         <v>1</v>
       </c>
       <c r="AA62" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB62" s="2">
-        <v>0.88888888888888884</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="AC62" s="11">
         <f t="shared" si="2"/>
-        <v>1.8693382526932072</v>
+        <v>1.542589844260005</v>
       </c>
     </row>
     <row r="63" spans="1:29" ht="17">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B63" s="2">
-        <v>1180</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="D63" s="2">
-        <v>113</v>
+        <v>99.5</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>59</v>
       </c>
       <c r="F63" s="2">
-        <v>123</v>
+        <v>2.91</v>
       </c>
       <c r="G63" s="2">
-        <v>0.91869918699186992</v>
+        <v>34.192439862542955</v>
       </c>
       <c r="H63" s="2">
-        <v>18.169</v>
+        <v>6.0439999999999996</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J63" s="2">
         <v>90</v>
       </c>
       <c r="K63" s="3">
-        <v>47.44</v>
+        <v>46.444000000000003</v>
       </c>
       <c r="L63" s="2">
-        <v>1.897133220910624</v>
+        <v>1.9378175867711651</v>
       </c>
       <c r="M63" s="2">
-        <v>307.27678800000001</v>
+        <v>401.78200400000003</v>
       </c>
       <c r="N63" s="2">
-        <v>171.27784100000002</v>
+        <v>220.08053999999998</v>
       </c>
       <c r="O63" s="2">
-        <v>135.99903099999997</v>
+        <v>181.70129399999999</v>
       </c>
       <c r="P63" s="2">
-        <v>326.98653399999995</v>
+        <v>355.54163900000003</v>
       </c>
       <c r="Q63" s="2">
-        <v>186.83260499999997</v>
+        <v>93.098927000000018</v>
       </c>
       <c r="R63" s="2">
-        <v>140.15379000000001</v>
+        <v>262.44285100000008</v>
       </c>
       <c r="S63" s="2">
-        <v>0.93972306517062887</v>
+        <v>1.130056116999562</v>
       </c>
       <c r="T63" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U63" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V63" s="2">
         <v>0</v>
       </c>
       <c r="W63" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X63" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y63" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA63" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AB63" s="2">
-        <v>1.8571428571428572</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="AC63" s="11">
         <f t="shared" si="2"/>
-        <v>1.542589844260005</v>
+        <v>1.7556557079939787</v>
       </c>
     </row>
     <row r="64" spans="1:29" ht="17">
       <c r="A64" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B64" s="2">
         <v>138</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D64" s="2">
-        <v>99.5</v>
+        <v>212</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>60</v>
       </c>
       <c r="F64" s="2">
-        <v>2.91</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="G64" s="2">
-        <v>34.192439862542955</v>
+        <v>174.24242424242422</v>
       </c>
       <c r="H64" s="2">
-        <v>6.0439999999999996</v>
+        <v>-3.5390000000000001</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J64" s="2">
         <v>90</v>
       </c>
       <c r="K64" s="3">
-        <v>46.444000000000003</v>
+        <v>55.52</v>
       </c>
       <c r="L64" s="2">
-        <v>1.9378175867711651</v>
+        <v>1.6210374639769451</v>
       </c>
       <c r="M64" s="2">
         <v>401.78200400000003</v>
@@ -7031,16 +7021,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P64" s="2">
-        <v>355.54163900000003</v>
+        <v>365.21654600000005</v>
       </c>
       <c r="Q64" s="2">
-        <v>93.098927000000018</v>
+        <v>128.86028300000001</v>
       </c>
       <c r="R64" s="2">
-        <v>262.44285100000008</v>
+        <v>236.35607899999999</v>
       </c>
       <c r="S64" s="2">
-        <v>1.130056116999562</v>
+        <v>1.100119938158552</v>
       </c>
       <c r="T64" s="2">
         <v>12</v>
@@ -7058,58 +7048,58 @@
         <v>5</v>
       </c>
       <c r="Y64" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z64" s="2">
         <v>0</v>
       </c>
       <c r="AA64" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AB64" s="2">
-        <v>0.82352941176470584</v>
+        <v>0.70588235294117652</v>
       </c>
       <c r="AC64" s="11">
         <f t="shared" si="2"/>
-        <v>1.7556557079939787</v>
+        <v>1.9847249508056795</v>
       </c>
     </row>
     <row r="65" spans="1:29" ht="17">
       <c r="A65" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B65" s="2">
         <v>138</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D65" s="2">
-        <v>212</v>
+        <v>26.9</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F65" s="2">
-        <v>0.79200000000000004</v>
+        <v>0.72199999999999998</v>
       </c>
       <c r="G65" s="2">
-        <v>174.24242424242422</v>
+        <v>37.257617728531855</v>
       </c>
       <c r="H65" s="2">
-        <v>-3.5390000000000001</v>
+        <v>5.7229999999999999</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J65" s="2">
         <v>90</v>
       </c>
       <c r="K65" s="3">
-        <v>55.52</v>
+        <v>46.881</v>
       </c>
       <c r="L65" s="2">
-        <v>1.6210374639769451</v>
+        <v>1.9197542714532541</v>
       </c>
       <c r="M65" s="2">
         <v>401.78200400000003</v>
@@ -7121,16 +7111,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P65" s="2">
-        <v>365.21654600000005</v>
+        <v>361.04667599999999</v>
       </c>
       <c r="Q65" s="2">
-        <v>128.86028300000001</v>
+        <v>122.77821399999999</v>
       </c>
       <c r="R65" s="2">
-        <v>236.35607899999999</v>
+        <v>238.26829699999999</v>
       </c>
       <c r="S65" s="2">
-        <v>1.100119938158552</v>
+        <v>1.1128256558163134</v>
       </c>
       <c r="T65" s="2">
         <v>12</v>
@@ -7145,10 +7135,10 @@
         <v>17</v>
       </c>
       <c r="X65" s="2">
+        <v>7</v>
+      </c>
+      <c r="Y65" s="2">
         <v>5</v>
-      </c>
-      <c r="Y65" s="2">
-        <v>7</v>
       </c>
       <c r="Z65" s="2">
         <v>0</v>
@@ -7161,45 +7151,45 @@
       </c>
       <c r="AC65" s="11">
         <f t="shared" si="2"/>
-        <v>1.9847249508056795</v>
+        <v>1.6733024256716091</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="17">
       <c r="A66" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B66" s="2">
         <v>138</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D66" s="2">
-        <v>26.9</v>
+        <v>69.300000000000011</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>62</v>
       </c>
       <c r="F66" s="2">
-        <v>0.72199999999999998</v>
+        <v>100</v>
       </c>
       <c r="G66" s="2">
-        <v>37.257617728531855</v>
+        <v>0.69300000000000006</v>
       </c>
       <c r="H66" s="2">
-        <v>5.7229999999999999</v>
+        <v>3.3159999999999998</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J66" s="2">
         <v>90</v>
       </c>
       <c r="K66" s="3">
-        <v>46.881</v>
+        <v>57.631</v>
       </c>
       <c r="L66" s="2">
-        <v>1.9197542714532541</v>
+        <v>1.5616595235203277</v>
       </c>
       <c r="M66" s="2">
         <v>401.78200400000003</v>
@@ -7211,16 +7201,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P66" s="2">
-        <v>361.04667599999999</v>
+        <v>451.19195999999999</v>
       </c>
       <c r="Q66" s="2">
-        <v>122.77821399999999</v>
+        <v>138.02437800000001</v>
       </c>
       <c r="R66" s="2">
-        <v>238.26829699999999</v>
+        <v>313.16749299999992</v>
       </c>
       <c r="S66" s="2">
-        <v>1.1128256558163134</v>
+        <v>0.89049016742230969</v>
       </c>
       <c r="T66" s="2">
         <v>12</v>
@@ -7251,45 +7241,45 @@
       </c>
       <c r="AC66" s="11">
         <f t="shared" si="2"/>
-        <v>1.6733024256716091</v>
+        <v>2.0347129968431585</v>
       </c>
     </row>
     <row r="67" spans="1:29" ht="17">
       <c r="A67" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B67" s="2">
         <v>138</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D67" s="2">
-        <v>69.300000000000011</v>
+        <v>413</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>63</v>
       </c>
       <c r="F67" s="2">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="G67" s="2">
-        <v>0.69300000000000006</v>
+        <v>0.83636363636363631</v>
       </c>
       <c r="H67" s="2">
-        <v>3.3159999999999998</v>
+        <v>7.0330000000000004</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J67" s="2">
         <v>90</v>
       </c>
       <c r="K67" s="3">
-        <v>57.631</v>
+        <v>47.951000000000001</v>
       </c>
       <c r="L67" s="2">
-        <v>1.5616595235203277</v>
+        <v>1.8769160184354863</v>
       </c>
       <c r="M67" s="2">
         <v>401.78200400000003</v>
@@ -7301,16 +7291,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P67" s="2">
-        <v>451.19195999999999</v>
+        <v>460.04647499999993</v>
       </c>
       <c r="Q67" s="2">
-        <v>138.02437800000001</v>
+        <v>113.94948100000002</v>
       </c>
       <c r="R67" s="2">
-        <v>313.16749299999992</v>
+        <v>346.09716400000002</v>
       </c>
       <c r="S67" s="2">
-        <v>0.89049016742230969</v>
+        <v>0.87335090221047795</v>
       </c>
       <c r="T67" s="2">
         <v>12</v>
@@ -7325,61 +7315,61 @@
         <v>17</v>
       </c>
       <c r="X67" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y67" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z67" s="2">
         <v>0</v>
       </c>
       <c r="AA67" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AB67" s="2">
-        <v>0.70588235294117652</v>
+        <v>1</v>
       </c>
       <c r="AC67" s="11">
         <f t="shared" si="2"/>
-        <v>2.0347129968431585</v>
+        <v>1.9964348837749917</v>
       </c>
     </row>
     <row r="68" spans="1:29" ht="17">
       <c r="A68" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B68" s="2">
         <v>138</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D68" s="2">
-        <v>413</v>
+        <v>1470</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>64</v>
       </c>
       <c r="F68" s="2">
-        <v>165</v>
+        <v>52.7</v>
       </c>
       <c r="G68" s="2">
-        <v>0.83636363636363631</v>
+        <v>2.618595825426945</v>
       </c>
       <c r="H68" s="2">
-        <v>7.0330000000000004</v>
+        <v>10.057</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J68" s="2">
         <v>90</v>
       </c>
       <c r="K68" s="3">
-        <v>47.951000000000001</v>
+        <v>37.786000000000001</v>
       </c>
       <c r="L68" s="2">
-        <v>1.8769160184354863</v>
+        <v>2.3818345418938232</v>
       </c>
       <c r="M68" s="2">
         <v>401.78200400000003</v>
@@ -7391,16 +7381,16 @@
         <v>181.70129399999999</v>
       </c>
       <c r="P68" s="2">
-        <v>460.04647499999993</v>
+        <v>479.61241899999999</v>
       </c>
       <c r="Q68" s="2">
-        <v>113.94948100000002</v>
+        <v>138.09142900000001</v>
       </c>
       <c r="R68" s="2">
-        <v>346.09716400000002</v>
+        <v>341.52099600000003</v>
       </c>
       <c r="S68" s="2">
-        <v>0.87335090221047795</v>
+        <v>0.83772226923923765</v>
       </c>
       <c r="T68" s="2">
         <v>12</v>
@@ -7415,34 +7405,34 @@
         <v>17</v>
       </c>
       <c r="X68" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y68" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z68" s="2">
         <v>0</v>
       </c>
       <c r="AA68" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AB68" s="2">
-        <v>1</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AC68" s="11">
         <f t="shared" si="2"/>
-        <v>1.9964348837749917</v>
+        <v>1.4847810927686496</v>
       </c>
     </row>
     <row r="69" spans="1:29" ht="17">
       <c r="A69" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B69" s="2">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D69" s="2">
         <v>1470</v>
@@ -7451,34 +7441,34 @@
         <v>65</v>
       </c>
       <c r="F69" s="2">
-        <v>52.7</v>
+        <v>7.13</v>
       </c>
       <c r="G69" s="2">
-        <v>2.618595825426945</v>
+        <v>30.855539971949508</v>
       </c>
       <c r="H69" s="2">
-        <v>10.057</v>
+        <v>31.024000000000001</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J69" s="2">
         <v>90</v>
       </c>
       <c r="K69" s="3">
-        <v>37.786000000000001</v>
+        <v>55.347999999999999</v>
       </c>
       <c r="L69" s="2">
-        <v>2.3818345418938232</v>
+        <v>1.6260750162607502</v>
       </c>
       <c r="M69" s="2">
-        <v>401.78200400000003</v>
+        <v>489.53467200000006</v>
       </c>
       <c r="N69" s="2">
-        <v>220.08053999999998</v>
+        <v>159.10767099999998</v>
       </c>
       <c r="O69" s="2">
-        <v>181.70129399999999</v>
+        <v>330.42694800000004</v>
       </c>
       <c r="P69" s="2">
         <v>479.61241899999999</v>
@@ -7490,19 +7480,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S69" s="2">
-        <v>0.83772226923923765</v>
+        <v>1.0206880652104215</v>
       </c>
       <c r="T69" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U69" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V69" s="2">
         <v>0</v>
       </c>
       <c r="W69" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X69" s="2">
         <v>8</v>
@@ -7517,22 +7507,22 @@
         <v>11</v>
       </c>
       <c r="AB69" s="2">
-        <v>0.6470588235294118</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AC69" s="11">
         <f t="shared" si="2"/>
-        <v>1.4847810927686496</v>
+        <v>2.138951204243114</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="17">
       <c r="A70" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B70" s="2">
-        <v>220</v>
+        <v>702</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D70" s="2">
         <v>1470</v>
@@ -7541,34 +7531,34 @@
         <v>66</v>
       </c>
       <c r="F70" s="2">
-        <v>7.13</v>
+        <v>546</v>
       </c>
       <c r="G70" s="2">
-        <v>30.855539971949508</v>
+        <v>1.2857142857142858</v>
       </c>
       <c r="H70" s="2">
-        <v>31.024000000000001</v>
+        <v>25.725000000000001</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J70" s="2">
         <v>90</v>
       </c>
       <c r="K70" s="3">
-        <v>55.347999999999999</v>
+        <v>46.280999999999999</v>
       </c>
       <c r="L70" s="2">
-        <v>1.6260750162607502</v>
+        <v>1.9446425098852662</v>
       </c>
       <c r="M70" s="2">
-        <v>489.53467200000006</v>
+        <v>489.48157500000002</v>
       </c>
       <c r="N70" s="2">
-        <v>159.10767099999998</v>
+        <v>125.21337999999999</v>
       </c>
       <c r="O70" s="2">
-        <v>330.42694800000004</v>
+        <v>364.26828999999998</v>
       </c>
       <c r="P70" s="2">
         <v>479.61241899999999</v>
@@ -7580,19 +7570,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S70" s="2">
-        <v>1.0206880652104215</v>
+        <v>1.0205773570679788</v>
       </c>
       <c r="T70" s="2">
         <v>7</v>
       </c>
       <c r="U70" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X70" s="2">
         <v>8</v>
@@ -7607,22 +7597,22 @@
         <v>11</v>
       </c>
       <c r="AB70" s="2">
-        <v>0.7857142857142857</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="AC70" s="11">
         <f t="shared" si="2"/>
-        <v>2.138951204243114</v>
+        <v>1.8809339792006012</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="17">
       <c r="A71" s="2" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B71" s="2">
-        <v>702</v>
+        <v>99.5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D71" s="2">
         <v>1470</v>
@@ -7631,34 +7621,34 @@
         <v>67</v>
       </c>
       <c r="F71" s="2">
-        <v>546</v>
+        <v>688</v>
       </c>
       <c r="G71" s="2">
-        <v>1.2857142857142858</v>
+        <v>0.14462209302325582</v>
       </c>
       <c r="H71" s="2">
-        <v>25.725000000000001</v>
+        <v>27.274000000000001</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J71" s="2">
         <v>90</v>
       </c>
       <c r="K71" s="3">
-        <v>46.280999999999999</v>
+        <v>64.635000000000005</v>
       </c>
       <c r="L71" s="2">
-        <v>1.9446425098852662</v>
+        <v>1.392434439545138</v>
       </c>
       <c r="M71" s="2">
-        <v>489.48157500000002</v>
+        <v>355.54163900000003</v>
       </c>
       <c r="N71" s="2">
-        <v>125.21337999999999</v>
+        <v>93.098927000000018</v>
       </c>
       <c r="O71" s="2">
-        <v>364.26828999999998</v>
+        <v>262.44285100000008</v>
       </c>
       <c r="P71" s="2">
         <v>479.61241899999999</v>
@@ -7670,19 +7660,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S71" s="2">
-        <v>1.0205773570679788</v>
+        <v>0.74131032666191243</v>
       </c>
       <c r="T71" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U71" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W71" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X71" s="2">
         <v>8</v>
@@ -7697,22 +7687,22 @@
         <v>11</v>
       </c>
       <c r="AB71" s="2">
-        <v>0.84615384615384615</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AC71" s="11">
         <f t="shared" si="2"/>
-        <v>1.8809339792006012</v>
+        <v>2.1345901728310599</v>
       </c>
     </row>
     <row r="72" spans="1:29" ht="17">
       <c r="A72" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B72" s="2">
-        <v>99.5</v>
+        <v>26.9</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D72" s="2">
         <v>1470</v>
@@ -7721,34 +7711,34 @@
         <v>68</v>
       </c>
       <c r="F72" s="2">
-        <v>688</v>
+        <v>115</v>
       </c>
       <c r="G72" s="2">
-        <v>0.14462209302325582</v>
+        <v>0.23391304347826086</v>
       </c>
       <c r="H72" s="2">
-        <v>27.274000000000001</v>
+        <v>25.725000000000001</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J72" s="2">
         <v>90</v>
       </c>
       <c r="K72" s="3">
-        <v>64.635000000000005</v>
+        <v>55.18</v>
       </c>
       <c r="L72" s="2">
-        <v>1.392434439545138</v>
+        <v>1.6310257339615803</v>
       </c>
       <c r="M72" s="2">
-        <v>355.54163900000003</v>
+        <v>361.04667599999999</v>
       </c>
       <c r="N72" s="2">
-        <v>93.098927000000018</v>
+        <v>122.77821399999999</v>
       </c>
       <c r="O72" s="2">
-        <v>262.44285100000008</v>
+        <v>238.26829699999999</v>
       </c>
       <c r="P72" s="2">
         <v>479.61241899999999</v>
@@ -7760,19 +7750,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S72" s="2">
-        <v>0.74131032666191243</v>
+        <v>0.75278842185277106</v>
       </c>
       <c r="T72" s="2">
+        <v>7</v>
+      </c>
+      <c r="U72" s="2">
         <v>5</v>
       </c>
-      <c r="U72" s="2">
-        <v>9</v>
-      </c>
       <c r="V72" s="2">
         <v>0</v>
       </c>
       <c r="W72" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X72" s="2">
         <v>8</v>
@@ -7787,22 +7777,22 @@
         <v>11</v>
       </c>
       <c r="AB72" s="2">
-        <v>0.7857142857142857</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="AC72" s="11">
         <f t="shared" si="2"/>
-        <v>2.1345901728310599</v>
+        <v>2.0384293545578571</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="17">
       <c r="A73" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B73" s="2">
-        <v>26.9</v>
+        <v>69.300000000000011</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D73" s="2">
         <v>1470</v>
@@ -7811,34 +7801,34 @@
         <v>69</v>
       </c>
       <c r="F73" s="2">
-        <v>115</v>
+        <v>7.19</v>
       </c>
       <c r="G73" s="2">
-        <v>0.23391304347826086</v>
+        <v>9.6383866481223937</v>
       </c>
       <c r="H73" s="2">
-        <v>25.725000000000001</v>
+        <v>20.786999999999999</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J73" s="2">
         <v>90</v>
       </c>
       <c r="K73" s="3">
-        <v>55.18</v>
+        <v>67.56</v>
       </c>
       <c r="L73" s="2">
-        <v>1.6310257339615803</v>
+        <v>1.3321492007104796</v>
       </c>
       <c r="M73" s="2">
-        <v>361.04667599999999</v>
+        <v>451.19195999999999</v>
       </c>
       <c r="N73" s="2">
-        <v>122.77821399999999</v>
+        <v>138.02437800000001</v>
       </c>
       <c r="O73" s="2">
-        <v>238.26829699999999</v>
+        <v>313.16749299999992</v>
       </c>
       <c r="P73" s="2">
         <v>479.61241899999999</v>
@@ -7850,7 +7840,7 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S73" s="2">
-        <v>0.75278842185277106</v>
+        <v>0.94074286262383044</v>
       </c>
       <c r="T73" s="2">
         <v>7</v>
@@ -7881,18 +7871,18 @@
       </c>
       <c r="AC73" s="11">
         <f t="shared" si="2"/>
-        <v>2.0384293545578571</v>
+        <v>2.5252603285800173</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="17">
       <c r="A74" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B74" s="2">
-        <v>69.300000000000011</v>
+        <v>698</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D74" s="2">
         <v>1470</v>
@@ -7901,34 +7891,34 @@
         <v>70</v>
       </c>
       <c r="F74" s="2">
-        <v>7.19</v>
+        <v>198</v>
       </c>
       <c r="G74" s="2">
-        <v>9.6383866481223937</v>
+        <v>3.5252525252525251</v>
       </c>
       <c r="H74" s="2">
-        <v>20.786999999999999</v>
+        <v>23.596</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J74" s="2">
         <v>90</v>
       </c>
       <c r="K74" s="3">
-        <v>67.56</v>
+        <v>44.731999999999999</v>
       </c>
       <c r="L74" s="2">
-        <v>1.3321492007104796</v>
+        <v>2.0119824733971208</v>
       </c>
       <c r="M74" s="2">
-        <v>451.19195999999999</v>
+        <v>528.88547800000015</v>
       </c>
       <c r="N74" s="2">
-        <v>138.02437800000001</v>
+        <v>156.73678100000001</v>
       </c>
       <c r="O74" s="2">
-        <v>313.16749299999992</v>
+        <v>372.14883200000003</v>
       </c>
       <c r="P74" s="2">
         <v>479.61241899999999</v>
@@ -7940,19 +7930,19 @@
         <v>341.52099600000003</v>
       </c>
       <c r="S74" s="2">
-        <v>0.94074286262383044</v>
+        <v>1.1027351608257669</v>
       </c>
       <c r="T74" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U74" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V74" s="2">
         <v>0</v>
       </c>
       <c r="W74" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X74" s="2">
         <v>8</v>
@@ -7967,101 +7957,101 @@
         <v>11</v>
       </c>
       <c r="AB74" s="2">
-        <v>0.91666666666666663</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AC74" s="11">
         <f t="shared" si="2"/>
-        <v>2.5252603285800173</v>
+        <v>1.5443236627036447</v>
       </c>
     </row>
     <row r="75" spans="1:29" ht="17">
-      <c r="A75" s="2" t="s">
-        <v>151</v>
+      <c r="A75" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="B75" s="2">
-        <v>698</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>145</v>
+        <v>113</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="D75" s="2">
-        <v>1470</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>71</v>
+        <v>3000</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="F75" s="2">
-        <v>198</v>
+        <v>59.1</v>
       </c>
       <c r="G75" s="2">
-        <v>3.5252525252525251</v>
-      </c>
-      <c r="H75" s="2">
-        <v>23.596</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="J75" s="2">
-        <v>90</v>
+        <v>1.91</v>
+      </c>
+      <c r="H75" s="3">
+        <v>6.3029999999999999</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J75" s="3">
+        <v>48.423999999999999</v>
       </c>
       <c r="K75" s="3">
-        <v>44.731999999999999</v>
-      </c>
-      <c r="L75" s="2">
-        <v>2.0119824733971208</v>
+        <v>48.039000000000001</v>
+      </c>
+      <c r="L75" s="6">
+        <v>1.008014322</v>
       </c>
       <c r="M75" s="2">
-        <v>528.88547800000015</v>
+        <v>326.98653399999995</v>
       </c>
       <c r="N75" s="2">
-        <v>156.73678100000001</v>
+        <v>186.83260499999997</v>
       </c>
       <c r="O75" s="2">
-        <v>372.14883200000003</v>
+        <v>140.15379000000001</v>
       </c>
       <c r="P75" s="2">
-        <v>479.61241899999999</v>
+        <v>258.476448</v>
       </c>
       <c r="Q75" s="2">
-        <v>138.09142900000001</v>
+        <v>157.37730500000006</v>
       </c>
       <c r="R75" s="2">
-        <v>341.52099600000003</v>
+        <v>101.099051</v>
       </c>
       <c r="S75" s="2">
-        <v>1.1027351608257669</v>
+        <v>1.2650534953188459</v>
       </c>
       <c r="T75" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U75" s="2">
+        <v>2</v>
+      </c>
+      <c r="V75" s="2">
+        <v>1</v>
+      </c>
+      <c r="W75" s="2">
+        <v>7</v>
+      </c>
+      <c r="X75" s="2">
+        <v>4</v>
+      </c>
+      <c r="Y75" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z75" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA75" s="2">
         <v>9</v>
       </c>
-      <c r="V75" s="2">
-        <v>0</v>
-      </c>
-      <c r="W75" s="2">
-        <v>17</v>
-      </c>
-      <c r="X75" s="2">
-        <v>8</v>
-      </c>
-      <c r="Y75" s="2">
-        <v>3</v>
-      </c>
-      <c r="Z75" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="2">
-        <v>11</v>
-      </c>
       <c r="AB75" s="2">
-        <v>0.6470588235294118</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="AC75" s="11">
         <f t="shared" si="2"/>
-        <v>1.5443236627036447</v>
+        <v>2.504709960458932</v>
       </c>
     </row>
     <row r="76" spans="1:29" ht="17">
@@ -8069,127 +8059,127 @@
         <v>134</v>
       </c>
       <c r="B76" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D76" s="2">
-        <v>3000</v>
+        <v>1180</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F76" s="2">
-        <v>59.1</v>
+        <v>9.9500000000000005E-2</v>
       </c>
       <c r="G76" s="2">
-        <v>1.91</v>
+        <v>1145.73</v>
       </c>
       <c r="H76" s="3">
-        <v>6.3029999999999999</v>
+        <v>-3.0539999999999998</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J76" s="3">
-        <v>48.423999999999999</v>
+        <v>44.796999999999997</v>
       </c>
       <c r="K76" s="3">
-        <v>48.039000000000001</v>
+        <v>39.755000000000003</v>
       </c>
       <c r="L76" s="6">
-        <v>1.008014322</v>
+        <v>1.126826814</v>
       </c>
       <c r="M76" s="2">
-        <v>326.98653399999995</v>
+        <v>321.49026300000003</v>
       </c>
       <c r="N76" s="2">
-        <v>186.83260499999997</v>
+        <v>171.64188399999998</v>
       </c>
       <c r="O76" s="2">
-        <v>140.15379000000001</v>
+        <v>149.84830299999999</v>
       </c>
       <c r="P76" s="2">
-        <v>258.476448</v>
+        <v>307.27678800000001</v>
       </c>
       <c r="Q76" s="2">
-        <v>157.37730500000006</v>
+        <v>171.27784100000002</v>
       </c>
       <c r="R76" s="2">
-        <v>101.099051</v>
+        <v>135.99903099999997</v>
       </c>
       <c r="S76" s="2">
-        <v>1.2650534953188459</v>
+        <v>1.0462562600075083</v>
       </c>
       <c r="T76" s="2">
         <v>4</v>
       </c>
       <c r="U76" s="2">
+        <v>5</v>
+      </c>
+      <c r="V76" s="2">
         <v>2</v>
       </c>
-      <c r="V76" s="2">
-        <v>1</v>
-      </c>
       <c r="W76" s="2">
+        <v>11</v>
+      </c>
+      <c r="X76" s="2">
         <v>7</v>
       </c>
-      <c r="X76" s="2">
-        <v>4</v>
-      </c>
       <c r="Y76" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA76" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB76" s="2">
-        <v>0.77777777777777779</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="AC76" s="11">
         <f t="shared" si="2"/>
-        <v>2.504709960458932</v>
+        <v>2.673070772146338</v>
       </c>
     </row>
     <row r="77" spans="1:29" ht="17">
       <c r="A77" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B77" s="2">
         <v>114</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D77" s="2">
-        <v>1180</v>
+        <v>3000</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F77" s="2">
-        <v>9.9500000000000005E-2</v>
+        <v>7.7799999999999994E-2</v>
       </c>
       <c r="G77" s="2">
-        <v>1145.73</v>
+        <v>1465.3</v>
       </c>
       <c r="H77" s="3">
-        <v>-3.0539999999999998</v>
+        <v>12.696</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J77" s="3">
-        <v>44.796999999999997</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="K77" s="3">
-        <v>39.755000000000003</v>
+        <v>45.518999999999998</v>
       </c>
       <c r="L77" s="6">
-        <v>1.126826814</v>
+        <v>1.4246798039999999</v>
       </c>
       <c r="M77" s="2">
         <v>321.49026300000003</v>
@@ -8201,16 +8191,16 @@
         <v>149.84830299999999</v>
       </c>
       <c r="P77" s="2">
-        <v>307.27678800000001</v>
+        <v>258.476448</v>
       </c>
       <c r="Q77" s="2">
-        <v>171.27784100000002</v>
+        <v>157.37730500000006</v>
       </c>
       <c r="R77" s="2">
-        <v>135.99903099999997</v>
+        <v>101.099051</v>
       </c>
       <c r="S77" s="2">
-        <v>1.0462562600075083</v>
+        <v>1.2437893877278909</v>
       </c>
       <c r="T77" s="2">
         <v>4</v>
@@ -8225,160 +8215,160 @@
         <v>11</v>
       </c>
       <c r="X77" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y77" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA77" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AB77" s="2">
-        <v>0.84615384615384615</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="AC77" s="11">
         <f t="shared" si="2"/>
-        <v>2.673070772146338</v>
+        <v>2.1093085860498868</v>
       </c>
     </row>
     <row r="78" spans="1:29" ht="17">
-      <c r="A78" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B78" s="2">
-        <v>114</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D78" s="2">
-        <v>3000</v>
+      <c r="A78" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B78" s="3">
+        <v>867.3</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D78" s="3">
+        <v>101.7</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F78" s="2">
-        <v>7.7799999999999994E-2</v>
-      </c>
-      <c r="G78" s="2">
-        <v>1465.3</v>
-      </c>
-      <c r="H78" s="3">
-        <v>12.696</v>
+        <v>4.09</v>
+      </c>
+      <c r="G78" s="7">
+        <v>24.865525672371639</v>
+      </c>
+      <c r="H78" s="2">
+        <v>-27.199000000000002</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="J78" s="3">
-        <v>64.849999999999994</v>
+        <v>41.493000000000002</v>
       </c>
       <c r="K78" s="3">
-        <v>45.518999999999998</v>
-      </c>
-      <c r="L78" s="6">
-        <v>1.4246798039999999</v>
+        <v>35.933</v>
+      </c>
+      <c r="L78" s="3">
+        <v>1.1547324186680767</v>
       </c>
       <c r="M78" s="2">
-        <v>321.49026300000003</v>
+        <v>245.92968800000003</v>
       </c>
       <c r="N78" s="2">
-        <v>171.64188399999998</v>
+        <v>129.30007800000001</v>
       </c>
       <c r="O78" s="2">
-        <v>149.84830299999999</v>
+        <v>116.629651</v>
       </c>
       <c r="P78" s="2">
-        <v>258.476448</v>
+        <v>271.65998100000002</v>
       </c>
       <c r="Q78" s="2">
-        <v>157.37730500000006</v>
+        <v>121.86641</v>
       </c>
       <c r="R78" s="2">
-        <v>101.099051</v>
+        <v>149.79363000000001</v>
       </c>
       <c r="S78" s="2">
-        <v>1.2437893877278909</v>
+        <v>0.90528493411033562</v>
       </c>
       <c r="T78" s="2">
+        <v>3</v>
+      </c>
+      <c r="U78" s="2">
+        <v>1</v>
+      </c>
+      <c r="V78" s="2">
+        <v>0</v>
+      </c>
+      <c r="W78" s="2">
         <v>4</v>
       </c>
-      <c r="U78" s="2">
-        <v>5</v>
-      </c>
-      <c r="V78" s="2">
-        <v>2</v>
-      </c>
-      <c r="W78" s="2">
-        <v>11</v>
-      </c>
       <c r="X78" s="2">
+        <v>6</v>
+      </c>
+      <c r="Y78" s="2">
+        <v>7</v>
+      </c>
+      <c r="Z78" s="2">
+        <v>3</v>
+      </c>
+      <c r="AA78" s="2">
+        <v>16</v>
+      </c>
+      <c r="AB78" s="2">
         <v>4</v>
-      </c>
-      <c r="Y78" s="2">
-        <v>4</v>
-      </c>
-      <c r="Z78" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA78" s="2">
-        <v>9</v>
-      </c>
-      <c r="AB78" s="2">
-        <v>1.2222222222222223</v>
       </c>
       <c r="AC78" s="11">
         <f t="shared" si="2"/>
-        <v>2.1093085860498868</v>
+        <v>2.250552515442259</v>
       </c>
     </row>
     <row r="79" spans="1:29" ht="17">
       <c r="A79" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B79" s="3">
-        <v>867.3</v>
+        <v>209.8</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D79" s="3">
         <v>101.7</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F79" s="2">
-        <v>4.09</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="G79" s="7">
-        <v>24.865525672371639</v>
+        <v>438.36206896551721</v>
       </c>
       <c r="H79" s="2">
-        <v>-27.199000000000002</v>
+        <v>-20.690999999999999</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J79" s="3">
-        <v>41.493000000000002</v>
+        <v>44.796999999999997</v>
       </c>
       <c r="K79" s="3">
-        <v>35.933</v>
+        <v>41.962000000000003</v>
       </c>
       <c r="L79" s="3">
-        <v>1.1547324186680767</v>
+        <v>1.0675611267337113</v>
       </c>
       <c r="M79" s="2">
-        <v>245.92968800000003</v>
+        <v>443.05761199999995</v>
       </c>
       <c r="N79" s="2">
-        <v>129.30007800000001</v>
+        <v>273.54349500000006</v>
       </c>
       <c r="O79" s="2">
-        <v>116.629651</v>
+        <v>169.51407600000005</v>
       </c>
       <c r="P79" s="2">
         <v>271.65998100000002</v>
@@ -8390,19 +8380,19 @@
         <v>149.79363000000001</v>
       </c>
       <c r="S79" s="2">
-        <v>0.90528493411033562</v>
+        <v>1.6309270521520058</v>
       </c>
       <c r="T79" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U79" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V79" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W79" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="X79" s="2">
         <v>6</v>
@@ -8417,49 +8407,49 @@
         <v>16</v>
       </c>
       <c r="AB79" s="2">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="AC79" s="11">
         <f t="shared" si="2"/>
-        <v>2.250552515442259</v>
+        <v>2.2324388732662888</v>
       </c>
     </row>
     <row r="80" spans="1:29" ht="17">
       <c r="A80" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B80" s="3">
         <v>209.8</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D80" s="3">
-        <v>101.7</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F80" s="2">
-        <v>0.23200000000000001</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="G80" s="7">
-        <v>438.36206896551721</v>
+        <v>0.29429892141756547</v>
       </c>
       <c r="H80" s="2">
-        <v>-20.690999999999999</v>
+        <v>53.537999999999997</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J80" s="3">
-        <v>44.796999999999997</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="K80" s="3">
-        <v>41.962000000000003</v>
+        <v>59.643999999999998</v>
       </c>
       <c r="L80" s="3">
-        <v>1.0675611267337113</v>
+        <v>1.0872845550264905</v>
       </c>
       <c r="M80" s="2">
         <v>443.05761199999995</v>
@@ -8471,16 +8461,16 @@
         <v>169.51407600000005</v>
       </c>
       <c r="P80" s="2">
-        <v>271.65998100000002</v>
+        <v>313.33782000000002</v>
       </c>
       <c r="Q80" s="2">
-        <v>121.86641</v>
+        <v>153.24117900000005</v>
       </c>
       <c r="R80" s="2">
-        <v>149.79363000000001</v>
+        <v>160.0966</v>
       </c>
       <c r="S80" s="2">
-        <v>1.6309270521520058</v>
+        <v>1.4139934081369427</v>
       </c>
       <c r="T80" s="2">
         <v>12</v>
@@ -8495,152 +8485,153 @@
         <v>20</v>
       </c>
       <c r="X80" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y80" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z80" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="2">
         <v>6</v>
       </c>
-      <c r="Y80" s="2">
-        <v>7</v>
-      </c>
-      <c r="Z80" s="2">
-        <v>3</v>
-      </c>
-      <c r="AA80" s="2">
-        <v>16</v>
-      </c>
       <c r="AB80" s="2">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="AC80" s="11">
         <f t="shared" si="2"/>
-        <v>2.2324388732662888</v>
+        <v>1.9987220368365668</v>
       </c>
     </row>
     <row r="81" spans="1:29" ht="17">
       <c r="A81" s="3" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="B81" s="3">
-        <v>209.8</v>
+        <v>1480</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="D81" s="3">
-        <v>19.100000000000001</v>
+        <v>601</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F81" s="2">
-        <v>64.900000000000006</v>
+      <c r="F81" s="3">
+        <v>2.25</v>
       </c>
       <c r="G81" s="7">
-        <v>0.29429892141756547</v>
+        <v>267.11111111111109</v>
       </c>
       <c r="H81" s="2">
-        <v>53.537999999999997</v>
+        <v>25.981000000000002</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J81" s="3">
-        <v>64.849999999999994</v>
-      </c>
-      <c r="K81" s="3">
-        <v>59.643999999999998</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1.0872845550264905</v>
+        <v>163</v>
+      </c>
+      <c r="J81" s="7">
+        <v>48.484000000000002</v>
+      </c>
+      <c r="K81" s="7">
+        <v>47.137</v>
+      </c>
+      <c r="L81" s="7">
+        <f t="shared" ref="L81" si="3">J81/K81</f>
+        <v>1.0285762776587395</v>
       </c>
       <c r="M81" s="2">
-        <v>443.05761199999995</v>
+        <v>497.53826999999995</v>
       </c>
       <c r="N81" s="2">
-        <v>273.54349500000006</v>
+        <v>239.94313700000006</v>
       </c>
       <c r="O81" s="2">
-        <v>169.51407600000005</v>
+        <v>257.59497199999998</v>
       </c>
       <c r="P81" s="2">
-        <v>313.33782000000002</v>
+        <v>539.15123300000005</v>
       </c>
       <c r="Q81" s="2">
-        <v>153.24117900000005</v>
+        <v>297.34429000000006</v>
       </c>
       <c r="R81" s="2">
-        <v>160.0966</v>
+        <v>241.80690300000003</v>
       </c>
       <c r="S81" s="2">
-        <v>1.4139934081369427</v>
+        <v>0.92281764289315815</v>
       </c>
       <c r="T81" s="2">
+        <v>14</v>
+      </c>
+      <c r="U81" s="2">
+        <v>0</v>
+      </c>
+      <c r="V81" s="2">
+        <v>0</v>
+      </c>
+      <c r="W81" s="2">
+        <v>14</v>
+      </c>
+      <c r="X81" s="2">
         <v>12</v>
       </c>
-      <c r="U81" s="2">
-        <v>6</v>
-      </c>
-      <c r="V81" s="2">
-        <v>2</v>
-      </c>
-      <c r="W81" s="2">
-        <v>20</v>
-      </c>
-      <c r="X81" s="2">
-        <v>5</v>
-      </c>
       <c r="Y81" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z81" s="2">
         <v>0</v>
       </c>
       <c r="AA81" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AB81" s="2">
-        <v>0.3</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="AC81" s="11">
         <f t="shared" si="2"/>
-        <v>1.9987220368365668</v>
+        <v>2.751384222377276</v>
       </c>
     </row>
     <row r="82" spans="1:29" ht="17">
       <c r="A82" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B82" s="3">
         <v>1480</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D82" s="3">
-        <v>601</v>
+        <v>2060</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F82" s="3">
-        <v>2.25</v>
+        <v>179</v>
+      </c>
+      <c r="F82" s="2">
+        <v>1.66</v>
       </c>
       <c r="G82" s="7">
-        <v>267.11111111111109</v>
+        <v>891.56626506024099</v>
       </c>
       <c r="H82" s="2">
-        <v>25.981000000000002</v>
+        <v>37.536999999999999</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J82" s="7">
-        <v>48.484000000000002</v>
+        <v>84.430999999999997</v>
       </c>
       <c r="K82" s="7">
-        <v>47.137</v>
+        <v>82.947999999999993</v>
       </c>
       <c r="L82" s="7">
-        <f t="shared" ref="L82" si="3">J82/K82</f>
-        <v>1.0285762776587395</v>
+        <f>J82/K82</f>
+        <v>1.0178786709745866</v>
       </c>
       <c r="M82" s="2">
         <v>497.53826999999995</v>
@@ -8652,16 +8643,16 @@
         <v>257.59497199999998</v>
       </c>
       <c r="P82" s="2">
-        <v>539.15123300000005</v>
+        <v>411.8296180000001</v>
       </c>
       <c r="Q82" s="2">
-        <v>297.34429000000006</v>
+        <v>235.11411600000005</v>
       </c>
       <c r="R82" s="2">
-        <v>241.80690300000003</v>
+        <v>176.71553800000004</v>
       </c>
       <c r="S82" s="2">
-        <v>0.92281764289315815</v>
+        <v>1.2081167751271349</v>
       </c>
       <c r="T82" s="2">
         <v>14</v>
@@ -8676,114 +8667,114 @@
         <v>14</v>
       </c>
       <c r="X82" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y82" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z82" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA82" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AB82" s="2">
-        <v>1.1428571428571428</v>
+        <v>1</v>
       </c>
       <c r="AC82" s="11">
         <f t="shared" si="2"/>
-        <v>2.751384222377276</v>
+        <v>2.7740045538982785</v>
       </c>
     </row>
     <row r="83" spans="1:29" ht="17">
       <c r="A83" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B83" s="3">
-        <v>1480</v>
+        <v>100</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D83" s="3">
-        <v>2060</v>
+        <v>105</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F83" s="2">
-        <v>1.66</v>
+        <v>3.7</v>
       </c>
       <c r="G83" s="7">
-        <v>891.56626506024099</v>
+        <v>27.027027027027025</v>
       </c>
       <c r="H83" s="2">
-        <v>37.536999999999999</v>
+        <v>5.9850000000000003</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="J83" s="7">
-        <v>84.430999999999997</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="K83" s="7">
-        <v>82.947999999999993</v>
+        <v>62.48</v>
       </c>
       <c r="L83" s="7">
-        <f>J83/K83</f>
-        <v>1.0178786709745866</v>
+        <f t="shared" ref="L83:L87" si="4">J83/K83</f>
+        <v>1.037932138284251</v>
       </c>
       <c r="M83" s="2">
-        <v>497.53826999999995</v>
+        <v>462.43215500000002</v>
       </c>
       <c r="N83" s="2">
-        <v>239.94313700000006</v>
+        <v>239.18309600000001</v>
       </c>
       <c r="O83" s="2">
-        <v>257.59497199999998</v>
+        <v>223.24905699999997</v>
       </c>
       <c r="P83" s="2">
-        <v>411.8296180000001</v>
+        <v>530.66215899999997</v>
       </c>
       <c r="Q83" s="2">
-        <v>235.11411600000005</v>
+        <v>330.95660999999996</v>
       </c>
       <c r="R83" s="2">
-        <v>176.71553800000004</v>
+        <v>199.70535100000001</v>
       </c>
       <c r="S83" s="2">
-        <v>1.2081167751271349</v>
+        <v>0.87142477969679399</v>
       </c>
       <c r="T83" s="2">
+        <v>15</v>
+      </c>
+      <c r="U83" s="2">
+        <v>5</v>
+      </c>
+      <c r="V83" s="2">
+        <v>0</v>
+      </c>
+      <c r="W83" s="2">
+        <v>20</v>
+      </c>
+      <c r="X83" s="2">
         <v>14</v>
       </c>
-      <c r="U83" s="2">
-        <v>0</v>
-      </c>
-      <c r="V83" s="2">
-        <v>0</v>
-      </c>
-      <c r="W83" s="2">
-        <v>14</v>
-      </c>
-      <c r="X83" s="2">
-        <v>9</v>
-      </c>
       <c r="Y83" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z83" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA83" s="2">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AB83" s="2">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AC83" s="11">
         <f t="shared" si="2"/>
-        <v>2.7740045538982785</v>
+        <v>2.5834926414125432</v>
       </c>
     </row>
     <row r="84" spans="1:29" ht="17">
@@ -8791,129 +8782,129 @@
         <v>125</v>
       </c>
       <c r="B84" s="3">
-        <v>100</v>
+        <v>4370</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D84" s="3">
-        <v>105</v>
+        <v>921</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F84" s="2">
-        <v>3.7</v>
+        <v>140</v>
       </c>
       <c r="G84" s="7">
-        <v>27.027027027027025</v>
+        <v>6.5785714285714283</v>
       </c>
       <c r="H84" s="2">
-        <v>5.9850000000000003</v>
+        <v>37.963000000000001</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="J84" s="7">
-        <v>64.849999999999994</v>
+        <v>56.567</v>
       </c>
       <c r="K84" s="7">
-        <v>62.48</v>
+        <v>52.018999999999998</v>
       </c>
       <c r="L84" s="7">
-        <f t="shared" ref="L84:L88" si="4">J84/K84</f>
-        <v>1.037932138284251</v>
+        <f t="shared" si="4"/>
+        <v>1.0874295930333149</v>
       </c>
       <c r="M84" s="2">
-        <v>462.43215500000002</v>
+        <v>506.43552499999987</v>
       </c>
       <c r="N84" s="2">
-        <v>239.18309600000001</v>
+        <v>259.91992799999997</v>
       </c>
       <c r="O84" s="2">
-        <v>223.24905699999997</v>
+        <v>246.51551700000005</v>
       </c>
       <c r="P84" s="2">
-        <v>530.66215899999997</v>
+        <v>414.92451099999994</v>
       </c>
       <c r="Q84" s="2">
-        <v>330.95660999999996</v>
+        <v>301.91507500000006</v>
       </c>
       <c r="R84" s="2">
-        <v>199.70535100000001</v>
+        <v>113.009351</v>
       </c>
       <c r="S84" s="2">
-        <v>0.87142477969679399</v>
+        <v>1.2205485855233074</v>
       </c>
       <c r="T84" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U84" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V84" s="2">
         <v>0</v>
       </c>
       <c r="W84" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="X84" s="2">
         <v>14</v>
       </c>
       <c r="Y84" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z84" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA84" s="2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AB84" s="2">
-        <v>1.25</v>
+        <v>1.0625</v>
       </c>
       <c r="AC84" s="11">
         <f t="shared" si="2"/>
-        <v>2.5834926414125432</v>
+        <v>2.6295218214433778</v>
       </c>
     </row>
     <row r="85" spans="1:29" ht="17">
       <c r="A85" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B85" s="3">
         <v>4370</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D85" s="3">
-        <v>921</v>
+        <v>2060</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F85" s="2">
-        <v>140</v>
+        <v>177</v>
+      </c>
+      <c r="F85" s="3">
+        <v>1540</v>
       </c>
       <c r="G85" s="7">
-        <v>6.5785714285714283</v>
+        <v>1.3376623376623376</v>
       </c>
       <c r="H85" s="2">
-        <v>37.963000000000001</v>
+        <v>34.478999999999999</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="J85" s="7">
-        <v>56.567</v>
+        <v>82.206000000000003</v>
       </c>
       <c r="K85" s="7">
-        <v>52.018999999999998</v>
+        <v>79.210999999999999</v>
       </c>
       <c r="L85" s="7">
         <f t="shared" si="4"/>
-        <v>1.0874295930333149</v>
+        <v>1.037810405120501</v>
       </c>
       <c r="M85" s="2">
         <v>506.43552499999987</v>
@@ -8925,16 +8916,16 @@
         <v>246.51551700000005</v>
       </c>
       <c r="P85" s="2">
-        <v>414.92451099999994</v>
+        <v>411.8296180000001</v>
       </c>
       <c r="Q85" s="2">
-        <v>301.91507500000006</v>
+        <v>235.11411600000005</v>
       </c>
       <c r="R85" s="2">
-        <v>113.009351</v>
+        <v>176.71553800000004</v>
       </c>
       <c r="S85" s="2">
-        <v>1.2205485855233074</v>
+        <v>1.2297209886443858</v>
       </c>
       <c r="T85" s="2">
         <v>16</v>
@@ -8949,424 +8940,423 @@
         <v>16</v>
       </c>
       <c r="X85" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Y85" s="2">
         <v>3</v>
       </c>
       <c r="Z85" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA85" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AB85" s="2">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="AC85" s="11">
         <f t="shared" si="2"/>
-        <v>2.6295218214433778</v>
+        <v>2.6074686062351131</v>
       </c>
     </row>
     <row r="86" spans="1:29" ht="17">
       <c r="A86" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B86" s="3">
-        <v>4370</v>
+        <v>138</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="D86" s="3">
-        <v>2060</v>
+        <v>99.5</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F86" s="3">
-        <v>1540</v>
+        <v>181</v>
+      </c>
+      <c r="F86" s="2">
+        <v>19.2</v>
       </c>
       <c r="G86" s="7">
-        <v>1.3376623376623376</v>
+        <v>5.182291666666667</v>
       </c>
       <c r="H86" s="2">
-        <v>34.478999999999999</v>
+        <v>6.0439999999999996</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J86" s="7">
-        <v>82.206000000000003</v>
+        <v>48.484000000000002</v>
       </c>
       <c r="K86" s="7">
-        <v>79.210999999999999</v>
+        <v>46.444000000000003</v>
       </c>
       <c r="L86" s="7">
         <f t="shared" si="4"/>
-        <v>1.037810405120501</v>
+        <v>1.0439238653001464</v>
       </c>
       <c r="M86" s="2">
-        <v>506.43552499999987</v>
+        <v>401.78200400000003</v>
       </c>
       <c r="N86" s="2">
-        <v>259.91992799999997</v>
+        <v>220.08053999999998</v>
       </c>
       <c r="O86" s="2">
-        <v>246.51551700000005</v>
+        <v>181.70129399999999</v>
       </c>
       <c r="P86" s="2">
-        <v>411.8296180000001</v>
+        <v>355.54163900000003</v>
       </c>
       <c r="Q86" s="2">
-        <v>235.11411600000005</v>
+        <v>93.098927000000018</v>
       </c>
       <c r="R86" s="2">
-        <v>176.71553800000004</v>
+        <v>262.44285100000008</v>
       </c>
       <c r="S86" s="2">
-        <v>1.2297209886443858</v>
+        <v>1.130056116999562</v>
       </c>
       <c r="T86" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="U86" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V86" s="2">
         <v>0</v>
       </c>
       <c r="W86" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X86" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y86" s="2">
         <v>9</v>
       </c>
-      <c r="Y86" s="2">
-        <v>3</v>
-      </c>
       <c r="Z86" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA86" s="2">
         <v>14</v>
       </c>
       <c r="AB86" s="2">
-        <v>0.875</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="AC86" s="11">
         <f t="shared" si="2"/>
-        <v>2.6074686062351131</v>
+        <v>2.6495494294649973</v>
       </c>
     </row>
     <row r="87" spans="1:29" ht="17">
       <c r="A87" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B87" s="3">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D87" s="3">
-        <v>99.5</v>
+        <v>1470</v>
       </c>
       <c r="E87" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F87" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="G87" s="7">
+        <v>81.481481481481481</v>
+      </c>
+      <c r="H87" s="2">
+        <v>31.024000000000001</v>
+      </c>
+      <c r="I87" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F87" s="2">
-        <v>19.2</v>
-      </c>
-      <c r="G87" s="7">
-        <v>5.182291666666667</v>
-      </c>
-      <c r="H87" s="2">
-        <v>6.0439999999999996</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="J87" s="7">
-        <v>48.484000000000002</v>
+        <v>56.567</v>
       </c>
       <c r="K87" s="7">
-        <v>46.444000000000003</v>
+        <v>55.347999999999999</v>
       </c>
       <c r="L87" s="7">
         <f t="shared" si="4"/>
-        <v>1.0439238653001464</v>
+        <v>1.0220242827202428</v>
       </c>
       <c r="M87" s="2">
-        <v>401.78200400000003</v>
+        <v>489.53467200000006</v>
       </c>
       <c r="N87" s="2">
-        <v>220.08053999999998</v>
+        <v>159.10767099999998</v>
       </c>
       <c r="O87" s="2">
-        <v>181.70129399999999</v>
+        <v>330.42694800000004</v>
       </c>
       <c r="P87" s="2">
-        <v>355.54163900000003</v>
+        <v>479.61241899999999</v>
       </c>
       <c r="Q87" s="2">
-        <v>93.098927000000018</v>
+        <v>138.09142900000001</v>
       </c>
       <c r="R87" s="2">
-        <v>262.44285100000008</v>
+        <v>341.52099600000003</v>
       </c>
       <c r="S87" s="2">
-        <v>1.130056116999562</v>
+        <v>1.0206880652104215</v>
       </c>
       <c r="T87" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U87" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V87" s="2">
         <v>0</v>
       </c>
       <c r="W87" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X87" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y87" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z87" s="2">
         <v>0</v>
       </c>
       <c r="AA87" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AB87" s="2">
-        <v>0.82352941176470584</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AC87" s="11">
         <f t="shared" si="2"/>
-        <v>2.6495494294649973</v>
+        <v>2.7430019377836214</v>
       </c>
     </row>
     <row r="88" spans="1:29" ht="17">
-      <c r="A88" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B88" s="3">
-        <v>220</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D88" s="3">
-        <v>1470</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>66</v>
+      <c r="A88" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B88" s="2">
+        <v>1750</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D88" s="2">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="F88" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="G88" s="7">
-        <v>81.481481481481481</v>
-      </c>
-      <c r="H88" s="2">
-        <v>31.024000000000001</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J88" s="7">
-        <v>56.567</v>
-      </c>
-      <c r="K88" s="7">
-        <v>55.347999999999999</v>
-      </c>
-      <c r="L88" s="7">
-        <f t="shared" si="4"/>
-        <v>1.0220242827202428</v>
-      </c>
-      <c r="M88" s="2">
-        <v>489.53467200000006</v>
-      </c>
-      <c r="N88" s="2">
-        <v>159.10767099999998</v>
-      </c>
-      <c r="O88" s="2">
-        <v>330.42694800000004</v>
-      </c>
-      <c r="P88" s="2">
-        <v>479.61241899999999</v>
-      </c>
-      <c r="Q88" s="2">
-        <v>138.09142900000001</v>
-      </c>
-      <c r="R88" s="2">
-        <v>341.52099600000003</v>
-      </c>
-      <c r="S88" s="2">
-        <v>1.0206880652104215</v>
-      </c>
-      <c r="T88" s="2">
-        <v>7</v>
-      </c>
-      <c r="U88" s="2">
-        <v>7</v>
-      </c>
-      <c r="V88" s="2">
-        <v>0</v>
-      </c>
-      <c r="W88" s="2">
-        <v>14</v>
-      </c>
-      <c r="X88" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="G88" s="2">
+        <v>3.5923913043478302</v>
+      </c>
+      <c r="H88" s="9">
+        <v>23.481999999999999</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J88" s="2">
+        <v>72</v>
+      </c>
+      <c r="K88" s="9">
+        <v>66.914000000000001</v>
+      </c>
+      <c r="L88" s="9">
+        <v>1.0760080102818543</v>
+      </c>
+      <c r="M88" s="9">
+        <v>171.45177000000001</v>
+      </c>
+      <c r="N88" s="9">
+        <v>110.238232</v>
+      </c>
+      <c r="O88" s="9">
+        <v>61.213506000000002</v>
+      </c>
+      <c r="P88" s="10">
+        <v>401.37350800000002</v>
+      </c>
+      <c r="Q88" s="10">
+        <v>213.85547299999999</v>
+      </c>
+      <c r="R88" s="10">
+        <v>187.518067</v>
+      </c>
+      <c r="S88" s="9">
+        <v>0.42716264671857718</v>
+      </c>
+      <c r="T88" s="9">
+        <v>3</v>
+      </c>
+      <c r="U88" s="9">
+        <v>1</v>
+      </c>
+      <c r="V88" s="9">
+        <v>2</v>
+      </c>
+      <c r="W88" s="9">
+        <v>6</v>
+      </c>
+      <c r="X88" s="9">
+        <v>3</v>
+      </c>
+      <c r="Y88" s="9">
+        <v>3</v>
+      </c>
+      <c r="Z88" s="9">
+        <v>2</v>
+      </c>
+      <c r="AA88" s="9">
         <v>8</v>
       </c>
-      <c r="Y88" s="2">
-        <v>3</v>
-      </c>
-      <c r="Z88" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA88" s="2">
-        <v>11</v>
-      </c>
-      <c r="AB88" s="2">
-        <v>0.7857142857142857</v>
+      <c r="AB88" s="9">
+        <v>1.3333333333333333</v>
       </c>
       <c r="AC88" s="11">
         <f t="shared" si="2"/>
-        <v>2.7430019377836214</v>
+        <v>2.0906586563848126</v>
       </c>
     </row>
     <row r="89" spans="1:29" ht="17">
       <c r="A89" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B89" s="2">
+        <v>1480</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D89" s="2">
+        <v>601</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B89" s="2">
-        <v>1750</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D89" s="2">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="F89" s="2">
-        <v>18.399999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="G89" s="2">
-        <v>3.5923913043478302</v>
+        <v>10.848375451263538</v>
       </c>
       <c r="H89" s="9">
-        <v>23.481999999999999</v>
+        <v>-5.5229999999999997</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J89" s="2">
         <v>72</v>
       </c>
       <c r="K89" s="9">
-        <v>66.914000000000001</v>
+        <v>33.145000000000003</v>
       </c>
       <c r="L89" s="9">
-        <v>1.0760080102818543</v>
-      </c>
-      <c r="M89" s="9">
-        <v>171.45177000000001</v>
-      </c>
-      <c r="N89" s="9">
-        <v>110.238232</v>
-      </c>
-      <c r="O89" s="9">
-        <v>61.213506000000002</v>
+        <v>2.1722733443958364</v>
+      </c>
+      <c r="M89" s="10">
+        <v>308.80267300000003</v>
+      </c>
+      <c r="N89" s="10">
+        <v>201.33283900000001</v>
+      </c>
+      <c r="O89" s="10">
+        <v>107.46975</v>
       </c>
       <c r="P89" s="10">
-        <v>401.37350800000002</v>
+        <v>541.30428400000005</v>
       </c>
       <c r="Q89" s="10">
-        <v>213.85547299999999</v>
+        <v>264.874482</v>
       </c>
       <c r="R89" s="10">
-        <v>187.518067</v>
+        <v>276.42980499999999</v>
       </c>
       <c r="S89" s="9">
-        <v>0.42716264671857718</v>
+        <v>0.57047890092072506</v>
       </c>
       <c r="T89" s="9">
         <v>3</v>
       </c>
       <c r="U89" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V89" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W89" s="9">
+        <v>14</v>
+      </c>
+      <c r="X89" s="9">
         <v>6</v>
       </c>
-      <c r="X89" s="9">
-        <v>3</v>
-      </c>
       <c r="Y89" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Z89" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA89" s="9">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AB89" s="9">
-        <v>1.3333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="AC89" s="11">
         <f t="shared" si="2"/>
-        <v>2.0906586563848126</v>
+        <v>1.0704789009207252</v>
       </c>
     </row>
     <row r="90" spans="1:29" ht="17">
       <c r="A90" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B90" s="2">
         <v>1480</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D90" s="2">
-        <v>601</v>
+        <v>2060</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F90" s="2">
-        <v>55.4</v>
+        <v>5.04</v>
       </c>
       <c r="G90" s="2">
-        <v>10.848375451263538</v>
+        <v>293.65079365079401</v>
       </c>
       <c r="H90" s="9">
-        <v>-5.5229999999999997</v>
+        <v>14.73</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J90" s="2">
         <v>72</v>
       </c>
       <c r="K90" s="9">
-        <v>33.145000000000003</v>
+        <v>54.209000000000003</v>
       </c>
       <c r="L90" s="9">
-        <v>2.1722733443958364</v>
+        <v>1.3281927355236214</v>
       </c>
       <c r="M90" s="10">
         <v>308.80267300000003</v>
@@ -9378,16 +9368,16 @@
         <v>107.46975</v>
       </c>
       <c r="P90" s="10">
-        <v>541.30428400000005</v>
+        <v>320.9597</v>
       </c>
       <c r="Q90" s="10">
-        <v>264.874482</v>
+        <v>180.52893700000001</v>
       </c>
       <c r="R90" s="10">
-        <v>276.42980499999999</v>
+        <v>140.43079800000001</v>
       </c>
       <c r="S90" s="9">
-        <v>0.57047890092072506</v>
+        <v>0.96212288645583866</v>
       </c>
       <c r="T90" s="9">
         <v>3</v>
@@ -9401,62 +9391,62 @@
       <c r="W90" s="9">
         <v>14</v>
       </c>
-      <c r="X90" s="9">
-        <v>6</v>
-      </c>
-      <c r="Y90" s="9">
-        <v>11</v>
-      </c>
-      <c r="Z90" s="9">
-        <v>4</v>
-      </c>
-      <c r="AA90" s="9">
-        <v>21</v>
+      <c r="X90" s="10">
+        <v>2</v>
+      </c>
+      <c r="Y90" s="10">
+        <v>14</v>
+      </c>
+      <c r="Z90" s="10">
+        <v>1</v>
+      </c>
+      <c r="AA90" s="10">
+        <v>17</v>
       </c>
       <c r="AB90" s="9">
-        <v>1.5</v>
+        <v>1.2142857142857142</v>
       </c>
       <c r="AC90" s="11">
         <f t="shared" si="2"/>
-        <v>1.0704789009207252</v>
+        <v>2.4196444366465029</v>
       </c>
     </row>
     <row r="91" spans="1:29" ht="17">
       <c r="A91" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B91" s="2">
         <v>1480</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D91" s="2">
-        <v>2060</v>
+        <v>921</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F91" s="2">
-        <v>5.04</v>
+        <v>97.9</v>
       </c>
       <c r="G91" s="2">
-        <v>293.65079365079401</v>
+        <v>9.4075587334014301</v>
       </c>
       <c r="H91" s="9">
-        <v>14.73</v>
+        <v>27.146000000000001</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J91" s="2">
         <v>72</v>
       </c>
       <c r="K91" s="9">
-        <v>54.209000000000003</v>
+        <v>16.439</v>
       </c>
       <c r="L91" s="9">
-        <v>1.3281927355236214</v>
+        <v>4.3798284567187782</v>
       </c>
       <c r="M91" s="10">
         <v>308.80267300000003</v>
@@ -9468,16 +9458,16 @@
         <v>107.46975</v>
       </c>
       <c r="P91" s="10">
-        <v>320.9597</v>
+        <v>268.55290300000001</v>
       </c>
       <c r="Q91" s="10">
-        <v>180.52893700000001</v>
+        <v>185.45786000000001</v>
       </c>
       <c r="R91" s="10">
-        <v>140.43079800000001</v>
+        <v>83.095070000000007</v>
       </c>
       <c r="S91" s="9">
-        <v>0.96212288645583866</v>
+        <v>1.1498765031037479</v>
       </c>
       <c r="T91" s="9">
         <v>3</v>
@@ -9492,151 +9482,151 @@
         <v>14</v>
       </c>
       <c r="X91" s="10">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="10">
         <v>2</v>
       </c>
-      <c r="Y91" s="10">
-        <v>14</v>
-      </c>
-      <c r="Z91" s="10">
-        <v>1</v>
-      </c>
       <c r="AA91" s="10">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AB91" s="9">
-        <v>1.2142857142857142</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AC91" s="11">
         <f t="shared" si="2"/>
-        <v>2.4196444366465029</v>
+        <v>1.3501234968962521</v>
       </c>
     </row>
     <row r="92" spans="1:29" ht="17">
       <c r="A92" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B92" s="2">
-        <v>1480</v>
+        <v>100</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D92" s="2">
-        <v>921</v>
+        <v>105</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F92" s="2">
-        <v>97.9</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="G92" s="2">
-        <v>9.4075587334014301</v>
+        <v>10.288065843621398</v>
       </c>
       <c r="H92" s="9">
-        <v>27.146000000000001</v>
+        <v>-5.258</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J92" s="2">
         <v>72</v>
       </c>
       <c r="K92" s="9">
-        <v>16.439</v>
+        <v>35.959000000000003</v>
       </c>
       <c r="L92" s="9">
-        <v>4.3798284567187782</v>
+        <v>2.0022803748713813</v>
       </c>
       <c r="M92" s="10">
-        <v>308.80267300000003</v>
+        <v>509.061894</v>
       </c>
       <c r="N92" s="10">
-        <v>201.33283900000001</v>
+        <v>304.09381500000001</v>
       </c>
       <c r="O92" s="10">
-        <v>107.46975</v>
+        <v>204.96811299999999</v>
       </c>
       <c r="P92" s="10">
-        <v>268.55290300000001</v>
+        <v>404.02995700000002</v>
       </c>
       <c r="Q92" s="10">
-        <v>185.45786000000001</v>
+        <v>219.08395200000001</v>
       </c>
       <c r="R92" s="10">
-        <v>83.095070000000007</v>
+        <v>184.94590600000001</v>
       </c>
       <c r="S92" s="9">
-        <v>1.1498765031037479</v>
-      </c>
-      <c r="T92" s="9">
-        <v>3</v>
-      </c>
-      <c r="U92" s="9">
-        <v>7</v>
-      </c>
-      <c r="V92" s="9">
+        <v>1.2599607657310419</v>
+      </c>
+      <c r="T92" s="10">
+        <v>6</v>
+      </c>
+      <c r="U92" s="10">
+        <v>11</v>
+      </c>
+      <c r="V92" s="10">
         <v>4</v>
       </c>
       <c r="W92" s="9">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="X92" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y92" s="10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z92" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA92" s="10">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="AA92" s="9">
+        <v>17</v>
       </c>
       <c r="AB92" s="9">
-        <v>0.42857142857142855</v>
+        <v>0.80952380952380953</v>
       </c>
       <c r="AC92" s="11">
         <f t="shared" si="2"/>
-        <v>1.3501234968962521</v>
+        <v>1.5495630437927677</v>
       </c>
     </row>
     <row r="93" spans="1:29" ht="17">
       <c r="A93" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B93" s="2">
         <v>100</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="D93" s="2">
-        <v>105</v>
+        <v>497</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F93" s="2">
-        <v>9.7200000000000006</v>
+        <v>55.2</v>
       </c>
       <c r="G93" s="2">
-        <v>10.288065843621398</v>
+        <v>1.8115942028985506</v>
       </c>
       <c r="H93" s="9">
-        <v>-5.258</v>
+        <v>2.2519999999999998</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J93" s="2">
         <v>72</v>
       </c>
       <c r="K93" s="9">
-        <v>35.959000000000003</v>
+        <v>51.399000000000001</v>
       </c>
       <c r="L93" s="9">
-        <v>2.0022803748713813</v>
+        <v>1.4008054631413063</v>
       </c>
       <c r="M93" s="10">
         <v>509.061894</v>
@@ -9648,16 +9638,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P93" s="10">
-        <v>404.02995700000002</v>
+        <v>514.78644799999995</v>
       </c>
       <c r="Q93" s="10">
-        <v>219.08395200000001</v>
+        <v>268.82490200000001</v>
       </c>
       <c r="R93" s="10">
-        <v>184.94590600000001</v>
+        <v>245.96151399999999</v>
       </c>
       <c r="S93" s="9">
-        <v>1.2599607657310419</v>
+        <v>0.98887974999683759</v>
       </c>
       <c r="T93" s="10">
         <v>6</v>
@@ -9672,61 +9662,61 @@
         <v>21</v>
       </c>
       <c r="X93" s="10">
+        <v>9</v>
+      </c>
+      <c r="Y93" s="10">
         <v>4</v>
       </c>
-      <c r="Y93" s="10">
-        <v>8</v>
-      </c>
       <c r="Z93" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA93" s="9">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AB93" s="9">
-        <v>0.80952380952380953</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AC93" s="11">
         <f t="shared" si="2"/>
-        <v>1.5495630437927677</v>
+        <v>2.3023600011412455</v>
       </c>
     </row>
     <row r="94" spans="1:29" ht="17">
       <c r="A94" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B94" s="2">
         <v>100</v>
       </c>
       <c r="C94" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D94" s="2">
+        <v>601</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D94" s="2">
-        <v>497</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="F94" s="2">
-        <v>55.2</v>
+        <v>26.8</v>
       </c>
       <c r="G94" s="2">
-        <v>1.8115942028985506</v>
+        <v>3.7313432835820897</v>
       </c>
       <c r="H94" s="9">
-        <v>2.2519999999999998</v>
+        <v>11.231999999999999</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J94" s="2">
         <v>72</v>
       </c>
       <c r="K94" s="9">
-        <v>51.399000000000001</v>
+        <v>45.908000000000001</v>
       </c>
       <c r="L94" s="9">
-        <v>1.4008054631413063</v>
+        <v>1.5683540995033545</v>
       </c>
       <c r="M94" s="10">
         <v>509.061894</v>
@@ -9738,16 +9728,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P94" s="10">
-        <v>514.78644799999995</v>
+        <v>194.02388099999999</v>
       </c>
       <c r="Q94" s="10">
-        <v>268.82490200000001</v>
+        <v>79.629563000000005</v>
       </c>
       <c r="R94" s="10">
-        <v>245.96151399999999</v>
+        <v>114.394385</v>
       </c>
       <c r="S94" s="9">
-        <v>0.98887974999683759</v>
+        <v>2.6237074084710224</v>
       </c>
       <c r="T94" s="10">
         <v>6</v>
@@ -9762,61 +9752,61 @@
         <v>21</v>
       </c>
       <c r="X94" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y94" s="10">
+        <v>2</v>
+      </c>
+      <c r="Z94" s="10">
+        <v>1</v>
+      </c>
+      <c r="AA94" s="9">
         <v>4</v>
       </c>
-      <c r="Z94" s="10">
-        <v>2</v>
-      </c>
-      <c r="AA94" s="9">
-        <v>15</v>
-      </c>
       <c r="AB94" s="9">
-        <v>0.7142857142857143</v>
+        <v>0.19047619047619047</v>
       </c>
       <c r="AC94" s="11">
         <f t="shared" si="2"/>
-        <v>2.3023600011412455</v>
+        <v>1.4316459004966455</v>
       </c>
     </row>
     <row r="95" spans="1:29" ht="17">
       <c r="A95" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B95" s="2">
         <v>100</v>
       </c>
       <c r="C95" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D95" s="2">
+        <v>565</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D95" s="2">
-        <v>601</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="F95" s="2">
-        <v>26.8</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="G95" s="2">
-        <v>3.7313432835820897</v>
+        <v>2.8409090909090908</v>
       </c>
       <c r="H95" s="9">
-        <v>11.231999999999999</v>
+        <v>6.12</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J95" s="2">
         <v>72</v>
       </c>
       <c r="K95" s="9">
-        <v>45.908000000000001</v>
+        <v>63.408999999999999</v>
       </c>
       <c r="L95" s="9">
-        <v>1.5683540995033545</v>
+        <v>1.1354854989039411</v>
       </c>
       <c r="M95" s="10">
         <v>509.061894</v>
@@ -9828,16 +9818,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P95" s="10">
-        <v>194.02388099999999</v>
+        <v>548.452405</v>
       </c>
       <c r="Q95" s="10">
-        <v>79.629563000000005</v>
+        <v>272.29945600000002</v>
       </c>
       <c r="R95" s="10">
-        <v>114.394385</v>
+        <v>276.15266400000002</v>
       </c>
       <c r="S95" s="9">
-        <v>2.6237074084710224</v>
+        <v>0.92817879793963165</v>
       </c>
       <c r="T95" s="10">
         <v>6</v>
@@ -9852,61 +9842,61 @@
         <v>21</v>
       </c>
       <c r="X95" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y95" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z95" s="10">
         <v>1</v>
       </c>
       <c r="AA95" s="9">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AB95" s="9">
-        <v>0.19047619047619047</v>
+        <v>0.76190476190476186</v>
       </c>
       <c r="AC95" s="11">
         <f t="shared" si="2"/>
-        <v>1.4316459004966455</v>
+        <v>2.5545980609404522</v>
       </c>
     </row>
     <row r="96" spans="1:29" ht="17">
       <c r="A96" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B96" s="2">
         <v>100</v>
       </c>
       <c r="C96" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D96" s="2">
+        <v>225</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D96" s="2">
-        <v>565</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="F96" s="2">
-        <v>35.200000000000003</v>
+        <v>15.7</v>
       </c>
       <c r="G96" s="2">
-        <v>2.8409090909090908</v>
+        <v>6.369426751592357</v>
       </c>
       <c r="H96" s="9">
-        <v>6.12</v>
+        <v>31.081</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J96" s="2">
         <v>72</v>
       </c>
       <c r="K96" s="9">
-        <v>63.408999999999999</v>
+        <v>74.661000000000001</v>
       </c>
       <c r="L96" s="9">
-        <v>1.1354854989039411</v>
+        <v>0.96435890223811627</v>
       </c>
       <c r="M96" s="10">
         <v>509.061894</v>
@@ -9918,16 +9908,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P96" s="10">
-        <v>548.452405</v>
+        <v>324.99903799999998</v>
       </c>
       <c r="Q96" s="10">
-        <v>272.29945600000002</v>
+        <v>195.09350000000001</v>
       </c>
       <c r="R96" s="10">
-        <v>276.15266400000002</v>
+        <v>129.90543299999999</v>
       </c>
       <c r="S96" s="9">
-        <v>0.92817879793963165</v>
+        <v>1.5663489256235892</v>
       </c>
       <c r="T96" s="10">
         <v>6</v>
@@ -9942,61 +9932,61 @@
         <v>21</v>
       </c>
       <c r="X96" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y96" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z96" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA96" s="9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AB96" s="9">
-        <v>0.76190476190476186</v>
+        <v>0.47619047619047616</v>
       </c>
       <c r="AC96" s="11">
         <f t="shared" si="2"/>
-        <v>2.5545980609404522</v>
+        <v>1.9643589022381163</v>
       </c>
     </row>
     <row r="97" spans="1:29" ht="17">
       <c r="A97" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B97" s="2">
         <v>100</v>
       </c>
       <c r="C97" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D97" s="2">
+        <v>801</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D97" s="2">
-        <v>225</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="F97" s="2">
-        <v>15.7</v>
+        <v>158</v>
       </c>
       <c r="G97" s="2">
-        <v>6.369426751592357</v>
+        <v>0.63291139240506333</v>
       </c>
       <c r="H97" s="9">
-        <v>31.081</v>
+        <v>15.066000000000001</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J97" s="2">
         <v>72</v>
       </c>
       <c r="K97" s="9">
-        <v>74.661000000000001</v>
+        <v>72.995999999999995</v>
       </c>
       <c r="L97" s="9">
-        <v>0.96435890223811627</v>
+        <v>0.98635541673516358</v>
       </c>
       <c r="M97" s="10">
         <v>509.061894</v>
@@ -10008,16 +9998,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P97" s="10">
-        <v>324.99903799999998</v>
+        <v>352.63704300000001</v>
       </c>
       <c r="Q97" s="10">
-        <v>195.09350000000001</v>
+        <v>187.83172200000001</v>
       </c>
       <c r="R97" s="10">
-        <v>129.90543299999999</v>
+        <v>164.805374</v>
       </c>
       <c r="S97" s="9">
-        <v>1.5663489256235892</v>
+        <v>1.443585987646794</v>
       </c>
       <c r="T97" s="10">
         <v>6</v>
@@ -10032,7 +10022,7 @@
         <v>21</v>
       </c>
       <c r="X97" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y97" s="10">
         <v>3</v>
@@ -10041,232 +10031,232 @@
         <v>2</v>
       </c>
       <c r="AA97" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB97" s="9">
-        <v>0.47619047619047616</v>
+        <v>0.52380952380952384</v>
       </c>
       <c r="AC97" s="11">
         <f t="shared" si="2"/>
-        <v>1.9643589022381163</v>
+        <v>2.0665789528978933</v>
       </c>
     </row>
     <row r="98" spans="1:29" ht="17">
       <c r="A98" s="2" t="s">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="B98" s="2">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>203</v>
       </c>
       <c r="D98" s="2">
-        <v>801</v>
+        <v>221</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>204</v>
       </c>
       <c r="F98" s="2">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="G98" s="2">
-        <v>0.63291139240506333</v>
+        <v>1.9557522123893805</v>
       </c>
       <c r="H98" s="9">
-        <v>15.066000000000001</v>
+        <v>7.7590000000000003</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J98" s="2">
         <v>72</v>
       </c>
       <c r="K98" s="9">
-        <v>72.995999999999995</v>
+        <v>41.021000000000001</v>
       </c>
       <c r="L98" s="9">
-        <v>0.98635541673516358</v>
+        <v>1.7551985568367421</v>
       </c>
       <c r="M98" s="10">
-        <v>509.061894</v>
+        <v>328.36152499999997</v>
       </c>
       <c r="N98" s="10">
-        <v>304.09381500000001</v>
+        <v>200.67168100000001</v>
       </c>
       <c r="O98" s="10">
-        <v>204.96811299999999</v>
+        <v>127.689595</v>
       </c>
       <c r="P98" s="10">
-        <v>352.63704300000001</v>
+        <v>387.54889100000003</v>
       </c>
       <c r="Q98" s="10">
-        <v>187.83172200000001</v>
+        <v>221.91251700000001</v>
       </c>
       <c r="R98" s="10">
-        <v>164.805374</v>
+        <v>165.63628199999999</v>
       </c>
       <c r="S98" s="9">
-        <v>1.443585987646794</v>
+        <v>0.84727767934704257</v>
       </c>
       <c r="T98" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U98" s="10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V98" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W98" s="9">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="X98" s="10">
         <v>6</v>
       </c>
       <c r="Y98" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z98" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA98" s="9">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB98" s="9">
-        <v>0.52380952380952384</v>
+        <v>0.75</v>
       </c>
       <c r="AC98" s="11">
         <f t="shared" si="2"/>
-        <v>2.0665789528978933</v>
+        <v>1.8420791225103006</v>
       </c>
     </row>
     <row r="99" spans="1:29" ht="17">
       <c r="A99" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B99" s="2">
+        <v>100</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D99" s="2">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B99" s="2">
-        <v>259</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D99" s="2">
-        <v>221</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="F99" s="2">
-        <v>113</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="G99" s="2">
-        <v>1.9557522123893805</v>
+        <v>0.28164251207729468</v>
       </c>
       <c r="H99" s="9">
-        <v>7.7590000000000003</v>
+        <v>9.6210000000000004</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J99" s="2">
         <v>72</v>
       </c>
       <c r="K99" s="9">
-        <v>41.021000000000001</v>
+        <v>60.319000000000003</v>
       </c>
       <c r="L99" s="9">
-        <v>1.7551985568367421</v>
+        <v>1.1936537409439811</v>
       </c>
       <c r="M99" s="10">
-        <v>328.36152499999997</v>
+        <v>509.061894</v>
       </c>
       <c r="N99" s="10">
-        <v>200.67168100000001</v>
+        <v>304.09381500000001</v>
       </c>
       <c r="O99" s="10">
-        <v>127.689595</v>
-      </c>
-      <c r="P99" s="10">
-        <v>387.54889100000003</v>
-      </c>
-      <c r="Q99" s="10">
-        <v>221.91251700000001</v>
-      </c>
-      <c r="R99" s="10">
-        <v>165.63628199999999</v>
+        <v>204.96811299999999</v>
+      </c>
+      <c r="P99" s="9">
+        <v>467.95458200000007</v>
+      </c>
+      <c r="Q99" s="9">
+        <v>266.86430700000005</v>
+      </c>
+      <c r="R99" s="9">
+        <v>201.09016000000003</v>
       </c>
       <c r="S99" s="9">
-        <v>0.84727767934704257</v>
+        <v>1.0878446618137825</v>
       </c>
       <c r="T99" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U99" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V99" s="10">
+        <v>4</v>
+      </c>
+      <c r="W99" s="9">
+        <v>21</v>
+      </c>
+      <c r="X99" s="9">
+        <v>9</v>
+      </c>
+      <c r="Y99" s="9">
+        <v>4</v>
+      </c>
+      <c r="Z99" s="9">
         <v>1</v>
       </c>
-      <c r="W99" s="9">
-        <v>12</v>
-      </c>
-      <c r="X99" s="10">
-        <v>6</v>
-      </c>
-      <c r="Y99" s="10">
-        <v>2</v>
-      </c>
-      <c r="Z99" s="10">
-        <v>1</v>
-      </c>
       <c r="AA99" s="9">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AB99" s="9">
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AC99" s="11">
         <f t="shared" si="2"/>
-        <v>1.8420791225103006</v>
+        <v>2.3851682639089029</v>
       </c>
     </row>
     <row r="100" spans="1:29" ht="17">
       <c r="A100" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B100" s="2">
         <v>100</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>88</v>
+        <v>185</v>
       </c>
       <c r="D100" s="2">
-        <v>0.58299999999999996</v>
+        <v>1750</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F100" s="2">
-        <v>2.0699999999999998</v>
+        <v>109</v>
       </c>
       <c r="G100" s="2">
-        <v>0.28164251207729468</v>
+        <v>0.91743119266055051</v>
       </c>
       <c r="H100" s="9">
-        <v>9.6210000000000004</v>
+        <v>11.367000000000001</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J100" s="2">
         <v>72</v>
       </c>
       <c r="K100" s="9">
-        <v>60.319000000000003</v>
+        <v>31.901</v>
       </c>
       <c r="L100" s="9">
-        <v>1.1936537409439811</v>
+        <v>2.2569825397322969</v>
       </c>
       <c r="M100" s="10">
         <v>509.061894</v>
@@ -10278,16 +10268,16 @@
         <v>204.96811299999999</v>
       </c>
       <c r="P100" s="9">
-        <v>467.95458200000007</v>
+        <v>171.45177000000001</v>
       </c>
       <c r="Q100" s="9">
-        <v>266.86430700000005</v>
+        <v>110.238232</v>
       </c>
       <c r="R100" s="9">
-        <v>201.09016000000003</v>
+        <v>61.213506000000002</v>
       </c>
       <c r="S100" s="9">
-        <v>1.0878446618137825</v>
+        <v>2.9691259180351417</v>
       </c>
       <c r="T100" s="10">
         <v>6</v>
@@ -10302,241 +10292,241 @@
         <v>21</v>
       </c>
       <c r="X100" s="9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y100" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z100" s="9">
+        <v>2</v>
+      </c>
+      <c r="AA100" s="9">
+        <v>6</v>
+      </c>
+      <c r="AB100" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AC100" s="11">
+        <f t="shared" ref="AC100:AC103" si="5">(1-MIN(ABS(L100-1),1))+(1-MIN(ABS(S100-1),0.5))+(1-MIN(ABS(AB100-1),0.5))</f>
         <v>1</v>
-      </c>
-      <c r="AA100" s="9">
-        <v>14</v>
-      </c>
-      <c r="AB100" s="9">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AC100" s="11">
-        <f t="shared" si="2"/>
-        <v>2.3851682639089029</v>
       </c>
     </row>
     <row r="101" spans="1:29" ht="17">
       <c r="A101" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B101" s="2">
+        <v>259</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B101" s="2">
-        <v>100</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="D101" s="2">
-        <v>1750</v>
+        <v>4370</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F101" s="2">
-        <v>109</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="G101" s="2">
-        <v>0.91743119266055051</v>
+        <v>3.4952766531713904</v>
       </c>
       <c r="H101" s="9">
-        <v>11.367000000000001</v>
+        <v>-7.633</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J101" s="2">
         <v>72</v>
       </c>
       <c r="K101" s="9">
-        <v>31.901</v>
+        <v>23.245999999999999</v>
       </c>
       <c r="L101" s="9">
-        <v>2.2569825397322969</v>
+        <v>3.0973070635808311</v>
       </c>
       <c r="M101" s="10">
-        <v>509.061894</v>
+        <v>328.36152499999997</v>
       </c>
       <c r="N101" s="10">
-        <v>304.09381500000001</v>
+        <v>200.67168100000001</v>
       </c>
       <c r="O101" s="10">
-        <v>204.96811299999999</v>
+        <v>127.689595</v>
       </c>
       <c r="P101" s="9">
-        <v>171.45177000000001</v>
+        <v>167.93623199999999</v>
       </c>
       <c r="Q101" s="9">
-        <v>110.238232</v>
+        <v>97.028190999999993</v>
       </c>
       <c r="R101" s="9">
-        <v>61.213506000000002</v>
+        <v>70.907809999999998</v>
       </c>
       <c r="S101" s="9">
-        <v>2.9691259180351417</v>
+        <v>1.95527505345005</v>
       </c>
       <c r="T101" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U101" s="10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V101" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="X101" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y101" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z101" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="9">
         <v>2</v>
       </c>
-      <c r="AA101" s="9">
-        <v>6</v>
-      </c>
       <c r="AB101" s="9">
-        <v>0.2857142857142857</v>
+        <v>0.16666666699999999</v>
       </c>
       <c r="AC101" s="11">
-        <f t="shared" ref="AC101:AC104" si="5">(1-MIN(ABS(L101-1),1))+(1-MIN(ABS(S101-1),0.5))+(1-MIN(ABS(AB101-1),0.5))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:29" ht="17">
       <c r="A102" s="2" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="B102" s="2">
-        <v>259</v>
+        <v>4370</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D102" s="2">
-        <v>4370</v>
+        <v>921</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F102" s="2">
-        <v>74.099999999999994</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="G102" s="2">
-        <v>3.4952766531713904</v>
+        <v>13.870481927710841</v>
       </c>
       <c r="H102" s="9">
-        <v>-7.633</v>
+        <v>38.121000000000002</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J102" s="2">
         <v>72</v>
       </c>
       <c r="K102" s="9">
-        <v>23.245999999999999</v>
+        <v>52.271000000000001</v>
       </c>
       <c r="L102" s="9">
-        <v>3.0973070635808311</v>
-      </c>
-      <c r="M102" s="10">
-        <v>328.36152499999997</v>
-      </c>
-      <c r="N102" s="10">
-        <v>200.67168100000001</v>
-      </c>
-      <c r="O102" s="10">
-        <v>127.689595</v>
-      </c>
-      <c r="P102" s="9">
+        <v>1.3774368196514319</v>
+      </c>
+      <c r="M102" s="9">
         <v>167.93623199999999</v>
       </c>
-      <c r="Q102" s="9">
+      <c r="N102" s="9">
         <v>97.028190999999993</v>
       </c>
-      <c r="R102" s="9">
+      <c r="O102" s="9">
         <v>70.907809999999998</v>
       </c>
+      <c r="P102" s="10">
+        <v>268.55290300000001</v>
+      </c>
+      <c r="Q102" s="10">
+        <v>185.45786000000001</v>
+      </c>
+      <c r="R102" s="10">
+        <v>83.095070000000007</v>
+      </c>
       <c r="S102" s="9">
-        <v>1.95527505345005</v>
-      </c>
-      <c r="T102" s="10">
+        <v>0.62533761550885181</v>
+      </c>
+      <c r="T102" s="9">
+        <v>2</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>2</v>
+      </c>
+      <c r="X102" s="10">
         <v>3</v>
       </c>
-      <c r="U102" s="10">
-        <v>8</v>
-      </c>
-      <c r="V102" s="10">
+      <c r="Y102" s="10">
         <v>1</v>
       </c>
-      <c r="W102" s="9">
-        <v>12</v>
-      </c>
-      <c r="X102" s="9">
+      <c r="Z102" s="10">
         <v>2</v>
       </c>
-      <c r="Y102" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="9">
-        <v>2</v>
+      <c r="AA102" s="10">
+        <v>6</v>
       </c>
       <c r="AB102" s="9">
-        <v>0.16666666699999999</v>
+        <v>3</v>
       </c>
       <c r="AC102" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.74790079585742</v>
       </c>
     </row>
     <row r="103" spans="1:29" ht="17">
       <c r="A103" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B103" s="2">
         <v>4370</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D103" s="2">
-        <v>921</v>
+        <v>2060</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F103" s="2">
-        <v>66.400000000000006</v>
+        <v>71.3</v>
       </c>
       <c r="G103" s="2">
-        <v>13.870481927710841</v>
+        <v>28.892005610098177</v>
       </c>
       <c r="H103" s="9">
-        <v>38.121000000000002</v>
+        <v>-6.1219999999999999</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J103" s="2">
         <v>72</v>
       </c>
       <c r="K103" s="9">
-        <v>52.271000000000001</v>
+        <v>30.571999999999999</v>
       </c>
       <c r="L103" s="9">
-        <v>1.3774368196514319</v>
+        <v>2.355096166426796</v>
       </c>
       <c r="M103" s="9">
         <v>167.93623199999999</v>
@@ -10548,16 +10538,16 @@
         <v>70.907809999999998</v>
       </c>
       <c r="P103" s="10">
-        <v>268.55290300000001</v>
+        <v>320.9597</v>
       </c>
       <c r="Q103" s="10">
-        <v>185.45786000000001</v>
+        <v>180.52893700000001</v>
       </c>
       <c r="R103" s="10">
-        <v>83.095070000000007</v>
+        <v>140.43079800000001</v>
       </c>
       <c r="S103" s="9">
-        <v>0.62533761550885181</v>
+        <v>0.52323152096665093</v>
       </c>
       <c r="T103" s="9">
         <v>2</v>
@@ -10572,111 +10562,21 @@
         <v>2</v>
       </c>
       <c r="X103" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y103" s="10">
+        <v>14</v>
+      </c>
+      <c r="Z103" s="10">
         <v>1</v>
       </c>
-      <c r="Z103" s="10">
-        <v>2</v>
-      </c>
       <c r="AA103" s="10">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AB103" s="9">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="AC103" s="11">
-        <f t="shared" si="5"/>
-        <v>1.74790079585742</v>
-      </c>
-    </row>
-    <row r="104" spans="1:29" ht="17">
-      <c r="A104" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B104" s="2">
-        <v>4370</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D104" s="2">
-        <v>2060</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F104" s="2">
-        <v>71.3</v>
-      </c>
-      <c r="G104" s="2">
-        <v>28.892005610098177</v>
-      </c>
-      <c r="H104" s="9">
-        <v>-6.1219999999999999</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J104" s="2">
-        <v>72</v>
-      </c>
-      <c r="K104" s="9">
-        <v>30.571999999999999</v>
-      </c>
-      <c r="L104" s="9">
-        <v>2.355096166426796</v>
-      </c>
-      <c r="M104" s="9">
-        <v>167.93623199999999</v>
-      </c>
-      <c r="N104" s="9">
-        <v>97.028190999999993</v>
-      </c>
-      <c r="O104" s="9">
-        <v>70.907809999999998</v>
-      </c>
-      <c r="P104" s="10">
-        <v>320.9597</v>
-      </c>
-      <c r="Q104" s="10">
-        <v>180.52893700000001</v>
-      </c>
-      <c r="R104" s="10">
-        <v>140.43079800000001</v>
-      </c>
-      <c r="S104" s="9">
-        <v>0.52323152096665093</v>
-      </c>
-      <c r="T104" s="9">
-        <v>2</v>
-      </c>
-      <c r="U104" s="9">
-        <v>0</v>
-      </c>
-      <c r="V104" s="9">
-        <v>0</v>
-      </c>
-      <c r="W104" s="9">
-        <v>2</v>
-      </c>
-      <c r="X104" s="10">
-        <v>2</v>
-      </c>
-      <c r="Y104" s="10">
-        <v>14</v>
-      </c>
-      <c r="Z104" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA104" s="10">
-        <v>17</v>
-      </c>
-      <c r="AB104" s="9">
-        <v>8.5</v>
-      </c>
-      <c r="AC104" s="11">
         <f t="shared" si="5"/>
         <v>1.0232315209666509</v>
       </c>
